--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VSCode\Test\my-vue-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DC2929-25F2-4762-BAC5-B1C2CE1A5DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7448D40-B386-424A-BB47-ACDDCEEEFA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{BFCE4DB1-B638-4533-A727-1E11ECBF49A7}"/>
+    <workbookView xWindow="-26130" yWindow="2265" windowWidth="25425" windowHeight="12285" xr2:uid="{BFCE4DB1-B638-4533-A727-1E11ECBF49A7}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="777">
   <si>
     <t>Category</t>
   </si>
@@ -120,9 +120,6 @@
     <t>櫻桃蘿蔔濃湯</t>
   </si>
   <si>
-    <t>味增湯</t>
-  </si>
-  <si>
     <t>玉米濃湯</t>
   </si>
   <si>
@@ -141,9 +138,6 @@
     <t>蛋花湯</t>
   </si>
   <si>
-    <t>起司蛋烤餅</t>
-  </si>
-  <si>
     <t>麵粉</t>
   </si>
   <si>
@@ -174,9 +168,6 @@
     <t>司康餅</t>
   </si>
   <si>
-    <t>法式鹽薄餅</t>
-  </si>
-  <si>
     <t>奶油麵包捲</t>
   </si>
   <si>
@@ -225,9 +216,6 @@
     <t>花椰菜</t>
   </si>
   <si>
-    <t>蒜炒花椰菜</t>
-  </si>
-  <si>
     <t>涼拌豆腐</t>
   </si>
   <si>
@@ -309,12 +297,6 @@
     <t>溫泉蛋</t>
   </si>
   <si>
-    <t>烤蕃薯</t>
-  </si>
-  <si>
-    <t>蕃薯</t>
-  </si>
-  <si>
     <t>麵包</t>
   </si>
   <si>
@@ -330,12 +312,6 @@
     <t>稻米</t>
   </si>
   <si>
-    <t>終極咖喱</t>
-  </si>
-  <si>
-    <t>頂級咖喱</t>
-  </si>
-  <si>
     <t>炒米粉</t>
   </si>
   <si>
@@ -381,9 +357,6 @@
     <t>義大利麵沙拉</t>
   </si>
   <si>
-    <t>松茸飯</t>
-  </si>
-  <si>
     <t>焗烤筆管麵</t>
   </si>
   <si>
@@ -408,40 +381,19 @@
     <t>豆皮壽司</t>
   </si>
   <si>
-    <t>辣味咖喱</t>
-  </si>
-  <si>
-    <t>蛋包飯</t>
-  </si>
-  <si>
     <t>歐姆蛋</t>
   </si>
   <si>
-    <t>蒜味辣椒義大利麵</t>
-  </si>
-  <si>
-    <t>海苔咖喱</t>
-  </si>
-  <si>
     <t>果醬麵包</t>
   </si>
   <si>
-    <t>牛奶咖喱</t>
-  </si>
-  <si>
     <t>熱油火鍋</t>
   </si>
   <si>
     <t>炒飯</t>
   </si>
   <si>
-    <t>彩虹咖喱</t>
-  </si>
-  <si>
     <t>炒蕎麥麵</t>
-  </si>
-  <si>
-    <t>鰻魚蓋飯</t>
   </si>
   <si>
     <t>烤松茸</t>
@@ -1037,10 +989,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>醃製甜椒</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>綜合沙拉</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1060,10 +1008,6 @@
     <t>甜椒、醋、油-堅果油-香草油-橄欖油-葡萄籽油</t>
   </si>
   <si>
-    <t>櫻桃蘿蔔、洋蔥、橄欖油、蜂蜜、清爽蜂蜜、滑順蜂蜜、皇家蜂蜜</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Ingredients</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1290,9 +1234,6 @@
     <t>砂糖、鹽、胡椒、油</t>
   </si>
   <si>
-    <t>白菜、醬油、砂糖、鹽、胡椒、味增、醋</t>
-  </si>
-  <si>
     <t>胡蘿蔔、青椒、蘆筍、南瓜、鹽、胡椒</t>
   </si>
   <si>
@@ -1311,9 +1252,6 @@
     <t>起司、香草起司、頂級起司</t>
   </si>
   <si>
-    <t>大蒜、鹽、胡椒、油、堅果油、香草油、橄欖油、味增</t>
-  </si>
-  <si>
     <t>番茄、起司、香草起司、頂級起司、砂糖、鹽</t>
   </si>
   <si>
@@ -1404,12 +1342,6 @@
     <t>起司、香草起司、頂級起司、奶油、香草奶油、頂級奶油、鹽、胡椒</t>
   </si>
   <si>
-    <t>起司、香草起司、頂級起司、蜂蜜、清爽蜂蜜、滑順蜂蜜、皇家蜂蜜、砂糖</t>
-  </si>
-  <si>
-    <t>奶油、香草奶油、頂級奶油、醬油、砂糖、咖喱粉、蜂蜜、清爽蜂蜜、滑順蜂蜜、皇家蜂蜜</t>
-  </si>
-  <si>
     <t>番茄、美乃滋、香草美乃滋、頂級美乃滋、麵粉、鹽、胡椒</t>
   </si>
   <si>
@@ -1431,9 +1363,6 @@
     <t>洋蔥、青椒、醬油、胡椒、油</t>
   </si>
   <si>
-    <t>堅果油、香草油、南瓜籽油、葡萄籽油</t>
-  </si>
-  <si>
     <t>巨大番茄、結實洋蔥、黃金蘋果、頂級牛奶、頂級水牛奶</t>
   </si>
   <si>
@@ -1617,9 +1546,6 @@
     <t>青蔥、醬油、鹽</t>
   </si>
   <si>
-    <t>蕃薯、瓶裝栗子、鹽</t>
-  </si>
-  <si>
     <t>番茄、小黃瓜、大蒜、茄子、起司、香草起司、頂級起司</t>
   </si>
   <si>
@@ -1641,9 +1567,6 @@
     <t>檸檬、奶油、香草奶油、頂級奶油、砂糖</t>
   </si>
   <si>
-    <t>蕃薯、奶油、香草奶油、頂級奶油、米穀粉、砂糖</t>
-  </si>
-  <si>
     <t>牛奶、水牛奶、奶油、香草奶油、頂級奶油</t>
   </si>
   <si>
@@ -1701,9 +1624,6 @@
     <t>黃豆粉、砂糖、醬油、海苔</t>
   </si>
   <si>
-    <t>蕃薯、砂糖、鹽</t>
-  </si>
-  <si>
     <t>檸檬、蜂蜜、清爽蜂蜜、滑順蜂蜜、皇家蜂蜜、奶油、香草奶油、頂級奶油、砂糖、餅乾</t>
   </si>
   <si>
@@ -1782,586 +1702,706 @@
     <t>頂級牛奶、果實優格、皇家蜂蜜</t>
   </si>
   <si>
+    <t>番茄、薄荷-洋甘菊-薰衣草</t>
+  </si>
+  <si>
+    <t>番茄、起司-香草起司-頂級起司、橄欖油、鹽</t>
+  </si>
+  <si>
+    <t>酪梨、鮭魚、醬油</t>
+  </si>
+  <si>
+    <t>馬鈴薯、奶油-香草奶油-頂級奶油</t>
+  </si>
+  <si>
+    <t>蘆筍、牛奶-水牛奶、油-堅果油-香草油-橄欖油-葡萄籽油、洋蔥</t>
+  </si>
+  <si>
+    <t>洋蔥、奶油-香草奶油-頂級奶油</t>
+  </si>
+  <si>
+    <t>櫻桃蘿蔔、牛奶-水牛奶、鹽</t>
+  </si>
+  <si>
+    <t>南瓜、牛奶-水牛奶、洋蔥</t>
+  </si>
+  <si>
+    <t>馬鈴薯、洋蔥、牛奶-水牛奶</t>
+  </si>
+  <si>
+    <t>番茄、大蒜、麵包-白麵包-長棍麵包-佛卡夏</t>
+  </si>
+  <si>
+    <t>蛋-烏骨雞蛋</t>
+  </si>
+  <si>
+    <t>麵粉、頂級起司、頂級優格、頂級奶油</t>
+  </si>
+  <si>
+    <t>羊肚菌、水牛奶、奶油-香草奶油-頂級奶油、海膽</t>
+  </si>
+  <si>
+    <t>麵粉、菠菜、南瓜、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇</t>
+  </si>
+  <si>
+    <t>麵粉、香菇、胡蘿蔔、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>麵粉、白菜、香菇、青蔥</t>
+  </si>
+  <si>
+    <t>麵粉、高麗菜、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>高麗菜、白菜</t>
+  </si>
+  <si>
+    <t>高麗菜、胡蘿蔔</t>
+  </si>
+  <si>
+    <t>麵粉、奶油-香草奶油-頂級奶油、牛奶-水牛奶</t>
+  </si>
+  <si>
+    <t>蕎麥粉、馬鈴薯、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油</t>
+  </si>
+  <si>
+    <t>番茄、豆子、辣椒、胡椒</t>
+  </si>
+  <si>
+    <t>蕪菁、奶油-香草奶油-頂級奶油</t>
+  </si>
+  <si>
+    <t>麵粉、橄欖油</t>
+  </si>
+  <si>
+    <t>豆腐、醬油、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>豆腐、麵粉-米穀粉、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>蛋-烏骨雞蛋、醬油、砂糖</t>
+  </si>
+  <si>
+    <t>蛋-烏骨雞蛋、香菇、魚板</t>
+  </si>
+  <si>
+    <t>豆腐、胡蘿蔔</t>
+  </si>
+  <si>
+    <t>麵粉、鹽</t>
+  </si>
+  <si>
+    <t>馬鈴薯、麵粉、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>綠花椰菜、大蒜、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>豆腐、醬油</t>
+  </si>
+  <si>
+    <t>馬鈴薯、麵粉、蛋-烏骨雞蛋</t>
+  </si>
+  <si>
+    <t>蛋-烏骨雞蛋、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>麵包-白麵包</t>
+  </si>
+  <si>
+    <t>豆子、豆漿</t>
+  </si>
+  <si>
+    <t>香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇</t>
+  </si>
+  <si>
+    <t>柳根魚-珠星三塊魚-日本溪哥-鈍頭杜父魚-特氏東瀛鯉-黑腹鱊-長頜鬚鮈-虹鱒-鰱魚-博氏巨鯰</t>
+  </si>
+  <si>
+    <t>白菜、胡蘿蔔、青椒、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇</t>
+  </si>
+  <si>
+    <t>玉蜀黍、醬油、砂糖</t>
+  </si>
+  <si>
+    <t>馬鈴薯、麵包粉-白麵包粉、油-堅果油-香草油-橄欖油-葡萄籽油、起司-香草起司-頂級起司</t>
+  </si>
+  <si>
+    <t>麵粉、起司-香草起司-頂級起司、水牛奶</t>
+  </si>
+  <si>
+    <t>馬鈴薯、麵包粉-白麵包粉、油-堅果油-香草油-橄欖油-葡萄籽油、牛奶-水牛奶</t>
+  </si>
+  <si>
+    <t>麵粉、牛奶-水牛奶、馬鈴薯-蘆筍-胡蘿蔔-高麗菜-蕪菁-花椰菜</t>
+  </si>
+  <si>
+    <t>馬鈴薯、麵包粉-白麵包粉、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>麵包-白麵包、蛋-烏骨雞蛋、牛奶-水牛奶</t>
+  </si>
+  <si>
+    <t>玉蜀黍、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>馬鈴薯、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>蛋-烏骨雞蛋、醬油</t>
+  </si>
+  <si>
+    <t>米穀粉、國王菇、高麗菜、胡蘿蔔</t>
+  </si>
+  <si>
+    <t>馬鈴薯、洋蔥、頂級起司、頂級美乃滋</t>
+  </si>
+  <si>
+    <t>蕎麥粉、起司-香草起司-頂級起司、高麗菜、馬鈴薯</t>
+  </si>
+  <si>
+    <t>蕎麥粉、天婦羅</t>
+  </si>
+  <si>
+    <t>頂級牛奶、胡蘿蔔、白菜、菠菜</t>
+  </si>
+  <si>
+    <t>麵粉、起司-香草起司-頂級起司、奶油-香草奶油-頂級奶油、美乃滋-香草美乃滋-頂級美乃滋</t>
+  </si>
+  <si>
+    <t>麵粉、天婦羅</t>
+  </si>
+  <si>
+    <t>天婦羅、米飯</t>
+  </si>
+  <si>
+    <t>起司-香草起司-頂級起司、玉蜀黍、胡蘿蔔、綠花椰菜</t>
+  </si>
+  <si>
+    <t>義大利麵、綜合沙拉、美乃滋-香草美乃滋-頂級美乃滋</t>
+  </si>
+  <si>
+    <t>稻米、松茸、醬油</t>
+  </si>
+  <si>
+    <t>麵粉、起司-香草起司-頂級起司、美乃滋-香草美乃滋-頂級美乃滋</t>
+  </si>
+  <si>
+    <t>稻米、起司-香草起司-頂級起司、番茄、洋蔥</t>
+  </si>
+  <si>
+    <t>起司-香草起司-頂級起司、麵包-白麵包-長棍麵包-佛卡夏、綠花椰菜-馬鈴薯-蘆筍-甜椒-胡蘿蔔-洋菇-南瓜</t>
+  </si>
+  <si>
+    <t>義大利麵、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、奶油-香草奶油-頂級奶油</t>
+  </si>
+  <si>
+    <t>麵粉、高麗菜、青椒、醬油</t>
+  </si>
+  <si>
+    <t>歐姆蛋、米飯</t>
+  </si>
+  <si>
+    <t>麵粉、蘋果果醬-草莓果醬-葡萄果醬-藍莓果醬</t>
+  </si>
+  <si>
+    <t>橄欖油、麵包-白麵包-長棍麵包-佛卡夏、綠花椰菜-馬鈴薯-蘆筍-甜椒-胡蘿蔔-洋菇-南瓜</t>
+  </si>
+  <si>
+    <t>米飯、蛋-烏骨雞蛋、洋蔥、胡蘿蔔</t>
+  </si>
+  <si>
+    <t>麵粉、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、高麗菜</t>
+  </si>
+  <si>
+    <t>稻米、起司-香草起司-頂級起司、水牛奶</t>
+  </si>
+  <si>
+    <t>麵粉、香草奶油</t>
+  </si>
+  <si>
+    <t>麵粉、高麗菜、蛋-烏骨雞蛋</t>
+  </si>
+  <si>
+    <t>豆腐、白菜、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇</t>
+  </si>
+  <si>
+    <t>麵粉、番茄、起司-香草起司-頂級起司</t>
+  </si>
+  <si>
+    <t>青江菜、豆漿、奶油-香草奶油-頂級奶油</t>
+  </si>
+  <si>
+    <t>稻米、炸豆皮、胡蘿蔔</t>
+  </si>
+  <si>
+    <t>葡萄汁、麵包-白麵包-長棍麵包-佛卡夏、綠花椰菜-馬鈴薯-蘆筍-甜椒-胡蘿蔔-洋菇-南瓜</t>
+  </si>
+  <si>
+    <t>稻米、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇</t>
+  </si>
+  <si>
+    <t>生魚片、米飯、醋、蛋-烏骨雞蛋</t>
+  </si>
+  <si>
+    <t>蕎麥粉、麵粉</t>
+  </si>
+  <si>
+    <t>麵包-白麵包-長棍麵包-佛卡夏、薄荷-洋甘菊-薰衣草、美乃滋-香草美乃滋-頂級美乃滋</t>
+  </si>
+  <si>
+    <t>香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、奶油-香草奶油-頂級奶油</t>
+  </si>
+  <si>
+    <t>稻米、鹽、牛奶-水牛奶</t>
+  </si>
+  <si>
+    <t>飯糰、醬油</t>
+  </si>
+  <si>
+    <t>蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油</t>
+  </si>
+  <si>
+    <t>蛋-烏骨雞蛋、洋蔥、米飯</t>
+  </si>
+  <si>
+    <t>生魚片、米飯、醋</t>
+  </si>
+  <si>
+    <t>番茄、麵包-白麵包-長棍麵包-佛卡夏、綠花椰菜-馬鈴薯-蘆筍-甜椒-胡蘿蔔-洋菇-南瓜</t>
+  </si>
+  <si>
+    <t>麵粉、魚板、青蔥</t>
+  </si>
+  <si>
+    <t>稻米、鹽、薄荷-洋甘菊-薰衣草</t>
+  </si>
+  <si>
+    <t>麵包-白麵包-長棍麵包-佛卡夏、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
+  </si>
+  <si>
+    <t>麵粉、薄荷-洋甘菊-薰衣草、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>麵粉、油-堅果油-香草油-橄欖油-葡萄籽油、番茄</t>
+  </si>
+  <si>
+    <t>稻米、鹽</t>
+  </si>
+  <si>
+    <t>麵粉、葡萄</t>
+  </si>
+  <si>
+    <t>麵包-白麵包-長棍麵包-佛卡夏、番茄、小黃瓜</t>
+  </si>
+  <si>
+    <t>米飯、海苔</t>
+  </si>
+  <si>
+    <t>茄子、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>米飯、栗子</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋</t>
+  </si>
+  <si>
+    <t>蛋-烏骨雞蛋、米飯</t>
+  </si>
+  <si>
+    <t>麵粉、烏骨雞蛋、三腳胡蘿蔔、檸檬</t>
+  </si>
+  <si>
+    <t>長崎蛋糕、頂級烏骨雞蛋、頂級優格、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油、珠寶鳳梨</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、水牛奶、起司-香草起司-頂級起司</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、牛奶-水牛奶、南瓜</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油、櫻桃</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油、藍莓</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油、草莓</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、砂糖、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、油-堅果油-香草油-橄欖油-葡萄籽油、砂糖</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、牛奶-水牛奶、巧克力</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、牛奶-水牛奶、砂糖</t>
+  </si>
+  <si>
+    <t>麵粉、烏骨雞蛋、砂糖、核桃</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、牛奶-水牛奶、蜂蜜-清爽蜂蜜-滑順蜂蜜-皇家蜂蜜</t>
+  </si>
+  <si>
+    <t>糯米粉、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
+  </si>
+  <si>
+    <t>巧克力、麵包-白麵包-長棍麵包-佛卡夏、蘋果-葡萄-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
+  </si>
+  <si>
+    <t>蘋果、奶油-香草奶油-頂級奶油</t>
+  </si>
+  <si>
+    <t>牛奶-水牛奶、蛋-烏骨雞蛋、砂糖</t>
+  </si>
+  <si>
+    <t>麵粉、烏骨雞蛋、蜂蜜-清爽蜂蜜-滑順蜂蜜-皇家蜂蜜</t>
+  </si>
+  <si>
+    <t>年糕、草莓</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、牛奶-水牛奶</t>
+  </si>
+  <si>
+    <t>蛋-烏骨雞蛋、牛奶-水牛奶、麵粉</t>
+  </si>
+  <si>
+    <t>年糕、夏季茶葉</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、核桃</t>
+  </si>
+  <si>
+    <t>牛奶-水牛奶、蛋-烏骨雞蛋、豆漿</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、薄荷-洋甘菊-薰衣草</t>
+  </si>
+  <si>
+    <t>麵粉、頂級蛋-頂級烏骨雞蛋、頂級水牛奶、起司-香草起司-頂級起司</t>
+  </si>
+  <si>
+    <t>麵粉、頂級蛋-頂級烏骨雞蛋、頂級牛奶-頂級水牛奶、巧克力</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油、蘋果</t>
+  </si>
+  <si>
+    <t>麵粉、頂級蛋-頂級烏骨雞蛋、頂級牛奶-頂級水牛奶、草莓</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、牛奶-水牛奶、瓶裝栗子</t>
+  </si>
+  <si>
+    <t>牛奶-水牛奶、蛋-烏骨雞蛋、南瓜</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、巧克力</t>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、蜂蜜-清爽蜂蜜-滑順蜂蜜-皇家蜂蜜</t>
+  </si>
+  <si>
+    <t>香蕉、巧克力</t>
+  </si>
+  <si>
+    <t>牛奶-水牛奶、蛋-烏骨雞蛋</t>
+  </si>
+  <si>
+    <t>蜂蜜-清爽蜂蜜-滑順蜂蜜-皇家蜂蜜</t>
+  </si>
+  <si>
+    <t>海苔、醬油</t>
+  </si>
+  <si>
+    <t>香蕉汁、桃子汁、檸檬汁</t>
+  </si>
+  <si>
+    <t>紅茶、蘋果果醬-草莓果醬-葡萄果醬-藍莓果醬</t>
+  </si>
+  <si>
+    <t>紅茶罐、頂級牛奶</t>
+  </si>
+  <si>
+    <t>草莓汁、柳橙汁、櫻桃汁</t>
+  </si>
+  <si>
+    <t>草莓、砂糖、檸檬</t>
+  </si>
+  <si>
+    <t>葡萄汁、蘋果、柳橙</t>
+  </si>
+  <si>
+    <t>熱咖啡、牛奶-水牛奶</t>
+  </si>
+  <si>
+    <t>紅茶罐、牛奶-水牛奶</t>
+  </si>
+  <si>
+    <t>牛奶-水牛奶</t>
+  </si>
+  <si>
+    <t>春風果汁、夏風果汁、秋風果汁、皇家蜂蜜</t>
+  </si>
+  <si>
+    <t>藍莓汁、葡萄汁、蘋果汁</t>
+  </si>
+  <si>
+    <t>葡萄、砂糖、檸檬</t>
+  </si>
+  <si>
+    <t>蘋果、砂糖、檸檬</t>
+  </si>
+  <si>
+    <t>藍莓、砂糖、檸檬</t>
+  </si>
+  <si>
+    <t>愛心西瓜、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜、葡萄-蘋果-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
+  </si>
+  <si>
+    <t>香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、鹽</t>
+  </si>
+  <si>
+    <t>醃漬甜椒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>櫻桃蘿蔔、洋蔥、橄欖油、蜂蜜、清爽蜂蜜、滑順蜂蜜、皇家蜂蜜</t>
+  </si>
+  <si>
+    <t>玉蜀黍、牛奶-水牛奶、奶油-香草奶油-頂級奶油、洋蔥</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Festival</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>暖暖節</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>湯類</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>起司蛋烤餅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃鱸魚-烏鱧-馬蘇鉤吻鮭-鱒魚-鮭魚-銀魚-櫻鱒、馬鈴薯、麵粉-米穀粉、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白菜、醬油、砂糖、鹽、胡椒、味噌、醋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>法式鹹薄餅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>味噌湯</t>
+  </si>
+  <si>
+    <t>味噌、豆腐-青蔥-炸豆皮-馬鈴薯-鴻喜菇</t>
+  </si>
+  <si>
+    <t>大蒜、鹽、胡椒、油、堅果油、香草油、橄欖油、味噌</t>
+  </si>
+  <si>
+    <t>茄子、味噌</t>
+  </si>
+  <si>
+    <t>香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、玉蜀黍、奶油-香草奶油-頂級奶油、起司-香草起司-頂級起司</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉蜀黍、牛奶-水牛奶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>麵粉、蛋-烏骨雞蛋、番薯</t>
+  </si>
+  <si>
+    <t>烤番薯</t>
+  </si>
+  <si>
+    <t>番薯</t>
+  </si>
+  <si>
+    <t>麵粉、油-堅果油-香草油-橄欖油-葡萄籽油、蛋-烏骨雞蛋、香菇-南瓜-茄子-番薯-銀魚-西太公魚</t>
+  </si>
+  <si>
+    <t>番薯、瓶裝栗子、鹽</t>
+  </si>
+  <si>
+    <t>番薯、奶油、香草奶油、頂級奶油、米穀粉、砂糖</t>
+  </si>
+  <si>
+    <t>牛奶-水牛奶、砂糖、番薯</t>
+  </si>
+  <si>
+    <t>番薯、砂糖、鹽</t>
+  </si>
+  <si>
+    <t>蛋-烏骨雞蛋、玉蜀黍、洋蔥、小黃瓜-洋蔥-蘆筍-番茄-甜椒-胡蘿蔔-蕪菁-番薯-南瓜-茄子</t>
+  </si>
+  <si>
+    <t>蒜炒綠花椰菜</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>麵粉、洋蔥、藍鰓太陽魚-暗色頜鬚鮈-稻田魚-麥穗魚-西太公魚-香魚-鰻魚-鱸鰻-鯽魚-蘭氏鯽</t>
+  </si>
+  <si>
+    <t>藍鰓太陽魚-暗色頜鬚鮈-稻田魚-麥穗魚-西太公魚-香魚-鰻魚-鱸鰻-鯽魚-蘭氏鯽、醬油</t>
+  </si>
+  <si>
+    <t>麵粉、咖哩粉、洋蔥、胡蘿蔔</t>
+  </si>
+  <si>
+    <t>終極咖哩</t>
+  </si>
+  <si>
+    <t>咖哩飯、星形馬鈴薯、三腳胡蘿蔔</t>
+  </si>
+  <si>
+    <t>辣味咖哩</t>
+  </si>
+  <si>
+    <t>米飯、咖哩粉、香辛料、馬鈴薯-胡蘿蔔-洋蔥</t>
+  </si>
+  <si>
+    <t>海苔咖哩</t>
+  </si>
+  <si>
+    <t>牛奶咖哩</t>
+  </si>
+  <si>
+    <t>米飯、咖哩粉、牛奶-水牛奶、馬鈴薯-胡蘿蔔-洋蔥</t>
+  </si>
+  <si>
+    <t>彩虹咖哩</t>
+  </si>
+  <si>
+    <t>米飯、咖哩粉、菠菜、甜椒</t>
+  </si>
+  <si>
+    <t>麵粉、咖哩粉、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>米飯、咖哩粉、馬鈴薯-胡蘿蔔-洋蔥</t>
+  </si>
+  <si>
+    <t>米飯、咖哩粉、小黃瓜-洋蔥-蘆筍-番茄-甜椒-胡蘿蔔-蕪菁-番薯-南瓜-茄子</t>
+  </si>
+  <si>
+    <t>米飯、咖哩粉、番茄、豆子</t>
+  </si>
+  <si>
+    <t>奶油、香草奶油、頂級奶油、蜂蜜、清爽蜂蜜、滑順蜂蜜、皇家蜂蜜、砂糖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>奶油、香草奶油、頂級奶油、醬油、鹽、咖哩粉、蜂蜜、清爽蜂蜜、滑順蜂蜜、皇家蜂蜜</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>南瓜節</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>頂級咖哩-巨大番茄、指甲辣椒、頂級優格</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>堅果油、橄欖油、南瓜籽油、葡萄籽油</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>頂級咖哩</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白蘿蔔、白菜、青蔥、尼羅尖吻鱸-鮭魚-馬蘇鉤吻鮭-櫻鱒-褐鱒-黃鱸魚-香魚</t>
+  </si>
+  <si>
+    <t>尼羅尖吻鱸-鮭魚-馬蘇鉤吻鮭-櫻鱒-褐鱒-黃鱸魚-香魚、胡蘿蔔、馬鈴薯、洋蔥</t>
+  </si>
+  <si>
+    <t>尼羅尖吻鱸-鮭魚-馬蘇鉤吻鮭-櫻鱒-褐鱒-黃鱸魚-香魚、洋蔥、醋、檸檬</t>
+  </si>
+  <si>
+    <t>黃鱸魚-烏鱧-馬蘇鉤吻鮭-鱒魚-鮭魚-銀魚-櫻鱒、洋蔥、醋</t>
+  </si>
+  <si>
+    <t>松茸飯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>米飯、炸豆皮、醋、砂糖</t>
+  </si>
+  <si>
+    <t>米飯、咖哩粉、海苔、馬鈴薯-胡蘿蔔-洋蔥</t>
+  </si>
+  <si>
+    <t>蛋包飯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>義大利麵、辣椒、大蒜、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒜味辣椒義大利麵</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>米飯、鰻魚-鱸鰻、醬油、砂糖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鰻魚蓋飯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>義大利麵、番茄、茴魚-黑鰱-尼羅尖吻鱸-竹篙頭-真馬口魚-褐鱒-黑驢魚-赫茨扁吻鮈、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>米飯、茴魚-黑鰱-尼羅尖吻鱸-竹篙頭-真馬口魚-褐鱒-黑驢魚-赫茨扁吻鮈、甜椒、香辛料</t>
+  </si>
+  <si>
+    <t>茴魚-黑鰱-尼羅尖吻鱸-竹篙頭-真馬口魚-褐鱒-黑驢魚-赫茨扁吻鮈、麵粉、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>番茄、茴魚-黑鰱-尼羅尖吻鱸-竹篙頭-真馬口魚-褐鱒-黑驢魚-赫茨扁吻鮈、油-堅果油-香草油-橄欖油-葡萄籽油</t>
+  </si>
+  <si>
+    <t>奶油、香草奶油、頂級奶油、砂糖、巧克力</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>南瓜節、甜心節</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>砂糖、鹽、核桃、牛奶、水牛奶、蜂蜜、清爽蜂蜜、滑順蜂蜜、皇家蜂蜜</t>
-  </si>
-  <si>
-    <t>砂糖、鹽、核桃、牛奶、水牛奶、蜂蜜、清爽蜂蜜、滑順蜂蜜</t>
-  </si>
-  <si>
-    <t>番茄、薄荷-洋甘菊-薰衣草</t>
-  </si>
-  <si>
-    <t>番茄、起司-香草起司-頂級起司、橄欖油、鹽</t>
-  </si>
-  <si>
-    <t>酪梨、鮭魚、醬油</t>
-  </si>
-  <si>
-    <t>馬鈴薯、奶油-香草奶油-頂級奶油</t>
-  </si>
-  <si>
-    <t>蘆筍、牛奶-水牛奶、油-堅果油-香草油-橄欖油-葡萄籽油、洋蔥</t>
-  </si>
-  <si>
-    <t>洋蔥、奶油-香草奶油-頂級奶油</t>
-  </si>
-  <si>
-    <t>櫻桃蘿蔔、牛奶-水牛奶、鹽</t>
-  </si>
-  <si>
-    <t>味增、豆腐-青蔥-炸豆皮-馬鈴薯-鴻喜菇</t>
-  </si>
-  <si>
-    <t>玉米、牛奶-水牛奶、奶油-香草奶油-頂級奶油、洋蔥</t>
-  </si>
-  <si>
-    <t>南瓜、牛奶-水牛奶、洋蔥</t>
-  </si>
-  <si>
-    <t>馬鈴薯、洋蔥、牛奶-水牛奶</t>
-  </si>
-  <si>
-    <t>番茄、大蒜、麵包-白麵包-長棍麵包-佛卡夏</t>
-  </si>
-  <si>
-    <t>蛋-烏骨雞蛋</t>
-  </si>
-  <si>
-    <t>麵粉、頂級起司、頂級優格、頂級奶油</t>
-  </si>
-  <si>
-    <t>羊肚菌、水牛奶、奶油-香草奶油-頂級奶油、海膽</t>
-  </si>
-  <si>
-    <t>麵粉、菠菜、南瓜、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇</t>
-  </si>
-  <si>
-    <t>黃鱸魚-烏鱧-馬蘇勾吻鮭-鱒魚-鮭魚-銀魚-櫻鱒、馬鈴薯、麵粉-米穀粉、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>麵粉、香菇、胡蘿蔔、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>麵粉、白菜、香菇、青蔥</t>
-  </si>
-  <si>
-    <t>麵粉、高麗菜、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>高麗菜、白菜</t>
-  </si>
-  <si>
-    <t>高麗菜、胡蘿蔔</t>
-  </si>
-  <si>
-    <t>麵粉、奶油-香草奶油-頂級奶油、牛奶-水牛奶</t>
-  </si>
-  <si>
-    <t>蕎麥粉、馬鈴薯、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油</t>
-  </si>
-  <si>
-    <t>番茄、豆子、辣椒、胡椒</t>
-  </si>
-  <si>
-    <t>蕪菁、奶油-香草奶油-頂級奶油</t>
-  </si>
-  <si>
-    <t>麵粉、橄欖油</t>
-  </si>
-  <si>
-    <t>豆腐、醬油、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>豆腐、麵粉-米穀粉、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>蛋-烏骨雞蛋、醬油、砂糖</t>
-  </si>
-  <si>
-    <t>蛋-烏骨雞蛋、香菇、魚板</t>
-  </si>
-  <si>
-    <t>豆腐、胡蘿蔔</t>
-  </si>
-  <si>
-    <t>麵粉、鹽</t>
-  </si>
-  <si>
-    <t>馬鈴薯、麵粉、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、蕃薯</t>
-  </si>
-  <si>
-    <t>綠花椰菜、大蒜、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>豆腐、醬油</t>
-  </si>
-  <si>
-    <t>馬鈴薯、麵粉、蛋-烏骨雞蛋</t>
-  </si>
-  <si>
-    <t>玉米、牛奶-水牛奶</t>
-  </si>
-  <si>
-    <t>蛋-烏骨雞蛋、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>茄子、味增</t>
-  </si>
-  <si>
-    <t>麵包-白麵包</t>
-  </si>
-  <si>
-    <t>豆子、豆漿</t>
-  </si>
-  <si>
-    <t>香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇</t>
-  </si>
-  <si>
-    <t>麵粉、洋蔥、藍鰓太陽魚-暗色頜鬚鮈-稻田魚-麥穗魚-西太公魚-香魚-鰻魚-鱸鰻-鯽魚-藍氏鯽</t>
-  </si>
-  <si>
-    <t>柳根魚-珠星三塊魚-日本溪哥-鈍頭杜父魚-特氏東瀛鯉-黑腹鱊-長頜鬚鮈-虹鱒-鰱魚-博氏巨鯰</t>
-  </si>
-  <si>
-    <t>白菜、胡蘿蔔、青椒、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇</t>
-  </si>
-  <si>
-    <t>玉蜀黍、醬油、砂糖</t>
-  </si>
-  <si>
-    <t>麵粉、咖喱粉、洋蔥、胡蘿蔔</t>
-  </si>
-  <si>
-    <t>馬鈴薯、麵包粉-白麵包粉、油-堅果油-香草油-橄欖油-葡萄籽油、起司-香草起司-頂級起司</t>
-  </si>
-  <si>
-    <t>麵粉、起司-香草起司-頂級起司、水牛奶</t>
-  </si>
-  <si>
-    <t>馬鈴薯、麵包粉-白麵包粉、油-堅果油-香草油-橄欖油-葡萄籽油、牛奶-水牛奶</t>
-  </si>
-  <si>
-    <t>麵粉、牛奶-水牛奶、馬鈴薯-蘆筍-胡蘿蔔-高麗菜-蕪菁-花椰菜</t>
-  </si>
-  <si>
-    <t>馬鈴薯、麵包粉-白麵包粉、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>麵包-白麵包、蛋-烏骨雞蛋、牛奶-水牛奶</t>
-  </si>
-  <si>
-    <t>玉蜀黍、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>馬鈴薯、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>蛋-烏骨雞蛋、醬油</t>
-  </si>
-  <si>
-    <t>頂級咖喱、頂級咖喱、指甲辣椒、頂級優格</t>
-  </si>
-  <si>
-    <t>米穀粉、國王菇、高麗菜、胡蘿蔔</t>
-  </si>
-  <si>
-    <t>馬鈴薯、洋蔥、頂級起司、頂級美乃滋</t>
-  </si>
-  <si>
-    <t>咖喱飯、星形馬鈴薯、三腳胡蘿蔔</t>
-  </si>
-  <si>
-    <t>蕎麥粉、起司-香草起司-頂級起司、高麗菜、馬鈴薯</t>
-  </si>
-  <si>
-    <t>蕎麥粉、天婦羅</t>
-  </si>
-  <si>
-    <t>頂級牛奶、胡蘿蔔、白菜、菠菜</t>
-  </si>
-  <si>
-    <t>麵粉、起司-香草起司-頂級起司、奶油-香草奶油-頂級奶油、美乃滋-香草美乃滋-頂級美乃滋</t>
-  </si>
-  <si>
-    <t>白蘿蔔、白菜、青蔥、尼羅尖吻鱸-鮭魚-馬斯鉤吻鮭-櫻鱒-褐鱒-黃鱸魚-香魚</t>
-  </si>
-  <si>
-    <t>尼羅尖吻鱸-鮭魚-馬斯鉤吻鮭-櫻鱒-褐鱒-黃鱸魚-香魚、胡蘿蔔、馬鈴薯、洋蔥</t>
-  </si>
-  <si>
-    <t>香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、玉蜀黍、奶油-香草奶油-頂級奶油、起司-香草起司-頂級起司</t>
-  </si>
-  <si>
-    <t>麵粉、天婦羅</t>
-  </si>
-  <si>
-    <t>尼羅尖吻鱸-鮭魚-馬斯鉤吻鮭-櫻鱒-褐鱒-黃鱸魚-香魚、洋蔥、醋、檸檬</t>
-  </si>
-  <si>
-    <t>天婦羅、米飯</t>
-  </si>
-  <si>
-    <t>起司-香草起司-頂級起司、玉蜀黍、胡蘿蔔、綠花椰菜</t>
-  </si>
-  <si>
-    <t>義大利麵、綜合沙拉、美乃滋-香草美乃滋-頂級美乃滋</t>
-  </si>
-  <si>
-    <t>稻米、松茸、醬油</t>
-  </si>
-  <si>
-    <t>麵粉、起司-香草起司-頂級起司、美乃滋-香草美乃滋-頂級美乃滋</t>
-  </si>
-  <si>
-    <t>義大利麵、番茄、茴魚-黑鰱-尼羅尖吻鱸-竹嵩頭-真馬口魚-褐鱒-黑鱸魚-赫茨扁吻鮈、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>稻米、起司-香草起司-頂級起司、番茄、洋蔥</t>
-  </si>
-  <si>
-    <t>黃鱸魚-烏鱧-馬斯鉤吻鮭-鱒魚-鮭魚-銀魚-櫻鱒、洋蔥、醋</t>
-  </si>
-  <si>
-    <t>起司-香草起司-頂級起司、麵包-白麵包-長棍麵包-佛卡夏、綠花椰菜-馬鈴薯-蘆筍-甜椒-胡蘿蔔-洋菇-南瓜</t>
-  </si>
-  <si>
-    <t>義大利麵、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、奶油-香草奶油-頂級奶油</t>
-  </si>
-  <si>
-    <t>麵粉、高麗菜、青椒、醬油</t>
-  </si>
-  <si>
-    <t>白飯、炸豆皮、醋、砂糖</t>
-  </si>
-  <si>
-    <t>米飯、咖喱粉、香辛料、馬鈴薯-胡蘿蔔-洋蔥</t>
-  </si>
-  <si>
-    <t>歐姆蛋、米飯</t>
-  </si>
-  <si>
-    <t>義大利麵、辣椒、大蒜、油</t>
-  </si>
-  <si>
-    <t>白飯、咖喱粉、海苔、馬鈴薯-胡蘿蔔-洋蔥</t>
-  </si>
-  <si>
-    <t>麵粉、蘋果果醬-草莓果醬-葡萄果醬-藍莓果醬</t>
-  </si>
-  <si>
-    <t>米飯、咖喱粉、牛奶-水牛奶、馬鈴薯-胡蘿蔔-洋蔥</t>
-  </si>
-  <si>
-    <t>橄欖油、麵包-白麵包-長棍麵包-佛卡夏、綠花椰菜-馬鈴薯-蘆筍-甜椒-胡蘿蔔-洋菇-南瓜</t>
-  </si>
-  <si>
-    <t>米飯、蛋-烏骨雞蛋、洋蔥、胡蘿蔔</t>
-  </si>
-  <si>
-    <t>米飯、咖喱粉、菠菜、甜椒</t>
-  </si>
-  <si>
-    <t>麵粉、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、高麗菜</t>
-  </si>
-  <si>
-    <t>米飯、鰻魚、醬油、砂糖</t>
-  </si>
-  <si>
-    <t>稻米、起司-香草起司-頂級起司、水牛奶</t>
-  </si>
-  <si>
-    <t>麵粉、香草奶油</t>
-  </si>
-  <si>
-    <t>麵粉、高麗菜、蛋-烏骨雞蛋</t>
-  </si>
-  <si>
-    <t>麵粉、油-堅果油-香草油-橄欖油-葡萄籽油、蛋-烏骨雞蛋、香菇-南瓜-茄子-蕃薯-銀魚-西太公魚</t>
-  </si>
-  <si>
-    <t>米飯、茴魚-黑鰱-尼羅尖吻鱸-竹嵩頭-真馬口魚-褐鱒-黑鱸魚-赫茨扁吻鮈、甜椒、香辛料</t>
-  </si>
-  <si>
-    <t>豆腐、白菜、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇</t>
-  </si>
-  <si>
-    <t>麵粉、番茄、起司-香草起司-頂級起司</t>
-  </si>
-  <si>
-    <t>青江菜、豆漿、奶油-香草奶油-頂級奶油</t>
-  </si>
-  <si>
-    <t>麵粉、咖喱粉、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>茴魚-黑鰱-尼羅尖吻鱸-竹嵩頭-真馬口魚-褐鱒-黑鱸魚-赫茨扁吻鮈、麵粉、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>稻米、炸豆皮、胡蘿蔔</t>
-  </si>
-  <si>
-    <t>葡萄汁、麵包-白麵包-長棍麵包-佛卡夏、綠花椰菜-馬鈴薯-蘆筍-甜椒-胡蘿蔔-洋菇-南瓜</t>
-  </si>
-  <si>
-    <t>米飯、咖喱粉、馬鈴薯-胡蘿蔔-洋蔥</t>
-  </si>
-  <si>
-    <t>米飯、咖喱粉、小黃瓜-洋蔥-蘆筍-番茄-甜椒-胡蘿蔔-蕪菁-蕃薯-南瓜-茄子</t>
-  </si>
-  <si>
-    <t>稻米、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇</t>
-  </si>
-  <si>
-    <t>生魚片、米飯、醋、蛋-烏骨雞蛋</t>
-  </si>
-  <si>
-    <t>蕎麥粉、麵粉</t>
-  </si>
-  <si>
-    <t>米飯、咖喱粉、番茄、豆子</t>
-  </si>
-  <si>
-    <t>番茄、茴魚-黑鰱-尼羅尖吻鱸-竹嵩頭-真馬口魚-褐鱒-黑鱸魚-赫茨扁吻鮈、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>麵包-白麵包-長棍麵包-佛卡夏、薄荷-洋甘菊-薰衣草、美乃滋-香草美乃滋-頂級美乃滋</t>
-  </si>
-  <si>
-    <t>香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、奶油-香草奶油-頂級奶油</t>
-  </si>
-  <si>
-    <t>稻米、鹽、牛奶-水牛奶</t>
-  </si>
-  <si>
-    <t>飯糰、醬油</t>
-  </si>
-  <si>
-    <t>蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油</t>
-  </si>
-  <si>
-    <t>蛋-烏骨雞蛋、洋蔥、米飯</t>
-  </si>
-  <si>
-    <t>生魚片、米飯、醋</t>
-  </si>
-  <si>
-    <t>番茄、麵包-白麵包-長棍麵包-佛卡夏、綠花椰菜-馬鈴薯-蘆筍-甜椒-胡蘿蔔-洋菇-南瓜</t>
-  </si>
-  <si>
-    <t>麵粉、魚板、青蔥</t>
-  </si>
-  <si>
-    <t>稻米、鹽、薄荷-洋甘菊-薰衣草</t>
-  </si>
-  <si>
-    <t>麵包-白麵包-長棍麵包-佛卡夏、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
-  </si>
-  <si>
-    <t>麵粉、薄荷-洋甘菊-薰衣草、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>麵粉、油-堅果油-香草油-橄欖油-葡萄籽油、番茄</t>
-  </si>
-  <si>
-    <t>稻米、鹽</t>
-  </si>
-  <si>
-    <t>藍鰓太陽魚-暗色頜鬚鮈-稻田魚-麥穗魚-西太公魚-香魚-鰻魚-鱸鰻-鯽魚-藍氏鯽、醬油</t>
-  </si>
-  <si>
-    <t>麵粉、葡萄</t>
-  </si>
-  <si>
-    <t>麵包-白麵包-長棍麵包-佛卡夏、番茄、小黃瓜</t>
-  </si>
-  <si>
-    <t>米飯、海苔</t>
-  </si>
-  <si>
-    <t>茄子、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>米飯、栗子</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋</t>
-  </si>
-  <si>
-    <t>蛋-烏骨雞蛋、米飯</t>
-  </si>
-  <si>
-    <t>麵粉、烏骨雞蛋、三腳胡蘿蔔、檸檬</t>
-  </si>
-  <si>
-    <t>長崎蛋糕、頂級烏骨雞蛋、頂級優格、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油、珠寶鳳梨</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、水牛奶、起司-香草起司-頂級起司</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、牛奶-水牛奶、南瓜</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油、櫻桃</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油、藍莓</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油、草莓</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、砂糖、油-堅果油-香草油-橄欖油-葡萄籽油</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、油-堅果油-香草油-橄欖油-葡萄籽油、砂糖</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、牛奶-水牛奶、巧克力</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、牛奶-水牛奶、砂糖</t>
-  </si>
-  <si>
-    <t>麵粉、烏骨雞蛋、砂糖、核桃</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、牛奶-水牛奶、蜂蜜-清爽蜂蜜-滑順蜂蜜-皇家蜂蜜</t>
-  </si>
-  <si>
-    <t>糯米粉、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
-  </si>
-  <si>
-    <t>牛奶-水牛奶、砂糖、蕃薯</t>
-  </si>
-  <si>
-    <t>巧克力、麵包-白麵包-長棍麵包-佛卡夏、蘋果-葡萄-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
-  </si>
-  <si>
-    <t>蘋果、奶油-香草奶油-頂級奶油</t>
-  </si>
-  <si>
-    <t>牛奶-水牛奶、蛋-烏骨雞蛋、砂糖</t>
-  </si>
-  <si>
-    <t>麵粉、烏骨雞蛋、蜂蜜-清爽蜂蜜-滑順蜂蜜-皇家蜂蜜</t>
-  </si>
-  <si>
-    <t>年糕、草莓</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、牛奶-水牛奶</t>
-  </si>
-  <si>
-    <t>蛋-烏骨雞蛋、牛奶-水牛奶、麵粉</t>
-  </si>
-  <si>
-    <t>年糕、夏季茶葉</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、核桃</t>
-  </si>
-  <si>
-    <t>牛奶-水牛奶、蛋-烏骨雞蛋、豆漿</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、薄荷-洋甘菊-薰衣草</t>
-  </si>
-  <si>
-    <t>麵粉、頂級蛋-頂級烏骨雞蛋、頂級水牛奶、起司-香草起司-頂級起司</t>
-  </si>
-  <si>
-    <t>麵粉、頂級蛋-頂級烏骨雞蛋、頂級牛奶-頂級水牛奶、巧克力</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、奶油-香草奶油-頂級奶油、蘋果</t>
-  </si>
-  <si>
-    <t>麵粉、頂級蛋-頂級烏骨雞蛋、頂級牛奶-頂級水牛奶、草莓</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、牛奶-水牛奶、瓶裝栗子</t>
-  </si>
-  <si>
-    <t>牛奶-水牛奶、蛋-烏骨雞蛋、南瓜</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、巧克力</t>
-  </si>
-  <si>
-    <t>麵粉、蛋-烏骨雞蛋、蜂蜜-清爽蜂蜜-滑順蜂蜜-皇家蜂蜜</t>
-  </si>
-  <si>
-    <t>香蕉、巧克力</t>
-  </si>
-  <si>
-    <t>牛奶-水牛奶、蛋-烏骨雞蛋</t>
-  </si>
-  <si>
-    <t>蜂蜜-清爽蜂蜜-滑順蜂蜜-皇家蜂蜜</t>
-  </si>
-  <si>
-    <t>海苔、醬油</t>
-  </si>
-  <si>
-    <t>香蕉汁、桃子汁、檸檬汁</t>
-  </si>
-  <si>
-    <t>紅茶、蘋果果醬-草莓果醬-葡萄果醬-藍莓果醬</t>
-  </si>
-  <si>
-    <t>紅茶罐、頂級牛奶</t>
-  </si>
-  <si>
-    <t>草莓汁、柳橙汁、櫻桃汁</t>
-  </si>
-  <si>
-    <t>草莓、砂糖、檸檬</t>
-  </si>
-  <si>
-    <t>葡萄汁、蘋果、柳橙</t>
-  </si>
-  <si>
-    <t>熱咖啡、牛奶-水牛奶</t>
-  </si>
-  <si>
-    <t>紅茶罐、牛奶-水牛奶</t>
-  </si>
-  <si>
-    <t>牛奶-水牛奶</t>
-  </si>
-  <si>
-    <t>春風果汁、夏風果汁、秋風果汁、皇家蜂蜜</t>
-  </si>
-  <si>
-    <t>藍莓汁、葡萄汁、蘋果汁</t>
-  </si>
-  <si>
-    <t>葡萄、砂糖、檸檬</t>
-  </si>
-  <si>
-    <t>蘋果、砂糖、檸檬</t>
-  </si>
-  <si>
-    <t>藍莓、砂糖、檸檬</t>
-  </si>
-  <si>
-    <t>愛心西瓜、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜、葡萄-蘋果-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
-  </si>
-  <si>
-    <t>蛋-烏骨雞蛋、玉蜀黍、洋蔥、小黃瓜-洋蔥-蘆筍-番茄-甜椒-胡蘿蔔-蕪菁-蕃薯-南瓜-茄子</t>
-  </si>
-  <si>
-    <t>香菇-鴻喜菇-洋菇-牛肝菌-羊肚菌-松茸-國王菇、鹽</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2369,7 +2409,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="181" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -2964,7 +3004,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3012,24 +3052,7 @@
     <cellStyle name="壞" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="警告文字" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF5F5DC"/>
-          <bgColor rgb="FFF5F5DC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD3D3D3"/>
-          <bgColor rgb="FFD3D3D3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3339,7 +3362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE04E7DD-F155-4289-B904-E214A34C0638}">
-  <dimension ref="A1:F267"/>
+  <dimension ref="A1:G267"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.375" bestFit="1" customWidth="1"/>
@@ -3347,9 +3370,10 @@
     <col min="4" max="4" width="100.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3357,7 +3381,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="D1" t="s">
         <v>6</v>
@@ -3368,8 +3392,11 @@
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -3389,12 +3416,12 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -3409,107 +3436,107 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="C4" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="D4" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="E4" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="F4" s="2">
         <v>909</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>335</v>
+        <v>710</v>
       </c>
       <c r="C5" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="D5" t="s">
-        <v>341</v>
+        <v>711</v>
       </c>
       <c r="E5" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="F5" s="2">
         <v>598</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="C6" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="D6" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="E6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="F6" s="2">
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="C7" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="D7" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="E7" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="F7" s="2">
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="D8" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="E8" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="F8" s="2">
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -3517,19 +3544,19 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>580</v>
+        <v>552</v>
       </c>
       <c r="D9" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="E9" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="F9" s="2">
         <v>126</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -3537,19 +3564,19 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>581</v>
+        <v>553</v>
       </c>
       <c r="D10" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="E10" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="F10" s="2">
         <v>2429</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -3557,19 +3584,19 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>582</v>
+        <v>554</v>
       </c>
       <c r="D11" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="E11" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="F11" s="2">
         <v>1197</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -3577,19 +3604,19 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>583</v>
+        <v>555</v>
       </c>
       <c r="D12" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="E12" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="F12" s="2">
         <v>677</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -3600,16 +3627,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="E13" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="F13" s="2">
         <v>325</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -3617,19 +3644,22 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>584</v>
+        <v>556</v>
       </c>
       <c r="D14" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="E14" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="F14" s="2">
         <v>1728</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -3637,19 +3667,22 @@
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>585</v>
+        <v>557</v>
       </c>
       <c r="D15" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="E15" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="F15" s="2">
         <v>1024</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -3657,653 +3690,677 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>586</v>
+        <v>558</v>
       </c>
       <c r="D16" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="E16" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="F16" s="2">
         <v>770</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="C17" t="s">
-        <v>587</v>
+        <v>721</v>
       </c>
       <c r="D17" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="E17" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="F17" s="2">
         <v>260</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>588</v>
+        <v>712</v>
       </c>
       <c r="D18" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="E18" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="F18" s="2">
         <v>1815</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>589</v>
+        <v>559</v>
       </c>
       <c r="D19" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="E19" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="F19" s="2">
         <v>1320</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>715</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="D20" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="E20" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="F20" s="2">
         <v>709</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="D21" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="E21" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="F21" s="2">
         <v>490</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="D22" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="E22" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="F22" s="2">
         <v>137</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>592</v>
+        <v>562</v>
       </c>
       <c r="D23" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="E23" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="F23" s="2">
         <v>117</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>716</v>
       </c>
       <c r="C24" t="s">
-        <v>593</v>
+        <v>563</v>
       </c>
       <c r="D24" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="E24" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="F24" s="2">
         <v>10098</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>594</v>
+        <v>564</v>
       </c>
       <c r="D25" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="E25" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="F25" s="2">
         <v>2592</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>595</v>
+        <v>565</v>
       </c>
       <c r="D26" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="E26" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="F26" s="2">
         <v>1892</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>596</v>
+        <v>717</v>
       </c>
       <c r="D27" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="E27" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="F27" s="2">
         <v>1584</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>597</v>
+        <v>566</v>
       </c>
       <c r="D28" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="E28" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="F28" s="2">
         <v>1530</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="D29" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="E29" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="F29" s="2">
         <v>1377</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>599</v>
+        <v>568</v>
       </c>
       <c r="D30" t="s">
-        <v>414</v>
+        <v>718</v>
       </c>
       <c r="E30" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="F30" s="2">
         <v>1353</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>600</v>
+        <v>569</v>
       </c>
       <c r="D31" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="E31" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="F31" s="2">
         <v>1276</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>601</v>
+        <v>570</v>
       </c>
       <c r="D32" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="E32" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="F32" s="2">
         <v>1213</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>602</v>
+        <v>571</v>
       </c>
       <c r="D33" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="E33" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="F33" s="2">
         <v>1155</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>719</v>
       </c>
       <c r="C34" t="s">
-        <v>603</v>
+        <v>572</v>
       </c>
       <c r="D34" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="E34" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="F34" s="2">
         <v>1122</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>604</v>
+        <v>573</v>
       </c>
       <c r="D35" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="E35" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="F35" s="2">
         <v>1056</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>605</v>
+        <v>574</v>
       </c>
       <c r="D36" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="E36" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F36" s="2">
         <v>911</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>606</v>
+        <v>575</v>
       </c>
       <c r="D37" t="s">
-        <v>421</v>
+        <v>722</v>
       </c>
       <c r="E37" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F37" s="2">
         <v>882</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>607</v>
+        <v>576</v>
       </c>
       <c r="D38" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="E38" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F38" s="2">
         <v>843</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>608</v>
+        <v>577</v>
       </c>
       <c r="D39" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="E39" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F39" s="2">
         <v>824</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>609</v>
+        <v>578</v>
       </c>
       <c r="D40" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="E40" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F40" s="2">
         <v>809</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>610</v>
+        <v>579</v>
       </c>
       <c r="D41" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="E41" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F41" s="2">
         <v>801</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>611</v>
+        <v>580</v>
       </c>
       <c r="D42" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="E42" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F42" s="2">
         <v>747</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>15</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>612</v>
+        <v>581</v>
       </c>
       <c r="D43" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="E43" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F43" s="2">
         <v>743</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>583</v>
+        <v>555</v>
       </c>
       <c r="D44" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="E44" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F44" s="2">
         <v>677</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>15</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
-        <v>613</v>
+        <v>582</v>
       </c>
       <c r="D45" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="E45" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F45" s="2">
         <v>662</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>15</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
-        <v>614</v>
+        <v>583</v>
       </c>
       <c r="D46" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="E46" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F46" s="2">
         <v>632</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>15</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C47" t="s">
-        <v>615</v>
+        <v>726</v>
       </c>
       <c r="D47" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="E47" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F47" s="2">
         <v>609</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>15</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C48" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D48" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="E48" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F48" s="2">
         <v>602</v>
@@ -4314,16 +4371,16 @@
         <v>15</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>735</v>
       </c>
       <c r="C49" t="s">
-        <v>616</v>
+        <v>584</v>
       </c>
       <c r="D49" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="E49" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F49" s="2">
         <v>563</v>
@@ -4334,16 +4391,16 @@
         <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C50" t="s">
-        <v>617</v>
+        <v>585</v>
       </c>
       <c r="D50" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="E50" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F50" s="2">
         <v>458</v>
@@ -4354,16 +4411,16 @@
         <v>15</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C51" t="s">
-        <v>618</v>
+        <v>586</v>
       </c>
       <c r="D51" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="E51" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F51" s="2">
         <v>429</v>
@@ -4374,16 +4431,16 @@
         <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C52" t="s">
-        <v>619</v>
+        <v>725</v>
       </c>
       <c r="D52" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="E52" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F52" s="2">
         <v>403</v>
@@ -4394,16 +4451,16 @@
         <v>15</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>620</v>
+        <v>587</v>
       </c>
       <c r="D53" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="E53" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F53" s="2">
         <v>396</v>
@@ -4414,16 +4471,16 @@
         <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C54" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D54" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="E54" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F54" s="2">
         <v>267</v>
@@ -4434,16 +4491,16 @@
         <v>15</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C55" t="s">
-        <v>621</v>
+        <v>723</v>
       </c>
       <c r="D55" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="E55" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F55" s="2">
         <v>246</v>
@@ -4454,16 +4511,16 @@
         <v>15</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>622</v>
+        <v>588</v>
       </c>
       <c r="D56" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="E56" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F56" s="2">
         <v>234</v>
@@ -4474,16 +4531,16 @@
         <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C57" t="s">
-        <v>623</v>
+        <v>589</v>
       </c>
       <c r="D57" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="E57" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F57" s="2">
         <v>205</v>
@@ -4494,16 +4551,16 @@
         <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C58" t="s">
-        <v>624</v>
+        <v>590</v>
       </c>
       <c r="D58" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="E58" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F58" s="2">
         <v>195</v>
@@ -4514,16 +4571,16 @@
         <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C59" t="s">
-        <v>592</v>
+        <v>562</v>
       </c>
       <c r="D59" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="E59" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F59" s="2">
         <v>117</v>
@@ -4534,16 +4591,16 @@
         <v>15</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C60" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D60" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="E60" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F60" s="2">
         <v>111</v>
@@ -4554,16 +4611,16 @@
         <v>15</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C61" t="s">
-        <v>625</v>
+        <v>736</v>
       </c>
       <c r="D61" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="E61" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="F61" s="2">
         <v>924</v>
@@ -4574,16 +4631,16 @@
         <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C62" t="s">
-        <v>626</v>
+        <v>591</v>
       </c>
       <c r="D62" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E62" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="F62" s="2">
         <v>195</v>
@@ -4594,16 +4651,16 @@
         <v>15</v>
       </c>
       <c r="B63" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>626</v>
+        <v>591</v>
       </c>
       <c r="D63" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="E63" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="F63" s="2">
         <v>195</v>
@@ -4614,1622 +4671,1667 @@
         <v>15</v>
       </c>
       <c r="B64" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>627</v>
+        <v>592</v>
       </c>
       <c r="D64" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="E64" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="F64" s="2">
         <v>1509</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>15</v>
       </c>
       <c r="B65" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>628</v>
+        <v>593</v>
       </c>
       <c r="D65" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="E65" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="F65" s="2">
         <v>886</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>15</v>
       </c>
       <c r="B66" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>629</v>
+        <v>738</v>
       </c>
       <c r="D66" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="E66" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="F66" s="2">
         <v>1920</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>15</v>
       </c>
       <c r="B67" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>630</v>
+        <v>594</v>
       </c>
       <c r="D67" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="E67" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="F67" s="2">
         <v>1844</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>15</v>
       </c>
       <c r="B68" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C68" t="s">
-        <v>631</v>
+        <v>595</v>
       </c>
       <c r="D68" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="E68" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="F68" s="2">
         <v>1320</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>15</v>
       </c>
       <c r="B69" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C69" t="s">
-        <v>632</v>
+        <v>596</v>
       </c>
       <c r="D69" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="E69" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="F69" s="2">
         <v>1098</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>15</v>
       </c>
       <c r="B70" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C70" t="s">
-        <v>633</v>
+        <v>597</v>
       </c>
       <c r="D70" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="E70" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F70" s="2">
         <v>770</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G70" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>15</v>
       </c>
       <c r="B71" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>634</v>
+        <v>598</v>
       </c>
       <c r="D71" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="E71" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F71" s="2">
         <v>709</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>15</v>
       </c>
       <c r="B72" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C72" t="s">
-        <v>635</v>
+        <v>599</v>
       </c>
       <c r="D72" t="s">
-        <v>452</v>
+        <v>752</v>
       </c>
       <c r="E72" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F72" s="2">
         <v>647</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>15</v>
       </c>
       <c r="B73" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C73" t="s">
-        <v>636</v>
+        <v>600</v>
       </c>
       <c r="D73" t="s">
-        <v>453</v>
+        <v>753</v>
       </c>
       <c r="E73" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F73" s="2">
         <v>508</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G73" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>15</v>
       </c>
       <c r="B74" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C74" t="s">
-        <v>637</v>
+        <v>601</v>
       </c>
       <c r="D74" t="s">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="E74" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F74" s="2">
         <v>355</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>15</v>
       </c>
       <c r="B75" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C75" t="s">
-        <v>638</v>
+        <v>602</v>
       </c>
       <c r="D75" t="s">
-        <v>455</v>
+        <v>433</v>
       </c>
       <c r="E75" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F75" s="2">
         <v>301</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>15</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>727</v>
       </c>
       <c r="C76" t="s">
-        <v>94</v>
+        <v>728</v>
       </c>
       <c r="D76" t="s">
-        <v>456</v>
+        <v>434</v>
       </c>
       <c r="E76" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F76" s="2">
         <v>202</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>15</v>
       </c>
       <c r="B77" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C77" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D77" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="F77" s="2">
         <v>195</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>15</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C78" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D78" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="F78" s="2">
         <v>182</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C79" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D79" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="F79" s="2">
         <v>91</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>16</v>
       </c>
       <c r="B80" t="s">
-        <v>100</v>
+        <v>739</v>
       </c>
       <c r="C80" t="s">
-        <v>639</v>
+        <v>755</v>
       </c>
       <c r="D80" t="s">
-        <v>459</v>
+        <v>437</v>
       </c>
       <c r="F80" s="2">
         <v>12353</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C81" t="s">
-        <v>640</v>
+        <v>603</v>
       </c>
       <c r="D81" t="s">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="F81" s="2">
         <v>7508</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>16</v>
       </c>
       <c r="B82" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C82" t="s">
-        <v>641</v>
+        <v>604</v>
       </c>
       <c r="D82" t="s">
-        <v>461</v>
+        <v>756</v>
       </c>
       <c r="F82" s="2">
         <v>6957</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>16</v>
       </c>
       <c r="B83" t="s">
-        <v>101</v>
+        <v>757</v>
       </c>
       <c r="C83" t="s">
-        <v>642</v>
+        <v>740</v>
       </c>
       <c r="D83" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
       <c r="F83" s="2">
         <v>3724</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>16</v>
       </c>
       <c r="B84" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C84" t="s">
-        <v>643</v>
+        <v>605</v>
       </c>
       <c r="D84" t="s">
-        <v>463</v>
+        <v>440</v>
       </c>
       <c r="F84" s="2">
         <v>2784</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>16</v>
       </c>
       <c r="B85" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C85" t="s">
-        <v>644</v>
+        <v>606</v>
       </c>
       <c r="D85" t="s">
-        <v>464</v>
+        <v>441</v>
       </c>
       <c r="F85" s="2">
         <v>2641</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G85" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>16</v>
       </c>
       <c r="B86" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C86" t="s">
-        <v>645</v>
+        <v>607</v>
       </c>
       <c r="D86" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="F86" s="2">
         <v>2640</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G86" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>16</v>
       </c>
       <c r="B87" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C87" t="s">
-        <v>646</v>
+        <v>608</v>
       </c>
       <c r="D87" t="s">
-        <v>466</v>
+        <v>443</v>
       </c>
       <c r="F87" s="2">
         <v>2592</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>16</v>
       </c>
       <c r="B88" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>647</v>
+        <v>758</v>
       </c>
       <c r="D88" t="s">
-        <v>467</v>
+        <v>444</v>
       </c>
       <c r="F88" s="2">
         <v>2487</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G88" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>16</v>
       </c>
       <c r="B89" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C89" t="s">
-        <v>648</v>
+        <v>759</v>
       </c>
       <c r="D89" t="s">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="F89" s="2">
         <v>2324</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G89" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>16</v>
       </c>
       <c r="B90" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C90" t="s">
-        <v>649</v>
+        <v>724</v>
       </c>
       <c r="D90" t="s">
-        <v>469</v>
+        <v>446</v>
       </c>
       <c r="F90" s="2">
         <v>2295</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>16</v>
       </c>
       <c r="B91" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C91" t="s">
-        <v>650</v>
+        <v>609</v>
       </c>
       <c r="D91" t="s">
-        <v>470</v>
+        <v>447</v>
       </c>
       <c r="F91" s="2">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2188</v>
+      </c>
+      <c r="G91" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>16</v>
       </c>
       <c r="B92" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>651</v>
+        <v>760</v>
       </c>
       <c r="D92" t="s">
-        <v>471</v>
+        <v>448</v>
       </c>
       <c r="F92" s="2">
         <v>2160</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>16</v>
       </c>
       <c r="B93" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C93" t="s">
-        <v>652</v>
+        <v>610</v>
       </c>
       <c r="D93" t="s">
-        <v>472</v>
+        <v>449</v>
       </c>
       <c r="F93" s="2">
         <v>2089</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>16</v>
       </c>
       <c r="B94" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C94" t="s">
-        <v>653</v>
+        <v>611</v>
       </c>
       <c r="D94" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
       <c r="F94" s="2">
         <v>1901</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>16</v>
       </c>
       <c r="B95" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C95" t="s">
-        <v>654</v>
+        <v>612</v>
       </c>
       <c r="D95" t="s">
-        <v>474</v>
+        <v>451</v>
       </c>
       <c r="F95" s="2">
         <v>1817</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>16</v>
       </c>
       <c r="B96" t="s">
-        <v>117</v>
+        <v>762</v>
       </c>
       <c r="C96" t="s">
-        <v>655</v>
+        <v>613</v>
       </c>
       <c r="D96" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
       <c r="F96" s="2">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C97" t="s">
-        <v>656</v>
+        <v>614</v>
       </c>
       <c r="D97" t="s">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="F97" s="2">
         <v>1568</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>16</v>
       </c>
       <c r="B98" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C98" t="s">
-        <v>657</v>
+        <v>770</v>
       </c>
       <c r="D98" t="s">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="F98" s="2">
         <v>1566</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G98" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C99" t="s">
-        <v>658</v>
+        <v>615</v>
       </c>
       <c r="D99" t="s">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="F99" s="2">
         <v>1552</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>16</v>
       </c>
       <c r="B100" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C100" t="s">
-        <v>659</v>
+        <v>761</v>
       </c>
       <c r="D100" t="s">
-        <v>479</v>
+        <v>456</v>
       </c>
       <c r="F100" s="2">
         <v>1469</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>16</v>
       </c>
       <c r="B101" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C101" t="s">
-        <v>660</v>
+        <v>616</v>
       </c>
       <c r="D101" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="F101" s="2">
         <v>1452</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>16</v>
       </c>
       <c r="B102" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C102" t="s">
-        <v>661</v>
+        <v>617</v>
       </c>
       <c r="D102" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="F102" s="2">
         <v>1449</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>16</v>
       </c>
       <c r="B103" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C103" t="s">
-        <v>662</v>
+        <v>618</v>
       </c>
       <c r="D103" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="F103" s="2">
         <v>1437</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>16</v>
       </c>
       <c r="B104" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C104" t="s">
-        <v>663</v>
+        <v>763</v>
       </c>
       <c r="D104" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="F104" s="2">
         <v>1437</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>16</v>
       </c>
       <c r="B105" t="s">
-        <v>126</v>
+        <v>741</v>
       </c>
       <c r="C105" t="s">
-        <v>664</v>
+        <v>742</v>
       </c>
       <c r="D105" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="F105" s="2">
         <v>1424</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>16</v>
       </c>
       <c r="B106" t="s">
-        <v>127</v>
+        <v>765</v>
       </c>
       <c r="C106" t="s">
-        <v>665</v>
+        <v>619</v>
       </c>
       <c r="D106" t="s">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="F106" s="2">
-        <v>1401</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>16</v>
       </c>
       <c r="B107" t="s">
-        <v>129</v>
+        <v>767</v>
       </c>
       <c r="C107" t="s">
-        <v>666</v>
+        <v>766</v>
       </c>
       <c r="D107" t="s">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="F107" s="2">
         <v>1410</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>16</v>
       </c>
       <c r="B108" t="s">
-        <v>130</v>
+        <v>743</v>
       </c>
       <c r="C108" t="s">
-        <v>667</v>
+        <v>764</v>
       </c>
       <c r="D108" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="F108" s="2">
         <v>1388</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>16</v>
       </c>
       <c r="B109" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C109" t="s">
-        <v>668</v>
+        <v>620</v>
       </c>
       <c r="D109" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="F109" s="2">
         <v>1339</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>16</v>
       </c>
       <c r="B110" t="s">
-        <v>132</v>
+        <v>744</v>
       </c>
       <c r="C110" t="s">
-        <v>669</v>
+        <v>745</v>
       </c>
       <c r="D110" t="s">
-        <v>487</v>
+        <v>464</v>
       </c>
       <c r="F110" s="2">
         <v>1334</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>16</v>
       </c>
       <c r="B111" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C111" t="s">
-        <v>670</v>
+        <v>621</v>
       </c>
       <c r="D111" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="F111" s="2">
         <v>1325</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>16</v>
       </c>
       <c r="B112" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="C112" t="s">
-        <v>671</v>
+        <v>622</v>
       </c>
       <c r="D112" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="F112" s="2">
         <v>1316</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>16</v>
       </c>
       <c r="B113" t="s">
-        <v>135</v>
+        <v>746</v>
       </c>
       <c r="C113" t="s">
-        <v>672</v>
+        <v>747</v>
       </c>
       <c r="D113" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="F113" s="2">
         <v>1304</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>16</v>
       </c>
       <c r="B114" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C114" t="s">
-        <v>673</v>
+        <v>623</v>
       </c>
       <c r="D114" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="F114" s="2">
         <v>1271</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>16</v>
       </c>
       <c r="B115" t="s">
-        <v>137</v>
+        <v>769</v>
       </c>
       <c r="C115" t="s">
-        <v>674</v>
+        <v>768</v>
       </c>
       <c r="D115" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="F115" s="2">
         <v>1262</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>16</v>
       </c>
       <c r="B116" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C116" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D116" t="s">
-        <v>471</v>
+        <v>448</v>
       </c>
       <c r="F116" s="2">
         <v>1200</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>16</v>
       </c>
       <c r="B117" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="C117" t="s">
-        <v>675</v>
+        <v>624</v>
       </c>
       <c r="D117" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="F117" s="2">
         <v>1188</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>16</v>
       </c>
       <c r="B118" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C118" t="s">
-        <v>676</v>
+        <v>625</v>
       </c>
       <c r="D118" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="F118" s="2">
         <v>1182</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>16</v>
       </c>
       <c r="B119" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="C119" t="s">
-        <v>677</v>
+        <v>626</v>
       </c>
       <c r="D119" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="F119" s="2">
         <v>1172</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>16</v>
       </c>
       <c r="B120" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C120" t="s">
-        <v>678</v>
+        <v>729</v>
       </c>
       <c r="D120" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="F120" s="2">
         <v>1152</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>16</v>
       </c>
       <c r="B121" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="C121" t="s">
-        <v>679</v>
+        <v>771</v>
       </c>
       <c r="D121" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="F121" s="2">
         <v>1151</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>16</v>
       </c>
       <c r="B122" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="C122" t="s">
-        <v>680</v>
+        <v>627</v>
       </c>
       <c r="D122" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="F122" s="2">
         <v>1147</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G122" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>16</v>
       </c>
       <c r="B123" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="C123" t="s">
-        <v>681</v>
+        <v>628</v>
       </c>
       <c r="D123" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="F123" s="2">
         <v>1142</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>16</v>
       </c>
       <c r="B124" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="C124" t="s">
-        <v>682</v>
+        <v>629</v>
       </c>
       <c r="D124" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="F124" s="2">
         <v>1131</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G124" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>16</v>
       </c>
       <c r="B125" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="C125" t="s">
-        <v>683</v>
+        <v>748</v>
       </c>
       <c r="D125" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="F125" s="2">
         <v>1073</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>16</v>
       </c>
       <c r="B126" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="C126" t="s">
-        <v>684</v>
+        <v>772</v>
       </c>
       <c r="D126" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="F126" s="2">
         <v>1073</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>16</v>
       </c>
       <c r="B127" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C127" t="s">
-        <v>685</v>
+        <v>630</v>
       </c>
       <c r="D127" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="F127" s="2">
         <v>1052</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>16</v>
       </c>
       <c r="B128" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C128" t="s">
-        <v>686</v>
+        <v>631</v>
       </c>
       <c r="D128" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="F128" s="2">
         <v>937</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>16</v>
       </c>
       <c r="B129" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="C129" t="s">
-        <v>687</v>
+        <v>749</v>
       </c>
       <c r="D129" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="F129" s="2">
         <v>911</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>16</v>
       </c>
       <c r="B130" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C130" t="s">
-        <v>688</v>
+        <v>750</v>
       </c>
       <c r="D130" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="F130" s="2">
         <v>911</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>16</v>
       </c>
       <c r="B131" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="C131" t="s">
-        <v>689</v>
+        <v>632</v>
       </c>
       <c r="D131" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="F131" s="2">
         <v>874</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>16</v>
       </c>
       <c r="B132" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C132" t="s">
-        <v>690</v>
+        <v>633</v>
       </c>
       <c r="D132" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="F132" s="2">
         <v>867</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>16</v>
       </c>
       <c r="B133" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="C133" t="s">
-        <v>691</v>
+        <v>634</v>
       </c>
       <c r="D133" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="F133" s="2">
         <v>838</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>16</v>
       </c>
       <c r="B134" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="C134" t="s">
-        <v>692</v>
+        <v>751</v>
       </c>
       <c r="D134" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="F134" s="2">
         <v>837</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>16</v>
       </c>
       <c r="B135" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C135" t="s">
-        <v>693</v>
+        <v>773</v>
       </c>
       <c r="D135" t="s">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="F135" s="2">
         <v>835</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G135" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>16</v>
       </c>
       <c r="B136" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="C136" t="s">
-        <v>694</v>
+        <v>635</v>
       </c>
       <c r="D136" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="F136" s="2">
         <v>817</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>16</v>
       </c>
       <c r="B137" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C137" t="s">
-        <v>695</v>
+        <v>636</v>
       </c>
       <c r="D137" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="F137" s="2">
         <v>809</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>16</v>
       </c>
       <c r="B138" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="C138" t="s">
-        <v>609</v>
+        <v>578</v>
       </c>
       <c r="D138" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="F138" s="2">
         <v>809</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>16</v>
       </c>
       <c r="B139" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="C139" t="s">
-        <v>696</v>
+        <v>637</v>
       </c>
       <c r="D139" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="F139" s="2">
         <v>801</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G139" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>16</v>
       </c>
       <c r="B140" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="C140" t="s">
-        <v>697</v>
+        <v>638</v>
       </c>
       <c r="D140" t="s">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="F140" s="2">
         <v>735</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>16</v>
       </c>
       <c r="B141" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C141" t="s">
-        <v>698</v>
+        <v>639</v>
       </c>
       <c r="D141" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="F141" s="2">
         <v>721</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>16</v>
       </c>
       <c r="B142" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="C142" t="s">
-        <v>699</v>
+        <v>640</v>
       </c>
       <c r="D142" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="F142" s="2">
         <v>664</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>16</v>
       </c>
       <c r="B143" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="C143" t="s">
-        <v>700</v>
+        <v>641</v>
       </c>
       <c r="D143" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="F143" s="2">
         <v>657</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>16</v>
       </c>
       <c r="B144" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="C144" t="s">
-        <v>701</v>
+        <v>642</v>
       </c>
       <c r="D144" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="F144" s="2">
         <v>650</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>16</v>
       </c>
       <c r="B145" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C145" t="s">
-        <v>702</v>
+        <v>643</v>
       </c>
       <c r="D145" t="s">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="F145" s="2">
         <v>647</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G145" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>16</v>
       </c>
       <c r="B146" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="C146" t="s">
-        <v>703</v>
+        <v>644</v>
       </c>
       <c r="D146" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="F146" s="2">
         <v>647</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G146" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>16</v>
       </c>
       <c r="B147" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="C147" t="s">
-        <v>704</v>
+        <v>645</v>
       </c>
       <c r="D147" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="F147" s="2">
         <v>647</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
       <c r="B148" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C148" t="s">
-        <v>705</v>
+        <v>646</v>
       </c>
       <c r="D148" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="F148" s="2">
         <v>616</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>16</v>
       </c>
       <c r="B149" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C149" t="s">
-        <v>706</v>
+        <v>647</v>
       </c>
       <c r="D149" t="s">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="F149" s="2">
         <v>604</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>16</v>
       </c>
       <c r="B150" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="C150" t="s">
-        <v>707</v>
+        <v>648</v>
       </c>
       <c r="D150" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="F150" s="2">
         <v>544</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G150" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>16</v>
       </c>
       <c r="B151" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="C151" t="s">
-        <v>708</v>
+        <v>737</v>
       </c>
       <c r="D151" t="s">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="F151" s="2">
         <v>451</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="C152" t="s">
-        <v>709</v>
+        <v>649</v>
       </c>
       <c r="D152" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="F152" s="2">
         <v>444</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C153" t="s">
-        <v>710</v>
+        <v>650</v>
       </c>
       <c r="D153" t="s">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="F153" s="2">
         <v>375</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="C154" t="s">
-        <v>711</v>
+        <v>651</v>
       </c>
       <c r="D154" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
       <c r="F154" s="2">
         <v>370</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="C155" t="s">
-        <v>712</v>
+        <v>652</v>
       </c>
       <c r="D155" t="s">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="F155" s="2">
         <v>342</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="C156" t="s">
-        <v>713</v>
+        <v>653</v>
       </c>
       <c r="D156" t="s">
-        <v>523</v>
+        <v>730</v>
       </c>
       <c r="F156" s="2">
         <v>329</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>16</v>
       </c>
@@ -6237,1984 +6339,2212 @@
         <v>19</v>
       </c>
       <c r="C157" t="s">
-        <v>714</v>
+        <v>654</v>
       </c>
       <c r="D157" t="s">
-        <v>524</v>
+        <v>500</v>
       </c>
       <c r="F157" s="2">
         <v>328</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="C158" t="s">
-        <v>715</v>
+        <v>655</v>
       </c>
       <c r="D158" t="s">
-        <v>525</v>
+        <v>501</v>
       </c>
       <c r="F158" s="2">
         <v>248</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="C159" t="s">
-        <v>626</v>
+        <v>591</v>
       </c>
       <c r="D159" t="s">
-        <v>526</v>
+        <v>502</v>
       </c>
       <c r="F159" s="2">
         <v>195</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>17</v>
       </c>
       <c r="B160" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="C160" t="s">
-        <v>716</v>
+        <v>656</v>
       </c>
       <c r="D160" t="s">
-        <v>527</v>
+        <v>503</v>
       </c>
       <c r="E160" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="F160" s="2">
         <v>3258</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G160" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>17</v>
       </c>
       <c r="B161" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="C161" t="s">
-        <v>717</v>
+        <v>657</v>
       </c>
       <c r="D161" t="s">
-        <v>528</v>
+        <v>504</v>
       </c>
       <c r="E161" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="F161" s="2">
-        <v>8050</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6192</v>
+      </c>
+      <c r="G161" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>17</v>
       </c>
       <c r="B162" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C162" t="s">
-        <v>718</v>
+        <v>658</v>
       </c>
       <c r="D162" t="s">
-        <v>529</v>
+        <v>505</v>
       </c>
       <c r="E162" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="F162" s="2">
-        <v>4069</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3130</v>
+      </c>
+      <c r="G162" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>17</v>
       </c>
       <c r="B163" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="C163" t="s">
-        <v>719</v>
+        <v>659</v>
       </c>
       <c r="D163" t="s">
-        <v>530</v>
+        <v>506</v>
       </c>
       <c r="E163" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F163" s="2">
-        <v>2083</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1602</v>
+      </c>
+      <c r="G163" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>17</v>
       </c>
       <c r="B164" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="C164" t="s">
-        <v>720</v>
+        <v>660</v>
       </c>
       <c r="D164" t="s">
-        <v>531</v>
+        <v>731</v>
       </c>
       <c r="E164" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F164" s="2">
-        <v>1849</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1422</v>
+      </c>
+      <c r="G164" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>17</v>
       </c>
       <c r="B165" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="C165" t="s">
-        <v>721</v>
+        <v>661</v>
       </c>
       <c r="D165" t="s">
-        <v>529</v>
+        <v>505</v>
       </c>
       <c r="E165" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F165" s="2">
-        <v>1826</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1404</v>
+      </c>
+      <c r="G165" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>17</v>
       </c>
       <c r="B166" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C166" t="s">
-        <v>722</v>
+        <v>662</v>
       </c>
       <c r="D166" t="s">
-        <v>529</v>
+        <v>505</v>
       </c>
       <c r="E166" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F166" s="2">
-        <v>1791</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1377</v>
+      </c>
+      <c r="G166" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>17</v>
       </c>
       <c r="B167" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C167" t="s">
-        <v>723</v>
+        <v>663</v>
       </c>
       <c r="D167" t="s">
-        <v>529</v>
+        <v>505</v>
       </c>
       <c r="E167" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F167" s="2">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1368</v>
+      </c>
+      <c r="G167" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>17</v>
       </c>
       <c r="B168" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="C168" t="s">
-        <v>724</v>
+        <v>664</v>
       </c>
       <c r="D168" t="s">
-        <v>532</v>
+        <v>507</v>
       </c>
       <c r="E168" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F168" s="2">
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1332</v>
+      </c>
+      <c r="G168" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>17</v>
       </c>
       <c r="B169" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="C169" t="s">
-        <v>725</v>
+        <v>665</v>
       </c>
       <c r="D169" t="s">
-        <v>533</v>
+        <v>508</v>
       </c>
       <c r="E169" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F169" s="2">
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1332</v>
+      </c>
+      <c r="G169" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>17</v>
       </c>
       <c r="B170" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="C170" t="s">
-        <v>726</v>
+        <v>666</v>
       </c>
       <c r="D170" t="s">
-        <v>534</v>
+        <v>509</v>
       </c>
       <c r="E170" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F170" s="2">
-        <v>1615</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1242</v>
+      </c>
+      <c r="G170" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>17</v>
       </c>
       <c r="B171" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="C171" t="s">
-        <v>727</v>
+        <v>667</v>
       </c>
       <c r="D171" t="s">
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="E171" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F171" s="2">
-        <v>1615</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1242</v>
+      </c>
+      <c r="G171" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>17</v>
       </c>
       <c r="B172" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C172" t="s">
-        <v>728</v>
+        <v>668</v>
       </c>
       <c r="D172" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="E172" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F172" s="2">
-        <v>1568</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1206</v>
+      </c>
+      <c r="G172" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>17</v>
       </c>
       <c r="B173" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="C173" t="s">
-        <v>729</v>
+        <v>669</v>
       </c>
       <c r="D173" t="s">
-        <v>537</v>
+        <v>512</v>
       </c>
       <c r="E173" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F173" s="2">
-        <v>1498</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1152</v>
+      </c>
+      <c r="G173" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>17</v>
       </c>
       <c r="B174" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="C174" t="s">
-        <v>730</v>
+        <v>670</v>
       </c>
       <c r="D174" t="s">
-        <v>538</v>
+        <v>513</v>
       </c>
       <c r="E174" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F174" s="2">
-        <v>1416</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1089</v>
+      </c>
+      <c r="G174" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>17</v>
       </c>
       <c r="B175" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="C175" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D175" t="s">
-        <v>539</v>
+        <v>514</v>
       </c>
       <c r="E175" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F175" s="2">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+        <v>932</v>
+      </c>
+      <c r="G175" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>17</v>
       </c>
       <c r="B176" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C176" t="s">
-        <v>732</v>
+        <v>671</v>
       </c>
       <c r="D176" t="s">
-        <v>540</v>
+        <v>515</v>
       </c>
       <c r="E176" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F176" s="2">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+        <v>924</v>
+      </c>
+      <c r="G176" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="C177" t="s">
-        <v>733</v>
+        <v>672</v>
       </c>
       <c r="D177" t="s">
-        <v>541</v>
+        <v>516</v>
       </c>
       <c r="E177" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F177" s="2">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+        <v>838</v>
+      </c>
+      <c r="G177" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="C178" t="s">
-        <v>734</v>
+        <v>673</v>
       </c>
       <c r="D178" t="s">
-        <v>542</v>
+        <v>517</v>
       </c>
       <c r="E178" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F178" s="2">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+        <v>832</v>
+      </c>
+      <c r="G178" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C179" t="s">
-        <v>735</v>
+        <v>674</v>
       </c>
       <c r="D179" t="s">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="E179" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F179" s="2">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+        <v>801</v>
+      </c>
+      <c r="G179" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="C180" t="s">
-        <v>736</v>
+        <v>675</v>
       </c>
       <c r="D180" t="s">
-        <v>544</v>
+        <v>519</v>
       </c>
       <c r="E180" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F180" s="2">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+      <c r="G180" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C181" t="s">
-        <v>737</v>
+        <v>676</v>
       </c>
       <c r="D181" t="s">
-        <v>545</v>
+        <v>520</v>
       </c>
       <c r="E181" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F181" s="2">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+        <v>601</v>
+      </c>
+      <c r="G181" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="C182" t="s">
-        <v>738</v>
+        <v>677</v>
       </c>
       <c r="D182" t="s">
-        <v>546</v>
+        <v>521</v>
       </c>
       <c r="E182" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F182" s="2">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+        <v>601</v>
+      </c>
+      <c r="G182" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="C183" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="D183" t="s">
-        <v>547</v>
+        <v>522</v>
       </c>
       <c r="E183" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F183" s="2">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+        <v>588</v>
+      </c>
+      <c r="G183" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="C184" t="s">
-        <v>739</v>
+        <v>678</v>
       </c>
       <c r="D184" t="s">
-        <v>548</v>
+        <v>523</v>
       </c>
       <c r="E184" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F184" s="2">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+        <v>544</v>
+      </c>
+      <c r="G184" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="C185" t="s">
-        <v>740</v>
+        <v>679</v>
       </c>
       <c r="D185" t="s">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="E185" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F185" s="2">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+        <v>524</v>
+      </c>
+      <c r="G185" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="C186" t="s">
-        <v>741</v>
+        <v>680</v>
       </c>
       <c r="D186" t="s">
-        <v>541</v>
+        <v>516</v>
       </c>
       <c r="E186" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F186" s="2">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+        <v>501</v>
+      </c>
+      <c r="G186" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="C187" t="s">
-        <v>742</v>
+        <v>681</v>
       </c>
       <c r="D187" t="s">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="E187" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="F187" s="2">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+      <c r="G187" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C188" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="D188" t="s">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="E188" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="F188" s="2">
         <v>390</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G188" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="C189" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="D189" t="s">
-        <v>551</v>
+        <v>733</v>
       </c>
       <c r="E189" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="F189" s="2">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+      <c r="G189" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="C190" t="s">
-        <v>743</v>
+        <v>682</v>
       </c>
       <c r="D190" t="s">
-        <v>552</v>
+        <v>526</v>
       </c>
       <c r="E190" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="F190" s="2">
-        <v>3570</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2746</v>
+      </c>
+      <c r="G190" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C191" t="s">
-        <v>744</v>
+        <v>683</v>
       </c>
       <c r="D191" t="s">
-        <v>553</v>
+        <v>527</v>
       </c>
       <c r="E191" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="F191" s="2">
         <v>2322</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G191" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="C192" t="s">
-        <v>745</v>
+        <v>684</v>
       </c>
       <c r="D192" t="s">
-        <v>529</v>
+        <v>505</v>
       </c>
       <c r="E192" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="F192" s="2">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1458</v>
+      </c>
+      <c r="G192" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="C193" t="s">
-        <v>746</v>
+        <v>685</v>
       </c>
       <c r="D193" t="s">
-        <v>553</v>
+        <v>774</v>
       </c>
       <c r="E193" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="F193" s="2">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1350</v>
+      </c>
+      <c r="G193" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="C194" t="s">
-        <v>747</v>
+        <v>686</v>
       </c>
       <c r="D194" t="s">
-        <v>537</v>
+        <v>512</v>
       </c>
       <c r="E194" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="F194" s="2">
-        <v>1615</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1242</v>
+      </c>
+      <c r="G194" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C195" t="s">
-        <v>748</v>
+        <v>687</v>
       </c>
       <c r="D195" t="s">
-        <v>554</v>
+        <v>528</v>
       </c>
       <c r="E195" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="F195" s="2">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+        <v>986</v>
+      </c>
+      <c r="G195" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="C196" t="s">
-        <v>749</v>
+        <v>688</v>
       </c>
       <c r="D196" t="s">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="E196" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="F196" s="2">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+        <v>832</v>
+      </c>
+      <c r="G196" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C197" t="s">
-        <v>750</v>
+        <v>689</v>
       </c>
       <c r="D197" t="s">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="E197" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="F197" s="2">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+        <v>755</v>
+      </c>
+      <c r="G197" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="C198" t="s">
-        <v>751</v>
+        <v>690</v>
       </c>
       <c r="D198" t="s">
-        <v>556</v>
+        <v>530</v>
       </c>
       <c r="E198" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="F198" s="2">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+        <v>735</v>
+      </c>
+      <c r="G198" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="C199" t="s">
-        <v>752</v>
+        <v>691</v>
       </c>
       <c r="D199" t="s">
-        <v>557</v>
+        <v>531</v>
       </c>
       <c r="E199" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="F199" s="2">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+      <c r="G199" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="C200" t="s">
-        <v>714</v>
+        <v>654</v>
       </c>
       <c r="D200" t="s">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="E200" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="F200" s="2">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+      <c r="G200" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>18</v>
       </c>
       <c r="B201" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C201" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D201" t="s">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="E201" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F201" s="2">
         <v>85</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="C202" t="s">
-        <v>753</v>
+        <v>692</v>
       </c>
       <c r="D202" t="s">
-        <v>559</v>
+        <v>533</v>
       </c>
       <c r="E202" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="F202" s="2">
         <v>325</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="C203" t="s">
-        <v>754</v>
+        <v>693</v>
       </c>
       <c r="D203" t="s">
-        <v>560</v>
+        <v>534</v>
       </c>
       <c r="E203" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="F203" s="2">
         <v>424</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="C204" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="D204" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E204" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="F204" s="2">
         <v>1287</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G204" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="C205" t="s">
-        <v>755</v>
+        <v>694</v>
       </c>
       <c r="D205" t="s">
-        <v>562</v>
+        <v>536</v>
       </c>
       <c r="E205" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="F205" s="2">
         <v>1020</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="C206" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D206" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E206" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="F206" s="2">
         <v>401</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G206" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C207" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="D207" t="s">
-        <v>563</v>
+        <v>537</v>
       </c>
       <c r="E207" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="F207" s="2">
         <v>13031</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G207" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="C208" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="D208" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E208" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="F208" s="2">
         <v>2148</v>
       </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G208" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C209" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="D209" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E209" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="F209" s="2">
         <v>1901</v>
       </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G209" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="C210" t="s">
-        <v>756</v>
+        <v>695</v>
       </c>
       <c r="D210" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="E210" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="F210" s="2">
         <v>1850</v>
       </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G210" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="C211" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="D211" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E211" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="F211" s="2">
         <v>1320</v>
       </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G211" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="C212" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="D212" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E212" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="F212" s="2">
         <v>1287</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G212" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="C213" t="s">
-        <v>757</v>
+        <v>696</v>
       </c>
       <c r="D213" t="s">
-        <v>565</v>
+        <v>539</v>
       </c>
       <c r="E213" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="F213" s="2">
         <v>1194</v>
       </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G213" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="C214" t="s">
-        <v>758</v>
+        <v>697</v>
       </c>
       <c r="D214" t="s">
-        <v>562</v>
+        <v>536</v>
       </c>
       <c r="E214" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="F214" s="2">
         <v>935</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="C215" t="s">
-        <v>759</v>
+        <v>698</v>
       </c>
       <c r="D215" t="s">
-        <v>566</v>
+        <v>540</v>
       </c>
       <c r="E215" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F215" s="2">
         <v>855</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="C216" t="s">
-        <v>760</v>
+        <v>699</v>
       </c>
       <c r="D216" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="E216" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F216" s="2">
         <v>826</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="C217" t="s">
-        <v>761</v>
+        <v>700</v>
       </c>
       <c r="D217" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="E217" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F217" s="2">
         <v>780</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G217" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="C218" t="s">
-        <v>761</v>
+        <v>700</v>
       </c>
       <c r="D218" t="s">
-        <v>569</v>
+        <v>543</v>
       </c>
       <c r="E218" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F218" s="2">
         <v>780</v>
       </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G218" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="C219" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="D219" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E219" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F219" s="2">
         <v>756</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="C220" t="s">
-        <v>762</v>
+        <v>701</v>
       </c>
       <c r="D220" t="s">
-        <v>541</v>
+        <v>516</v>
       </c>
       <c r="E220" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F220" s="2">
         <v>674</v>
       </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G220" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="D221" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E221" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F221" s="2">
         <v>658</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="D222" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E222" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F222" s="2">
         <v>586</v>
       </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G222" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="C223" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="D223" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E223" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F223" s="2">
         <v>429</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>18</v>
       </c>
       <c r="B224" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="C224" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="D224" t="s">
-        <v>540</v>
+        <v>515</v>
       </c>
       <c r="E224" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F224" s="2">
         <v>401</v>
       </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G224" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>18</v>
       </c>
       <c r="B225" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C225" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="D225" t="s">
-        <v>540</v>
+        <v>515</v>
       </c>
       <c r="E225" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F225" s="2">
         <v>401</v>
       </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G225" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>18</v>
       </c>
       <c r="B226" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="C226" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="D226" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
       <c r="E226" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F226" s="2">
         <v>401</v>
       </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G226" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>18</v>
       </c>
       <c r="B227" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="C227" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="D227" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
       <c r="E227" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F227" s="2">
         <v>390</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>18</v>
       </c>
       <c r="B228" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C228" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="D228" t="s">
-        <v>569</v>
+        <v>543</v>
       </c>
       <c r="E228" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F228" s="2">
         <v>380</v>
       </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G228" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>18</v>
       </c>
       <c r="B229" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="C229" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="D229" t="s">
-        <v>540</v>
+        <v>515</v>
       </c>
       <c r="E229" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F229" s="2">
         <v>364</v>
       </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G229" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>18</v>
       </c>
       <c r="B230" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="C230" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="D230" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="E230" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F230" s="2">
         <v>344</v>
       </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G230" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>18</v>
       </c>
       <c r="B231" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="C231" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="E231" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F231" s="2">
         <v>344</v>
       </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G231" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>18</v>
       </c>
       <c r="B232" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="C232" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="D232" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="E232" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F232" s="2">
         <v>344</v>
       </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G232" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>18</v>
       </c>
       <c r="B233" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="C233" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="D233" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="E233" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F233" s="2">
         <v>260</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>18</v>
       </c>
       <c r="B234" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="C234" t="s">
-        <v>763</v>
+        <v>702</v>
       </c>
       <c r="D234" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="E234" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F234" s="2">
         <v>195</v>
       </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G234" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>18</v>
       </c>
       <c r="B235" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="C235" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="D235" t="s">
-        <v>540</v>
+        <v>515</v>
       </c>
       <c r="E235" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F235" s="2">
         <v>182</v>
       </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G235" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>18</v>
       </c>
       <c r="B236" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C236" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D236" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E236" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F236" s="2">
         <v>156</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>18</v>
       </c>
       <c r="B237" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="C237" t="s">
         <v>20</v>
       </c>
       <c r="D237" t="s">
-        <v>576</v>
+        <v>550</v>
       </c>
       <c r="E237" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F237" s="2">
         <v>55</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>18</v>
       </c>
       <c r="B238" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="C238" t="s">
-        <v>764</v>
+        <v>703</v>
       </c>
       <c r="D238" t="s">
-        <v>577</v>
+        <v>551</v>
       </c>
       <c r="E238" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="F238" s="2">
         <v>9511</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>18</v>
       </c>
       <c r="B239" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="C239" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="D239" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E239" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="F239" s="2">
         <v>1452</v>
       </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G239" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>18</v>
       </c>
       <c r="B240" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="C240" t="s">
-        <v>765</v>
+        <v>704</v>
       </c>
       <c r="D240" t="s">
-        <v>562</v>
+        <v>536</v>
       </c>
       <c r="E240" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="F240" s="2">
         <v>1010</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>18</v>
       </c>
       <c r="B241" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="C241" t="s">
-        <v>766</v>
+        <v>705</v>
       </c>
       <c r="D241" t="s">
-        <v>566</v>
+        <v>540</v>
       </c>
       <c r="E241" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="F241" s="2">
         <v>1007</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>18</v>
       </c>
       <c r="B242" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="C242" t="s">
-        <v>767</v>
+        <v>706</v>
       </c>
       <c r="D242" t="s">
-        <v>566</v>
+        <v>540</v>
       </c>
       <c r="E242" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F242" s="2">
         <v>932</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>18</v>
       </c>
       <c r="B243" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="C243" t="s">
-        <v>768</v>
+        <v>707</v>
       </c>
       <c r="D243" t="s">
-        <v>566</v>
+        <v>540</v>
       </c>
       <c r="E243" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F243" s="2">
         <v>863</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>18</v>
       </c>
       <c r="B244" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="C244" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="D244" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E244" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F244" s="2">
         <v>832</v>
       </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G244" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>18</v>
       </c>
       <c r="B245" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="C245" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="D245" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E245" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F245" s="2">
         <v>832</v>
       </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G245" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>18</v>
       </c>
       <c r="B246" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="C246" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="D246" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E246" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F246" s="2">
         <v>777</v>
       </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G246" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>18</v>
       </c>
       <c r="B247" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="C247" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="D247" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E247" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F247" s="2">
         <v>755</v>
       </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G247" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>18</v>
       </c>
       <c r="B248" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="C248" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D248" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E248" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F248" s="2">
         <v>740</v>
       </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G248" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>18</v>
       </c>
       <c r="B249" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="C249" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="D249" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E249" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F249" s="2">
         <v>647</v>
       </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G249" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>18</v>
       </c>
       <c r="B250" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="C250" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="D250" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E250" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F250" s="2">
         <v>647</v>
       </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G250" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>18</v>
       </c>
       <c r="B251" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="C251" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="D251" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E251" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F251" s="2">
         <v>642</v>
       </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G251" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>18</v>
       </c>
       <c r="B252" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="C252" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="D252" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E252" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F252" s="2">
         <v>632</v>
       </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G252" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>18</v>
       </c>
       <c r="B253" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="C253" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="D253" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E253" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F253" s="2">
         <v>601</v>
       </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G253" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>18</v>
       </c>
       <c r="B254" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="C254" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="D254" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="E254" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="F254" s="2">
         <v>586</v>
       </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G254" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>18</v>
       </c>
       <c r="B255" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C255" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="D255" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E255" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="F255" s="2">
         <v>260</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>18</v>
       </c>
       <c r="B256" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C256" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="D256" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E256" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="F256" s="2">
         <v>260</v>
@@ -8225,16 +8555,16 @@
         <v>18</v>
       </c>
       <c r="B257" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C257" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="D257" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E257" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="F257" s="2">
         <v>228</v>
@@ -8245,16 +8575,16 @@
         <v>18</v>
       </c>
       <c r="B258" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="C258" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="D258" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E258" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="F258" s="2">
         <v>221</v>
@@ -8265,16 +8595,16 @@
         <v>18</v>
       </c>
       <c r="B259" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="C259" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="D259" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E259" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="F259" s="2">
         <v>182</v>
@@ -8285,16 +8615,16 @@
         <v>18</v>
       </c>
       <c r="B260" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="C260" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="D260" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E260" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="F260" s="2">
         <v>182</v>
@@ -8305,16 +8635,16 @@
         <v>18</v>
       </c>
       <c r="B261" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="C261" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="D261" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E261" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="F261" s="2">
         <v>180</v>
@@ -8325,16 +8655,16 @@
         <v>18</v>
       </c>
       <c r="B262" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="C262" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="D262" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E262" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="F262" s="2">
         <v>176</v>
@@ -8345,16 +8675,16 @@
         <v>18</v>
       </c>
       <c r="B263" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="C263" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="D263" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="E263" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="F263" s="2">
         <v>163</v>
@@ -8365,16 +8695,16 @@
         <v>18</v>
       </c>
       <c r="B264" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="C264" t="s">
-        <v>769</v>
+        <v>708</v>
       </c>
       <c r="D264" t="s">
-        <v>578</v>
+        <v>776</v>
       </c>
       <c r="E264" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="F264" s="2">
         <v>3274</v>
@@ -8385,16 +8715,16 @@
         <v>18</v>
       </c>
       <c r="B265" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="C265" t="s">
-        <v>770</v>
+        <v>734</v>
       </c>
       <c r="D265" t="s">
-        <v>579</v>
+        <v>776</v>
       </c>
       <c r="E265" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="F265" s="2">
         <v>1233</v>
@@ -8405,16 +8735,16 @@
         <v>18</v>
       </c>
       <c r="B266" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="C266" t="s">
-        <v>771</v>
+        <v>709</v>
       </c>
       <c r="D266" t="s">
-        <v>579</v>
+        <v>776</v>
       </c>
       <c r="E266" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="F266" s="2">
         <v>662</v>
@@ -8425,16 +8755,16 @@
         <v>18</v>
       </c>
       <c r="B267" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="C267" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="D267" t="s">
-        <v>579</v>
+        <v>776</v>
       </c>
       <c r="E267" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="F267" s="2">
         <v>130</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VSCode\Test\my-vue-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7448D40-B386-424A-BB47-ACDDCEEEFA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5428EE7C-88B2-41C9-BA36-F57937449F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26130" yWindow="2265" windowWidth="25425" windowHeight="12285" xr2:uid="{BFCE4DB1-B638-4533-A727-1E11ECBF49A7}"/>
+    <workbookView xWindow="8655" yWindow="4755" windowWidth="25425" windowHeight="12285" xr2:uid="{BFCE4DB1-B638-4533-A727-1E11ECBF49A7}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,6 @@
     <t>番茄沙拉</t>
   </si>
   <si>
-    <t>義式蕃茄起司沙拉</t>
-  </si>
-  <si>
     <t>夏威夷鮮魚沙拉</t>
   </si>
   <si>
@@ -2401,6 +2398,10 @@
   </si>
   <si>
     <t>砂糖、鹽、核桃、牛奶、水牛奶、蜂蜜、清爽蜂蜜、滑順蜂蜜、皇家蜂蜜</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>義式番茄起司沙拉</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3381,7 +3382,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D1" t="s">
         <v>6</v>
@@ -3393,7 +3394,7 @@
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3421,7 +3422,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -3441,16 +3442,16 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D4" t="s">
         <v>320</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>321</v>
-      </c>
-      <c r="E4" t="s">
-        <v>322</v>
       </c>
       <c r="F4" s="2">
         <v>909</v>
@@ -3461,16 +3462,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>709</v>
+      </c>
+      <c r="C5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D5" t="s">
         <v>710</v>
       </c>
-      <c r="C5" t="s">
-        <v>323</v>
-      </c>
-      <c r="D5" t="s">
-        <v>711</v>
-      </c>
       <c r="E5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F5" s="2">
         <v>598</v>
@@ -3481,16 +3482,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D6" t="s">
         <v>325</v>
       </c>
-      <c r="D6" t="s">
-        <v>326</v>
-      </c>
       <c r="E6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F6" s="2">
         <v>404</v>
@@ -3501,16 +3502,16 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C7" t="s">
         <v>329</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>330</v>
       </c>
-      <c r="D7" t="s">
-        <v>331</v>
-      </c>
       <c r="E7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F7" s="2">
         <v>260</v>
@@ -3521,16 +3522,16 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D8" t="s">
         <v>334</v>
       </c>
-      <c r="D8" t="s">
-        <v>335</v>
-      </c>
       <c r="E8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F8" s="2">
         <v>137</v>
@@ -3544,13 +3545,13 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F9" s="2">
         <v>126</v>
@@ -3561,16 +3562,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>776</v>
       </c>
       <c r="C10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F10" s="2">
         <v>2429</v>
@@ -3581,16 +3582,16 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F11" s="2">
         <v>1197</v>
@@ -3601,16 +3602,16 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F12" s="2">
         <v>677</v>
@@ -3621,16 +3622,16 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
       <c r="D13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F13" s="2">
         <v>325</v>
@@ -3641,22 +3642,22 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E14" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F14" s="2">
         <v>1728</v>
       </c>
       <c r="G14" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3664,22 +3665,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F15" s="2">
         <v>1024</v>
       </c>
       <c r="G15" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3687,22 +3688,22 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F16" s="2">
         <v>770</v>
       </c>
       <c r="G16" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3710,22 +3711,22 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
+        <v>719</v>
+      </c>
+      <c r="C17" t="s">
         <v>720</v>
       </c>
-      <c r="C17" t="s">
-        <v>721</v>
-      </c>
       <c r="D17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F17" s="2">
         <v>260</v>
       </c>
       <c r="G17" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3733,22 +3734,22 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D18" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E18" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="2">
         <v>1815</v>
       </c>
       <c r="G18" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3756,39 +3757,39 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D19" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F19" s="2">
         <v>1320</v>
       </c>
       <c r="G19" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E20" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F20" s="2">
         <v>709</v>
@@ -3799,16 +3800,16 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D21" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F21" s="2">
         <v>490</v>
@@ -3819,22 +3820,22 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D22" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E22" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F22" s="2">
         <v>137</v>
       </c>
       <c r="G22" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3842,22 +3843,22 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D23" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F23" s="2">
         <v>117</v>
       </c>
       <c r="G23" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3865,16 +3866,16 @@
         <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C24" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D24" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F24" s="2">
         <v>10098</v>
@@ -3885,22 +3886,22 @@
         <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D25" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F25" s="2">
         <v>2592</v>
       </c>
       <c r="G25" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3908,16 +3909,16 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E26" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F26" s="2">
         <v>1892</v>
@@ -3928,16 +3929,16 @@
         <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E27" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F27" s="2">
         <v>1584</v>
@@ -3948,16 +3949,16 @@
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D28" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E28" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F28" s="2">
         <v>1530</v>
@@ -3968,16 +3969,16 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D29" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E29" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F29" s="2">
         <v>1377</v>
@@ -3988,16 +3989,16 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D30" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E30" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F30" s="2">
         <v>1353</v>
@@ -4008,16 +4009,16 @@
         <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D31" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E31" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F31" s="2">
         <v>1276</v>
@@ -4028,16 +4029,16 @@
         <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D32" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E32" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F32" s="2">
         <v>1213</v>
@@ -4048,16 +4049,16 @@
         <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D33" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E33" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F33" s="2">
         <v>1155</v>
@@ -4068,16 +4069,16 @@
         <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C34" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D34" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E34" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F34" s="2">
         <v>1122</v>
@@ -4088,16 +4089,16 @@
         <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D35" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E35" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F35" s="2">
         <v>1056</v>
@@ -4108,22 +4109,22 @@
         <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D36" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E36" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F36" s="2">
         <v>911</v>
       </c>
       <c r="G36" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -4131,16 +4132,16 @@
         <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D37" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E37" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F37" s="2">
         <v>882</v>
@@ -4151,16 +4152,16 @@
         <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D38" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E38" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F38" s="2">
         <v>843</v>
@@ -4171,16 +4172,16 @@
         <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D39" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E39" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F39" s="2">
         <v>824</v>
@@ -4191,16 +4192,16 @@
         <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D40" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E40" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F40" s="2">
         <v>809</v>
@@ -4211,16 +4212,16 @@
         <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C41" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D41" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E41" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F41" s="2">
         <v>801</v>
@@ -4231,16 +4232,16 @@
         <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D42" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E42" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F42" s="2">
         <v>747</v>
@@ -4251,16 +4252,16 @@
         <v>15</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D43" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F43" s="2">
         <v>743</v>
@@ -4271,16 +4272,16 @@
         <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C44" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D44" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E44" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F44" s="2">
         <v>677</v>
@@ -4291,16 +4292,16 @@
         <v>15</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D45" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E45" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F45" s="2">
         <v>662</v>
@@ -4311,16 +4312,16 @@
         <v>15</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D46" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E46" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F46" s="2">
         <v>632</v>
@@ -4331,16 +4332,16 @@
         <v>15</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D47" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E47" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F47" s="2">
         <v>609</v>
@@ -4351,16 +4352,16 @@
         <v>15</v>
       </c>
       <c r="B48" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" t="s">
         <v>60</v>
       </c>
-      <c r="C48" t="s">
-        <v>61</v>
-      </c>
       <c r="D48" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E48" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F48" s="2">
         <v>602</v>
@@ -4371,16 +4372,16 @@
         <v>15</v>
       </c>
       <c r="B49" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C49" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D49" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E49" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F49" s="2">
         <v>563</v>
@@ -4391,16 +4392,16 @@
         <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D50" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E50" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F50" s="2">
         <v>458</v>
@@ -4411,16 +4412,16 @@
         <v>15</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D51" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E51" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F51" s="2">
         <v>429</v>
@@ -4431,16 +4432,16 @@
         <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C52" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D52" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E52" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F52" s="2">
         <v>403</v>
@@ -4451,16 +4452,16 @@
         <v>15</v>
       </c>
       <c r="B53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C53" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D53" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E53" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F53" s="2">
         <v>396</v>
@@ -4471,16 +4472,16 @@
         <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D54" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E54" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F54" s="2">
         <v>267</v>
@@ -4491,16 +4492,16 @@
         <v>15</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D55" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E55" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F55" s="2">
         <v>246</v>
@@ -4511,16 +4512,16 @@
         <v>15</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C56" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D56" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E56" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F56" s="2">
         <v>234</v>
@@ -4531,16 +4532,16 @@
         <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C57" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D57" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E57" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F57" s="2">
         <v>205</v>
@@ -4551,16 +4552,16 @@
         <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C58" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E58" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F58" s="2">
         <v>195</v>
@@ -4571,16 +4572,16 @@
         <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C59" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D59" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E59" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F59" s="2">
         <v>117</v>
@@ -4591,16 +4592,16 @@
         <v>15</v>
       </c>
       <c r="B60" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" t="s">
         <v>72</v>
       </c>
-      <c r="C60" t="s">
-        <v>73</v>
-      </c>
       <c r="D60" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E60" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F60" s="2">
         <v>111</v>
@@ -4611,16 +4612,16 @@
         <v>15</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C61" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D61" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E61" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F61" s="2">
         <v>924</v>
@@ -4631,16 +4632,16 @@
         <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C62" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D62" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E62" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F62" s="2">
         <v>195</v>
@@ -4651,16 +4652,16 @@
         <v>15</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C63" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D63" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F63" s="2">
         <v>195</v>
@@ -4671,16 +4672,16 @@
         <v>15</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D64" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E64" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F64" s="2">
         <v>1509</v>
@@ -4691,16 +4692,16 @@
         <v>15</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D65" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E65" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F65" s="2">
         <v>886</v>
@@ -4711,16 +4712,16 @@
         <v>15</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C66" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D66" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E66" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F66" s="2">
         <v>1920</v>
@@ -4731,16 +4732,16 @@
         <v>15</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D67" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E67" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F67" s="2">
         <v>1844</v>
@@ -4751,16 +4752,16 @@
         <v>15</v>
       </c>
       <c r="B68" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D68" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E68" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F68" s="2">
         <v>1320</v>
@@ -4771,16 +4772,16 @@
         <v>15</v>
       </c>
       <c r="B69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C69" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D69" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E69" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F69" s="2">
         <v>1098</v>
@@ -4791,22 +4792,22 @@
         <v>15</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C70" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D70" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E70" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F70" s="2">
         <v>770</v>
       </c>
       <c r="G70" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -4814,16 +4815,16 @@
         <v>15</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C71" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D71" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E71" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F71" s="2">
         <v>709</v>
@@ -4834,16 +4835,16 @@
         <v>15</v>
       </c>
       <c r="B72" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C72" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D72" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E72" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F72" s="2">
         <v>647</v>
@@ -4854,22 +4855,22 @@
         <v>15</v>
       </c>
       <c r="B73" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C73" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D73" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E73" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F73" s="2">
         <v>508</v>
       </c>
       <c r="G73" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -4877,16 +4878,16 @@
         <v>15</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C74" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D74" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E74" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F74" s="2">
         <v>355</v>
@@ -4897,16 +4898,16 @@
         <v>15</v>
       </c>
       <c r="B75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C75" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D75" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E75" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F75" s="2">
         <v>301</v>
@@ -4917,16 +4918,16 @@
         <v>15</v>
       </c>
       <c r="B76" t="s">
+        <v>726</v>
+      </c>
+      <c r="C76" t="s">
         <v>727</v>
       </c>
-      <c r="C76" t="s">
-        <v>728</v>
-      </c>
       <c r="D76" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E76" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F76" s="2">
         <v>202</v>
@@ -4937,13 +4938,13 @@
         <v>15</v>
       </c>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C77" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F77" s="2">
         <v>195</v>
@@ -4954,13 +4955,13 @@
         <v>15</v>
       </c>
       <c r="B78" t="s">
+        <v>89</v>
+      </c>
+      <c r="C78" t="s">
         <v>90</v>
       </c>
-      <c r="C78" t="s">
-        <v>91</v>
-      </c>
       <c r="D78" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F78" s="2">
         <v>182</v>
@@ -4971,13 +4972,13 @@
         <v>15</v>
       </c>
       <c r="B79" t="s">
+        <v>91</v>
+      </c>
+      <c r="C79" t="s">
         <v>92</v>
       </c>
-      <c r="C79" t="s">
-        <v>93</v>
-      </c>
       <c r="D79" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F79" s="2">
         <v>91</v>
@@ -4988,13 +4989,13 @@
         <v>16</v>
       </c>
       <c r="B80" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C80" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D80" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F80" s="2">
         <v>12353</v>
@@ -5005,13 +5006,13 @@
         <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C81" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D81" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F81" s="2">
         <v>7508</v>
@@ -5022,13 +5023,13 @@
         <v>16</v>
       </c>
       <c r="B82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C82" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D82" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F82" s="2">
         <v>6957</v>
@@ -5039,13 +5040,13 @@
         <v>16</v>
       </c>
       <c r="B83" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C83" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D83" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F83" s="2">
         <v>3724</v>
@@ -5056,13 +5057,13 @@
         <v>16</v>
       </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C84" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D84" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F84" s="2">
         <v>2784</v>
@@ -5073,19 +5074,19 @@
         <v>16</v>
       </c>
       <c r="B85" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C85" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D85" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F85" s="2">
         <v>2641</v>
       </c>
       <c r="G85" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -5093,19 +5094,19 @@
         <v>16</v>
       </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C86" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D86" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F86" s="2">
         <v>2640</v>
       </c>
       <c r="G86" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -5113,13 +5114,13 @@
         <v>16</v>
       </c>
       <c r="B87" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C87" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D87" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F87" s="2">
         <v>2592</v>
@@ -5130,19 +5131,19 @@
         <v>16</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C88" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D88" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F88" s="2">
         <v>2487</v>
       </c>
       <c r="G88" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -5150,19 +5151,19 @@
         <v>16</v>
       </c>
       <c r="B89" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C89" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D89" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F89" s="2">
         <v>2324</v>
       </c>
       <c r="G89" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -5170,13 +5171,13 @@
         <v>16</v>
       </c>
       <c r="B90" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C90" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D90" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F90" s="2">
         <v>2295</v>
@@ -5187,19 +5188,19 @@
         <v>16</v>
       </c>
       <c r="B91" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C91" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D91" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F91" s="2">
         <v>2188</v>
       </c>
       <c r="G91" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -5207,13 +5208,13 @@
         <v>16</v>
       </c>
       <c r="B92" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C92" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D92" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F92" s="2">
         <v>2160</v>
@@ -5224,13 +5225,13 @@
         <v>16</v>
       </c>
       <c r="B93" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C93" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D93" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F93" s="2">
         <v>2089</v>
@@ -5241,13 +5242,13 @@
         <v>16</v>
       </c>
       <c r="B94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D94" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F94" s="2">
         <v>1901</v>
@@ -5258,13 +5259,13 @@
         <v>16</v>
       </c>
       <c r="B95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C95" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D95" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F95" s="2">
         <v>1817</v>
@@ -5275,13 +5276,13 @@
         <v>16</v>
       </c>
       <c r="B96" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C96" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D96" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F96" s="2">
         <v>1760</v>
@@ -5292,13 +5293,13 @@
         <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C97" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D97" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F97" s="2">
         <v>1568</v>
@@ -5309,19 +5310,19 @@
         <v>16</v>
       </c>
       <c r="B98" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C98" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D98" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F98" s="2">
         <v>1566</v>
       </c>
       <c r="G98" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -5329,13 +5330,13 @@
         <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C99" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D99" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F99" s="2">
         <v>1552</v>
@@ -5346,13 +5347,13 @@
         <v>16</v>
       </c>
       <c r="B100" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C100" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D100" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F100" s="2">
         <v>1469</v>
@@ -5363,13 +5364,13 @@
         <v>16</v>
       </c>
       <c r="B101" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C101" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D101" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F101" s="2">
         <v>1452</v>
@@ -5380,13 +5381,13 @@
         <v>16</v>
       </c>
       <c r="B102" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C102" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D102" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F102" s="2">
         <v>1449</v>
@@ -5397,13 +5398,13 @@
         <v>16</v>
       </c>
       <c r="B103" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C103" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D103" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F103" s="2">
         <v>1437</v>
@@ -5414,13 +5415,13 @@
         <v>16</v>
       </c>
       <c r="B104" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C104" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D104" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F104" s="2">
         <v>1437</v>
@@ -5431,13 +5432,13 @@
         <v>16</v>
       </c>
       <c r="B105" t="s">
+        <v>740</v>
+      </c>
+      <c r="C105" t="s">
         <v>741</v>
       </c>
-      <c r="C105" t="s">
-        <v>742</v>
-      </c>
       <c r="D105" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F105" s="2">
         <v>1424</v>
@@ -5448,13 +5449,13 @@
         <v>16</v>
       </c>
       <c r="B106" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C106" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D106" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F106" s="2">
         <v>1410</v>
@@ -5465,13 +5466,13 @@
         <v>16</v>
       </c>
       <c r="B107" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C107" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D107" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F107" s="2">
         <v>1410</v>
@@ -5482,13 +5483,13 @@
         <v>16</v>
       </c>
       <c r="B108" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C108" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D108" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F108" s="2">
         <v>1388</v>
@@ -5499,13 +5500,13 @@
         <v>16</v>
       </c>
       <c r="B109" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C109" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D109" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F109" s="2">
         <v>1339</v>
@@ -5516,13 +5517,13 @@
         <v>16</v>
       </c>
       <c r="B110" t="s">
+        <v>743</v>
+      </c>
+      <c r="C110" t="s">
         <v>744</v>
       </c>
-      <c r="C110" t="s">
-        <v>745</v>
-      </c>
       <c r="D110" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F110" s="2">
         <v>1334</v>
@@ -5533,13 +5534,13 @@
         <v>16</v>
       </c>
       <c r="B111" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C111" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D111" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F111" s="2">
         <v>1325</v>
@@ -5550,13 +5551,13 @@
         <v>16</v>
       </c>
       <c r="B112" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C112" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D112" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F112" s="2">
         <v>1316</v>
@@ -5567,13 +5568,13 @@
         <v>16</v>
       </c>
       <c r="B113" t="s">
+        <v>745</v>
+      </c>
+      <c r="C113" t="s">
         <v>746</v>
       </c>
-      <c r="C113" t="s">
-        <v>747</v>
-      </c>
       <c r="D113" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F113" s="2">
         <v>1304</v>
@@ -5584,13 +5585,13 @@
         <v>16</v>
       </c>
       <c r="B114" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C114" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D114" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F114" s="2">
         <v>1271</v>
@@ -5601,13 +5602,13 @@
         <v>16</v>
       </c>
       <c r="B115" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C115" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D115" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F115" s="2">
         <v>1262</v>
@@ -5618,13 +5619,13 @@
         <v>16</v>
       </c>
       <c r="B116" t="s">
+        <v>121</v>
+      </c>
+      <c r="C116" t="s">
         <v>122</v>
       </c>
-      <c r="C116" t="s">
-        <v>123</v>
-      </c>
       <c r="D116" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F116" s="2">
         <v>1200</v>
@@ -5635,13 +5636,13 @@
         <v>16</v>
       </c>
       <c r="B117" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C117" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D117" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F117" s="2">
         <v>1188</v>
@@ -5652,13 +5653,13 @@
         <v>16</v>
       </c>
       <c r="B118" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C118" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D118" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F118" s="2">
         <v>1182</v>
@@ -5669,13 +5670,13 @@
         <v>16</v>
       </c>
       <c r="B119" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C119" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D119" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F119" s="2">
         <v>1172</v>
@@ -5686,13 +5687,13 @@
         <v>16</v>
       </c>
       <c r="B120" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C120" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D120" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F120" s="2">
         <v>1152</v>
@@ -5703,13 +5704,13 @@
         <v>16</v>
       </c>
       <c r="B121" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C121" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D121" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F121" s="2">
         <v>1151</v>
@@ -5720,19 +5721,19 @@
         <v>16</v>
       </c>
       <c r="B122" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D122" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F122" s="2">
         <v>1147</v>
       </c>
       <c r="G122" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -5740,13 +5741,13 @@
         <v>16</v>
       </c>
       <c r="B123" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C123" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D123" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F123" s="2">
         <v>1142</v>
@@ -5757,19 +5758,19 @@
         <v>16</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C124" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D124" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F124" s="2">
         <v>1131</v>
       </c>
       <c r="G124" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5777,13 +5778,13 @@
         <v>16</v>
       </c>
       <c r="B125" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C125" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D125" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F125" s="2">
         <v>1073</v>
@@ -5794,13 +5795,13 @@
         <v>16</v>
       </c>
       <c r="B126" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C126" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D126" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F126" s="2">
         <v>1073</v>
@@ -5811,13 +5812,13 @@
         <v>16</v>
       </c>
       <c r="B127" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C127" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D127" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F127" s="2">
         <v>1052</v>
@@ -5828,13 +5829,13 @@
         <v>16</v>
       </c>
       <c r="B128" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C128" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D128" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F128" s="2">
         <v>937</v>
@@ -5845,13 +5846,13 @@
         <v>16</v>
       </c>
       <c r="B129" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C129" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D129" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F129" s="2">
         <v>911</v>
@@ -5862,13 +5863,13 @@
         <v>16</v>
       </c>
       <c r="B130" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C130" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D130" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F130" s="2">
         <v>911</v>
@@ -5879,13 +5880,13 @@
         <v>16</v>
       </c>
       <c r="B131" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C131" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D131" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F131" s="2">
         <v>874</v>
@@ -5896,13 +5897,13 @@
         <v>16</v>
       </c>
       <c r="B132" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C132" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D132" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F132" s="2">
         <v>867</v>
@@ -5913,13 +5914,13 @@
         <v>16</v>
       </c>
       <c r="B133" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C133" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D133" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F133" s="2">
         <v>838</v>
@@ -5930,13 +5931,13 @@
         <v>16</v>
       </c>
       <c r="B134" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C134" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D134" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F134" s="2">
         <v>837</v>
@@ -5947,19 +5948,19 @@
         <v>16</v>
       </c>
       <c r="B135" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C135" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D135" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F135" s="2">
         <v>835</v>
       </c>
       <c r="G135" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5967,13 +5968,13 @@
         <v>16</v>
       </c>
       <c r="B136" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C136" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D136" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F136" s="2">
         <v>817</v>
@@ -5984,13 +5985,13 @@
         <v>16</v>
       </c>
       <c r="B137" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C137" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F137" s="2">
         <v>809</v>
@@ -6001,13 +6002,13 @@
         <v>16</v>
       </c>
       <c r="B138" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C138" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D138" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F138" s="2">
         <v>809</v>
@@ -6018,19 +6019,19 @@
         <v>16</v>
       </c>
       <c r="B139" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C139" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D139" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F139" s="2">
         <v>801</v>
       </c>
       <c r="G139" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -6038,13 +6039,13 @@
         <v>16</v>
       </c>
       <c r="B140" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C140" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D140" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F140" s="2">
         <v>735</v>
@@ -6055,13 +6056,13 @@
         <v>16</v>
       </c>
       <c r="B141" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C141" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D141" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F141" s="2">
         <v>721</v>
@@ -6072,13 +6073,13 @@
         <v>16</v>
       </c>
       <c r="B142" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C142" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D142" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F142" s="2">
         <v>664</v>
@@ -6089,13 +6090,13 @@
         <v>16</v>
       </c>
       <c r="B143" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C143" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D143" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F143" s="2">
         <v>657</v>
@@ -6106,13 +6107,13 @@
         <v>16</v>
       </c>
       <c r="B144" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C144" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D144" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F144" s="2">
         <v>650</v>
@@ -6123,19 +6124,19 @@
         <v>16</v>
       </c>
       <c r="B145" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C145" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D145" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F145" s="2">
         <v>647</v>
       </c>
       <c r="G145" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -6143,19 +6144,19 @@
         <v>16</v>
       </c>
       <c r="B146" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C146" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D146" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F146" s="2">
         <v>647</v>
       </c>
       <c r="G146" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6163,13 +6164,13 @@
         <v>16</v>
       </c>
       <c r="B147" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C147" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D147" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F147" s="2">
         <v>647</v>
@@ -6180,13 +6181,13 @@
         <v>16</v>
       </c>
       <c r="B148" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C148" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D148" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F148" s="2">
         <v>616</v>
@@ -6197,13 +6198,13 @@
         <v>16</v>
       </c>
       <c r="B149" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C149" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D149" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F149" s="2">
         <v>604</v>
@@ -6214,19 +6215,19 @@
         <v>16</v>
       </c>
       <c r="B150" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C150" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D150" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F150" s="2">
         <v>544</v>
       </c>
       <c r="G150" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -6234,13 +6235,13 @@
         <v>16</v>
       </c>
       <c r="B151" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C151" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D151" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F151" s="2">
         <v>451</v>
@@ -6251,13 +6252,13 @@
         <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C152" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D152" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F152" s="2">
         <v>444</v>
@@ -6268,13 +6269,13 @@
         <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C153" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D153" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F153" s="2">
         <v>375</v>
@@ -6285,13 +6286,13 @@
         <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C154" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D154" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F154" s="2">
         <v>370</v>
@@ -6302,13 +6303,13 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C155" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D155" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F155" s="2">
         <v>342</v>
@@ -6319,13 +6320,13 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C156" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D156" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F156" s="2">
         <v>329</v>
@@ -6339,10 +6340,10 @@
         <v>19</v>
       </c>
       <c r="C157" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D157" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F157" s="2">
         <v>328</v>
@@ -6353,13 +6354,13 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D158" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F158" s="2">
         <v>248</v>
@@ -6370,13 +6371,13 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D159" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F159" s="2">
         <v>195</v>
@@ -6387,22 +6388,22 @@
         <v>17</v>
       </c>
       <c r="B160" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D160" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E160" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F160" s="2">
         <v>3258</v>
       </c>
       <c r="G160" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -6410,22 +6411,22 @@
         <v>17</v>
       </c>
       <c r="B161" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D161" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E161" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F161" s="2">
         <v>6192</v>
       </c>
       <c r="G161" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -6433,22 +6434,22 @@
         <v>17</v>
       </c>
       <c r="B162" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C162" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D162" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E162" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F162" s="2">
         <v>3130</v>
       </c>
       <c r="G162" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -6456,22 +6457,22 @@
         <v>17</v>
       </c>
       <c r="B163" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C163" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D163" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E163" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F163" s="2">
         <v>1602</v>
       </c>
       <c r="G163" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -6479,22 +6480,22 @@
         <v>17</v>
       </c>
       <c r="B164" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C164" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D164" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E164" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F164" s="2">
         <v>1422</v>
       </c>
       <c r="G164" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -6502,22 +6503,22 @@
         <v>17</v>
       </c>
       <c r="B165" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C165" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D165" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E165" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F165" s="2">
         <v>1404</v>
       </c>
       <c r="G165" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -6525,22 +6526,22 @@
         <v>17</v>
       </c>
       <c r="B166" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C166" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D166" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E166" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F166" s="2">
         <v>1377</v>
       </c>
       <c r="G166" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -6548,22 +6549,22 @@
         <v>17</v>
       </c>
       <c r="B167" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C167" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D167" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E167" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F167" s="2">
         <v>1368</v>
       </c>
       <c r="G167" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6571,22 +6572,22 @@
         <v>17</v>
       </c>
       <c r="B168" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C168" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D168" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E168" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F168" s="2">
         <v>1332</v>
       </c>
       <c r="G168" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6594,22 +6595,22 @@
         <v>17</v>
       </c>
       <c r="B169" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C169" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D169" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E169" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F169" s="2">
         <v>1332</v>
       </c>
       <c r="G169" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6617,22 +6618,22 @@
         <v>17</v>
       </c>
       <c r="B170" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C170" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D170" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E170" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F170" s="2">
         <v>1242</v>
       </c>
       <c r="G170" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6640,22 +6641,22 @@
         <v>17</v>
       </c>
       <c r="B171" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C171" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D171" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E171" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F171" s="2">
         <v>1242</v>
       </c>
       <c r="G171" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6663,22 +6664,22 @@
         <v>17</v>
       </c>
       <c r="B172" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C172" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D172" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E172" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F172" s="2">
         <v>1206</v>
       </c>
       <c r="G172" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6686,22 +6687,22 @@
         <v>17</v>
       </c>
       <c r="B173" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C173" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D173" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E173" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F173" s="2">
         <v>1152</v>
       </c>
       <c r="G173" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6709,22 +6710,22 @@
         <v>17</v>
       </c>
       <c r="B174" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C174" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D174" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E174" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F174" s="2">
         <v>1089</v>
       </c>
       <c r="G174" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6732,22 +6733,22 @@
         <v>17</v>
       </c>
       <c r="B175" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C175" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D175" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E175" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F175" s="2">
         <v>932</v>
       </c>
       <c r="G175" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6755,22 +6756,22 @@
         <v>17</v>
       </c>
       <c r="B176" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C176" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D176" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E176" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F176" s="2">
         <v>924</v>
       </c>
       <c r="G176" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6778,22 +6779,22 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C177" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D177" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E177" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F177" s="2">
         <v>838</v>
       </c>
       <c r="G177" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6801,22 +6802,22 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C178" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D178" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E178" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F178" s="2">
         <v>832</v>
       </c>
       <c r="G178" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6824,22 +6825,22 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C179" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D179" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E179" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F179" s="2">
         <v>801</v>
       </c>
       <c r="G179" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6847,22 +6848,22 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C180" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D180" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E180" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F180" s="2">
         <v>618</v>
       </c>
       <c r="G180" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6870,22 +6871,22 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C181" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D181" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E181" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F181" s="2">
         <v>601</v>
       </c>
       <c r="G181" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6893,22 +6894,22 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C182" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D182" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E182" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F182" s="2">
         <v>601</v>
       </c>
       <c r="G182" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6916,22 +6917,22 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C183" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D183" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E183" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F183" s="2">
         <v>588</v>
       </c>
       <c r="G183" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -6939,22 +6940,22 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C184" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D184" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E184" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F184" s="2">
         <v>544</v>
       </c>
       <c r="G184" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -6962,22 +6963,22 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C185" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D185" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E185" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F185" s="2">
         <v>524</v>
       </c>
       <c r="G185" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -6985,22 +6986,22 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C186" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D186" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E186" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F186" s="2">
         <v>501</v>
       </c>
       <c r="G186" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7008,22 +7009,22 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C187" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D187" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E187" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F187" s="2">
         <v>415</v>
       </c>
       <c r="G187" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7031,22 +7032,22 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C188" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D188" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E188" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F188" s="2">
         <v>390</v>
       </c>
       <c r="G188" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7054,22 +7055,22 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
+        <v>196</v>
+      </c>
+      <c r="C189" t="s">
         <v>197</v>
       </c>
-      <c r="C189" t="s">
-        <v>198</v>
-      </c>
       <c r="D189" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E189" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F189" s="2">
         <v>390</v>
       </c>
       <c r="G189" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7077,22 +7078,22 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C190" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D190" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E190" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F190" s="2">
         <v>2746</v>
       </c>
       <c r="G190" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7100,22 +7101,22 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C191" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D191" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E191" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F191" s="2">
         <v>2322</v>
       </c>
       <c r="G191" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7123,22 +7124,22 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C192" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D192" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E192" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F192" s="2">
         <v>1458</v>
       </c>
       <c r="G192" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7146,22 +7147,22 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C193" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D193" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E193" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F193" s="2">
         <v>1350</v>
       </c>
       <c r="G193" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7169,22 +7170,22 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C194" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D194" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E194" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F194" s="2">
         <v>1242</v>
       </c>
       <c r="G194" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -7192,22 +7193,22 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C195" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D195" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E195" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F195" s="2">
         <v>986</v>
       </c>
       <c r="G195" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -7215,22 +7216,22 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C196" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D196" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E196" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F196" s="2">
         <v>832</v>
       </c>
       <c r="G196" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -7238,22 +7239,22 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C197" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D197" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E197" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F197" s="2">
         <v>755</v>
       </c>
       <c r="G197" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -7261,22 +7262,22 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C198" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D198" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E198" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F198" s="2">
         <v>735</v>
       </c>
       <c r="G198" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -7284,22 +7285,22 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C199" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D199" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E199" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F199" s="2">
         <v>328</v>
       </c>
       <c r="G199" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -7307,22 +7308,22 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C200" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D200" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E200" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F200" s="2">
         <v>328</v>
       </c>
       <c r="G200" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7330,16 +7331,16 @@
         <v>18</v>
       </c>
       <c r="B201" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C201" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D201" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E201" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F201" s="2">
         <v>85</v>
@@ -7350,16 +7351,16 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C202" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D202" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E202" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F202" s="2">
         <v>325</v>
@@ -7370,16 +7371,16 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C203" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D203" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E203" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F203" s="2">
         <v>424</v>
@@ -7390,22 +7391,22 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
+        <v>212</v>
+      </c>
+      <c r="C204" t="s">
         <v>213</v>
       </c>
-      <c r="C204" t="s">
-        <v>214</v>
-      </c>
       <c r="D204" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E204" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F204" s="2">
         <v>1287</v>
       </c>
       <c r="G204" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -7413,16 +7414,16 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C205" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D205" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E205" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F205" s="2">
         <v>1020</v>
@@ -7433,22 +7434,22 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
+        <v>216</v>
+      </c>
+      <c r="C206" t="s">
         <v>217</v>
       </c>
-      <c r="C206" t="s">
-        <v>218</v>
-      </c>
       <c r="D206" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E206" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F206" s="2">
         <v>401</v>
       </c>
       <c r="G206" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -7456,22 +7457,22 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
+        <v>218</v>
+      </c>
+      <c r="C207" t="s">
         <v>219</v>
       </c>
-      <c r="C207" t="s">
-        <v>220</v>
-      </c>
       <c r="D207" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E207" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F207" s="2">
         <v>13031</v>
       </c>
       <c r="G207" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -7479,22 +7480,22 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
+        <v>220</v>
+      </c>
+      <c r="C208" t="s">
         <v>221</v>
       </c>
-      <c r="C208" t="s">
-        <v>222</v>
-      </c>
       <c r="D208" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E208" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F208" s="2">
         <v>2148</v>
       </c>
       <c r="G208" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -7502,22 +7503,22 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
+        <v>222</v>
+      </c>
+      <c r="C209" t="s">
         <v>223</v>
       </c>
-      <c r="C209" t="s">
-        <v>224</v>
-      </c>
       <c r="D209" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E209" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F209" s="2">
         <v>1901</v>
       </c>
       <c r="G209" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7525,22 +7526,22 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C210" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D210" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E210" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F210" s="2">
         <v>1850</v>
       </c>
       <c r="G210" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -7548,22 +7549,22 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
+        <v>225</v>
+      </c>
+      <c r="C211" t="s">
         <v>226</v>
       </c>
-      <c r="C211" t="s">
-        <v>227</v>
-      </c>
       <c r="D211" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E211" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F211" s="2">
         <v>1320</v>
       </c>
       <c r="G211" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7571,22 +7572,22 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
+        <v>227</v>
+      </c>
+      <c r="C212" t="s">
         <v>228</v>
       </c>
-      <c r="C212" t="s">
-        <v>229</v>
-      </c>
       <c r="D212" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E212" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F212" s="2">
         <v>1287</v>
       </c>
       <c r="G212" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7594,22 +7595,22 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C213" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D213" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E213" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F213" s="2">
         <v>1194</v>
       </c>
       <c r="G213" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -7617,16 +7618,16 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C214" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D214" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E214" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F214" s="2">
         <v>935</v>
@@ -7637,16 +7638,16 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C215" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D215" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E215" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F215" s="2">
         <v>855</v>
@@ -7657,16 +7658,16 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C216" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D216" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E216" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F216" s="2">
         <v>826</v>
@@ -7677,22 +7678,22 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C217" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D217" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E217" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F217" s="2">
         <v>780</v>
       </c>
       <c r="G217" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7700,22 +7701,22 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C218" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D218" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E218" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F218" s="2">
         <v>780</v>
       </c>
       <c r="G218" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -7723,16 +7724,16 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
+        <v>238</v>
+      </c>
+      <c r="C219" t="s">
         <v>239</v>
       </c>
-      <c r="C219" t="s">
-        <v>240</v>
-      </c>
       <c r="D219" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E219" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F219" s="2">
         <v>756</v>
@@ -7743,22 +7744,22 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C220" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D220" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E220" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F220" s="2">
         <v>674</v>
       </c>
       <c r="G220" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -7766,16 +7767,16 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
+        <v>241</v>
+      </c>
+      <c r="C221" t="s">
         <v>242</v>
       </c>
-      <c r="C221" t="s">
-        <v>243</v>
-      </c>
       <c r="D221" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E221" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F221" s="2">
         <v>658</v>
@@ -7786,22 +7787,22 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
+        <v>243</v>
+      </c>
+      <c r="C222" t="s">
         <v>244</v>
       </c>
-      <c r="C222" t="s">
-        <v>245</v>
-      </c>
       <c r="D222" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E222" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F222" s="2">
         <v>586</v>
       </c>
       <c r="G222" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -7809,16 +7810,16 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
+        <v>245</v>
+      </c>
+      <c r="C223" t="s">
         <v>246</v>
       </c>
-      <c r="C223" t="s">
-        <v>247</v>
-      </c>
       <c r="D223" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E223" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F223" s="2">
         <v>429</v>
@@ -7829,22 +7830,22 @@
         <v>18</v>
       </c>
       <c r="B224" t="s">
+        <v>247</v>
+      </c>
+      <c r="C224" t="s">
         <v>248</v>
       </c>
-      <c r="C224" t="s">
-        <v>249</v>
-      </c>
       <c r="D224" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E224" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F224" s="2">
         <v>401</v>
       </c>
       <c r="G224" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -7852,22 +7853,22 @@
         <v>18</v>
       </c>
       <c r="B225" t="s">
+        <v>249</v>
+      </c>
+      <c r="C225" t="s">
         <v>250</v>
       </c>
-      <c r="C225" t="s">
-        <v>251</v>
-      </c>
       <c r="D225" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E225" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F225" s="2">
         <v>401</v>
       </c>
       <c r="G225" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -7875,22 +7876,22 @@
         <v>18</v>
       </c>
       <c r="B226" t="s">
+        <v>251</v>
+      </c>
+      <c r="C226" t="s">
         <v>252</v>
       </c>
-      <c r="C226" t="s">
-        <v>253</v>
-      </c>
       <c r="D226" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E226" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F226" s="2">
         <v>401</v>
       </c>
       <c r="G226" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -7898,16 +7899,16 @@
         <v>18</v>
       </c>
       <c r="B227" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C227" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D227" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E227" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F227" s="2">
         <v>390</v>
@@ -7918,22 +7919,22 @@
         <v>18</v>
       </c>
       <c r="B228" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C228" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D228" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E228" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F228" s="2">
         <v>380</v>
       </c>
       <c r="G228" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -7941,22 +7942,22 @@
         <v>18</v>
       </c>
       <c r="B229" t="s">
+        <v>255</v>
+      </c>
+      <c r="C229" t="s">
         <v>256</v>
       </c>
-      <c r="C229" t="s">
-        <v>257</v>
-      </c>
       <c r="D229" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E229" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F229" s="2">
         <v>364</v>
       </c>
       <c r="G229" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -7964,22 +7965,22 @@
         <v>18</v>
       </c>
       <c r="B230" t="s">
+        <v>257</v>
+      </c>
+      <c r="C230" t="s">
         <v>258</v>
       </c>
-      <c r="C230" t="s">
-        <v>259</v>
-      </c>
       <c r="D230" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E230" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F230" s="2">
         <v>344</v>
       </c>
       <c r="G230" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -7987,22 +7988,22 @@
         <v>18</v>
       </c>
       <c r="B231" t="s">
+        <v>259</v>
+      </c>
+      <c r="C231" t="s">
         <v>260</v>
       </c>
-      <c r="C231" t="s">
-        <v>261</v>
-      </c>
       <c r="D231" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E231" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F231" s="2">
         <v>344</v>
       </c>
       <c r="G231" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8010,22 +8011,22 @@
         <v>18</v>
       </c>
       <c r="B232" t="s">
+        <v>261</v>
+      </c>
+      <c r="C232" t="s">
         <v>262</v>
       </c>
-      <c r="C232" t="s">
-        <v>263</v>
-      </c>
       <c r="D232" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E232" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F232" s="2">
         <v>344</v>
       </c>
       <c r="G232" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8033,16 +8034,16 @@
         <v>18</v>
       </c>
       <c r="B233" t="s">
+        <v>263</v>
+      </c>
+      <c r="C233" t="s">
         <v>264</v>
       </c>
-      <c r="C233" t="s">
-        <v>265</v>
-      </c>
       <c r="D233" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E233" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F233" s="2">
         <v>260</v>
@@ -8053,22 +8054,22 @@
         <v>18</v>
       </c>
       <c r="B234" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C234" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D234" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E234" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F234" s="2">
         <v>195</v>
       </c>
       <c r="G234" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8076,22 +8077,22 @@
         <v>18</v>
       </c>
       <c r="B235" t="s">
+        <v>266</v>
+      </c>
+      <c r="C235" t="s">
         <v>267</v>
       </c>
-      <c r="C235" t="s">
-        <v>268</v>
-      </c>
       <c r="D235" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E235" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F235" s="2">
         <v>182</v>
       </c>
       <c r="G235" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8099,16 +8100,16 @@
         <v>18</v>
       </c>
       <c r="B236" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C236" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D236" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E236" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F236" s="2">
         <v>156</v>
@@ -8119,16 +8120,16 @@
         <v>18</v>
       </c>
       <c r="B237" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C237" t="s">
         <v>20</v>
       </c>
       <c r="D237" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E237" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F237" s="2">
         <v>55</v>
@@ -8139,16 +8140,16 @@
         <v>18</v>
       </c>
       <c r="B238" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C238" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D238" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E238" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F238" s="2">
         <v>9511</v>
@@ -8159,22 +8160,22 @@
         <v>18</v>
       </c>
       <c r="B239" t="s">
+        <v>270</v>
+      </c>
+      <c r="C239" t="s">
         <v>271</v>
       </c>
-      <c r="C239" t="s">
-        <v>272</v>
-      </c>
       <c r="D239" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E239" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F239" s="2">
         <v>1452</v>
       </c>
       <c r="G239" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -8182,16 +8183,16 @@
         <v>18</v>
       </c>
       <c r="B240" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C240" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D240" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E240" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F240" s="2">
         <v>1010</v>
@@ -8202,16 +8203,16 @@
         <v>18</v>
       </c>
       <c r="B241" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C241" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D241" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E241" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F241" s="2">
         <v>1007</v>
@@ -8222,16 +8223,16 @@
         <v>18</v>
       </c>
       <c r="B242" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C242" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D242" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E242" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F242" s="2">
         <v>932</v>
@@ -8242,16 +8243,16 @@
         <v>18</v>
       </c>
       <c r="B243" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C243" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D243" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E243" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F243" s="2">
         <v>863</v>
@@ -8262,22 +8263,22 @@
         <v>18</v>
       </c>
       <c r="B244" t="s">
+        <v>279</v>
+      </c>
+      <c r="C244" t="s">
         <v>280</v>
       </c>
-      <c r="C244" t="s">
-        <v>281</v>
-      </c>
       <c r="D244" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E244" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F244" s="2">
         <v>832</v>
       </c>
       <c r="G244" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -8285,22 +8286,22 @@
         <v>18</v>
       </c>
       <c r="B245" t="s">
+        <v>281</v>
+      </c>
+      <c r="C245" t="s">
         <v>282</v>
       </c>
-      <c r="C245" t="s">
-        <v>283</v>
-      </c>
       <c r="D245" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E245" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F245" s="2">
         <v>832</v>
       </c>
       <c r="G245" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -8308,22 +8309,22 @@
         <v>18</v>
       </c>
       <c r="B246" t="s">
+        <v>283</v>
+      </c>
+      <c r="C246" t="s">
         <v>284</v>
       </c>
-      <c r="C246" t="s">
-        <v>285</v>
-      </c>
       <c r="D246" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E246" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F246" s="2">
         <v>777</v>
       </c>
       <c r="G246" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -8331,22 +8332,22 @@
         <v>18</v>
       </c>
       <c r="B247" t="s">
+        <v>285</v>
+      </c>
+      <c r="C247" t="s">
         <v>286</v>
       </c>
-      <c r="C247" t="s">
-        <v>287</v>
-      </c>
       <c r="D247" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F247" s="2">
         <v>755</v>
       </c>
       <c r="G247" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -8354,22 +8355,22 @@
         <v>18</v>
       </c>
       <c r="B248" t="s">
+        <v>287</v>
+      </c>
+      <c r="C248" t="s">
         <v>288</v>
       </c>
-      <c r="C248" t="s">
-        <v>289</v>
-      </c>
       <c r="D248" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E248" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F248" s="2">
         <v>740</v>
       </c>
       <c r="G248" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -8377,22 +8378,22 @@
         <v>18</v>
       </c>
       <c r="B249" t="s">
+        <v>289</v>
+      </c>
+      <c r="C249" t="s">
         <v>290</v>
       </c>
-      <c r="C249" t="s">
-        <v>291</v>
-      </c>
       <c r="D249" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E249" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F249" s="2">
         <v>647</v>
       </c>
       <c r="G249" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -8400,22 +8401,22 @@
         <v>18</v>
       </c>
       <c r="B250" t="s">
+        <v>291</v>
+      </c>
+      <c r="C250" t="s">
         <v>292</v>
       </c>
-      <c r="C250" t="s">
-        <v>293</v>
-      </c>
       <c r="D250" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E250" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F250" s="2">
         <v>647</v>
       </c>
       <c r="G250" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -8423,22 +8424,22 @@
         <v>18</v>
       </c>
       <c r="B251" t="s">
+        <v>293</v>
+      </c>
+      <c r="C251" t="s">
         <v>294</v>
       </c>
-      <c r="C251" t="s">
-        <v>295</v>
-      </c>
       <c r="D251" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E251" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F251" s="2">
         <v>642</v>
       </c>
       <c r="G251" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -8446,22 +8447,22 @@
         <v>18</v>
       </c>
       <c r="B252" t="s">
+        <v>295</v>
+      </c>
+      <c r="C252" t="s">
         <v>296</v>
       </c>
-      <c r="C252" t="s">
-        <v>297</v>
-      </c>
       <c r="D252" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E252" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F252" s="2">
         <v>632</v>
       </c>
       <c r="G252" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -8469,22 +8470,22 @@
         <v>18</v>
       </c>
       <c r="B253" t="s">
+        <v>297</v>
+      </c>
+      <c r="C253" t="s">
         <v>298</v>
       </c>
-      <c r="C253" t="s">
-        <v>299</v>
-      </c>
       <c r="D253" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E253" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F253" s="2">
         <v>601</v>
       </c>
       <c r="G253" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -8492,22 +8493,22 @@
         <v>18</v>
       </c>
       <c r="B254" t="s">
+        <v>299</v>
+      </c>
+      <c r="C254" t="s">
         <v>300</v>
       </c>
-      <c r="C254" t="s">
-        <v>301</v>
-      </c>
       <c r="D254" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E254" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F254" s="2">
         <v>586</v>
       </c>
       <c r="G254" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -8515,16 +8516,16 @@
         <v>18</v>
       </c>
       <c r="B255" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C255" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D255" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E255" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F255" s="2">
         <v>260</v>
@@ -8535,16 +8536,16 @@
         <v>18</v>
       </c>
       <c r="B256" t="s">
+        <v>301</v>
+      </c>
+      <c r="C256" t="s">
         <v>302</v>
       </c>
-      <c r="C256" t="s">
-        <v>303</v>
-      </c>
       <c r="D256" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E256" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F256" s="2">
         <v>260</v>
@@ -8555,16 +8556,16 @@
         <v>18</v>
       </c>
       <c r="B257" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C257" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D257" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E257" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F257" s="2">
         <v>228</v>
@@ -8575,16 +8576,16 @@
         <v>18</v>
       </c>
       <c r="B258" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C258" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D258" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E258" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F258" s="2">
         <v>221</v>
@@ -8595,16 +8596,16 @@
         <v>18</v>
       </c>
       <c r="B259" t="s">
+        <v>304</v>
+      </c>
+      <c r="C259" t="s">
         <v>305</v>
       </c>
-      <c r="C259" t="s">
-        <v>306</v>
-      </c>
       <c r="D259" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E259" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F259" s="2">
         <v>182</v>
@@ -8615,16 +8616,16 @@
         <v>18</v>
       </c>
       <c r="B260" t="s">
+        <v>306</v>
+      </c>
+      <c r="C260" t="s">
         <v>307</v>
       </c>
-      <c r="C260" t="s">
-        <v>308</v>
-      </c>
       <c r="D260" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E260" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F260" s="2">
         <v>182</v>
@@ -8635,16 +8636,16 @@
         <v>18</v>
       </c>
       <c r="B261" t="s">
+        <v>308</v>
+      </c>
+      <c r="C261" t="s">
         <v>309</v>
       </c>
-      <c r="C261" t="s">
-        <v>310</v>
-      </c>
       <c r="D261" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E261" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F261" s="2">
         <v>180</v>
@@ -8655,16 +8656,16 @@
         <v>18</v>
       </c>
       <c r="B262" t="s">
+        <v>310</v>
+      </c>
+      <c r="C262" t="s">
         <v>311</v>
       </c>
-      <c r="C262" t="s">
-        <v>312</v>
-      </c>
       <c r="D262" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E262" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F262" s="2">
         <v>176</v>
@@ -8675,16 +8676,16 @@
         <v>18</v>
       </c>
       <c r="B263" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C263" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D263" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E263" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F263" s="2">
         <v>163</v>
@@ -8695,16 +8696,16 @@
         <v>18</v>
       </c>
       <c r="B264" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C264" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D264" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E264" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F264" s="2">
         <v>3274</v>
@@ -8715,16 +8716,16 @@
         <v>18</v>
       </c>
       <c r="B265" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C265" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D265" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E265" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F265" s="2">
         <v>1233</v>
@@ -8735,16 +8736,16 @@
         <v>18</v>
       </c>
       <c r="B266" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C266" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D266" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E266" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F266" s="2">
         <v>662</v>
@@ -8755,16 +8756,16 @@
         <v>18</v>
       </c>
       <c r="B267" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C267" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D267" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E267" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F267" s="2">
         <v>130</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VSCode\Test\my-vue-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5428EE7C-88B2-41C9-BA36-F57937449F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFEDE22-7658-4A0B-82F4-837D24EB94F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8655" yWindow="4755" windowWidth="25425" windowHeight="12285" xr2:uid="{BFCE4DB1-B638-4533-A727-1E11ECBF49A7}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{BFCE4DB1-B638-4533-A727-1E11ECBF49A7}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,6 @@
     <t>Category</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
     <t>Effect</t>
   </si>
   <si>
@@ -2056,9 +2053,6 @@
     <t>糯米粉、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜、櫻桃-藍莓-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
   </si>
   <si>
-    <t>巧克力、麵包-白麵包-長棍麵包-佛卡夏、蘋果-葡萄-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
-  </si>
-  <si>
     <t>蘋果、奶油-香草奶油-頂級奶油</t>
   </si>
   <si>
@@ -2087,9 +2081,6 @@
   </si>
   <si>
     <t>麵粉、蛋-烏骨雞蛋、薄荷-洋甘菊-薰衣草</t>
-  </si>
-  <si>
-    <t>麵粉、頂級蛋-頂級烏骨雞蛋、頂級水牛奶、起司-香草起司-頂級起司</t>
   </si>
   <si>
     <t>麵粉、頂級蛋-頂級烏骨雞蛋、頂級牛奶-頂級水牛奶、巧克力</t>
@@ -2402,6 +2393,18 @@
   </si>
   <si>
     <t>義式番茄起司沙拉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>麵粉、頂級蛋-頂級烏骨雞蛋、頂級水牛奶、起司-香草起司-頂級起司</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>巧克力、麵包-白麵包-長棍麵包-佛卡夏、蘋果-葡萄-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2412,7 +2415,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2567,6 +2570,15 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -2870,7 +2882,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2997,8 +3009,11 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3008,8 +3023,10 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - 輔色1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 輔色2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 輔色3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -3035,6 +3052,7 @@
     <cellStyle name="計算方式" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="連結的儲存格" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="備註" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="超連結" xfId="42" builtinId="8"/>
     <cellStyle name="說明文字" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="輔色1" xfId="18" builtinId="29" customBuiltin="1"/>
     <cellStyle name="輔色2" xfId="22" builtinId="33" customBuiltin="1"/>
@@ -3363,7 +3381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE04E7DD-F155-4289-B904-E214A34C0638}">
-  <dimension ref="A1:G267"/>
+  <dimension ref="A1:H267"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.375" bestFit="1" customWidth="1"/>
@@ -3372,424 +3390,427 @@
     <col min="5" max="5" width="36.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="69.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>774</v>
+      </c>
+      <c r="C1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>323</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>709</v>
+      </c>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
       </c>
       <c r="F2" s="2">
         <v>1859</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
       </c>
       <c r="F3" s="2">
         <v>1309</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D4" t="s">
         <v>319</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>320</v>
-      </c>
-      <c r="E4" t="s">
-        <v>321</v>
       </c>
       <c r="F4" s="2">
         <v>909</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D5" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="E5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F5" s="2">
         <v>598</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D6" t="s">
         <v>324</v>
       </c>
-      <c r="D6" t="s">
-        <v>325</v>
-      </c>
       <c r="E6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F6" s="2">
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>327</v>
+      </c>
+      <c r="C7" t="s">
         <v>328</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>329</v>
       </c>
-      <c r="D7" t="s">
-        <v>330</v>
-      </c>
       <c r="E7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F7" s="2">
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D8" t="s">
         <v>333</v>
       </c>
-      <c r="D8" t="s">
-        <v>334</v>
-      </c>
       <c r="E8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F8" s="2">
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F9" s="2">
         <v>126</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F10" s="2">
         <v>2429</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F11" s="2">
         <v>1197</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F12" s="2">
         <v>677</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
         <v>24</v>
       </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
       <c r="D13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F13" s="2">
         <v>325</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D14" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E14" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F14" s="2">
         <v>1728</v>
       </c>
       <c r="G14" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D15" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F15" s="2">
         <v>1024</v>
       </c>
       <c r="G15" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D16" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F16" s="2">
         <v>770</v>
       </c>
       <c r="G16" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C17" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F17" s="2">
         <v>260</v>
       </c>
       <c r="G17" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D18" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E18" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F18" s="2">
         <v>1815</v>
       </c>
       <c r="G18" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D19" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F19" s="2">
         <v>1320</v>
       </c>
       <c r="G19" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D20" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F20" s="2">
         <v>709</v>
@@ -3797,19 +3818,19 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D21" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E21" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F21" s="2">
         <v>490</v>
@@ -3817,65 +3838,65 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D22" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F22" s="2">
         <v>137</v>
       </c>
       <c r="G22" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D23" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F23" s="2">
         <v>117</v>
       </c>
       <c r="G23" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C24" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D24" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F24" s="2">
         <v>10098</v>
@@ -3883,42 +3904,42 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D25" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E25" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F25" s="2">
         <v>2592</v>
       </c>
       <c r="G25" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D26" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F26" s="2">
         <v>1892</v>
@@ -3926,19 +3947,19 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D27" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F27" s="2">
         <v>1584</v>
@@ -3946,19 +3967,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D28" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E28" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F28" s="2">
         <v>1530</v>
@@ -3966,19 +3987,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D29" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F29" s="2">
         <v>1377</v>
@@ -3986,19 +4007,19 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D30" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="E30" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F30" s="2">
         <v>1353</v>
@@ -4006,19 +4027,19 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D31" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E31" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F31" s="2">
         <v>1276</v>
@@ -4026,19 +4047,19 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D32" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E32" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F32" s="2">
         <v>1213</v>
@@ -4046,19 +4067,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D33" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E33" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F33" s="2">
         <v>1155</v>
@@ -4066,19 +4087,19 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C34" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D34" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E34" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F34" s="2">
         <v>1122</v>
@@ -4086,19 +4107,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D35" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E35" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F35" s="2">
         <v>1056</v>
@@ -4106,42 +4127,42 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D36" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E36" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F36" s="2">
         <v>911</v>
       </c>
       <c r="G36" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D37" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E37" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F37" s="2">
         <v>882</v>
@@ -4149,19 +4170,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D38" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E38" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F38" s="2">
         <v>843</v>
@@ -4169,19 +4190,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D39" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E39" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F39" s="2">
         <v>824</v>
@@ -4189,19 +4210,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D40" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E40" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F40" s="2">
         <v>809</v>
@@ -4209,19 +4230,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D41" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E41" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F41" s="2">
         <v>801</v>
@@ -4229,19 +4250,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D42" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E42" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F42" s="2">
         <v>747</v>
@@ -4249,19 +4270,19 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D43" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E43" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F43" s="2">
         <v>743</v>
@@ -4269,19 +4290,19 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C44" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D44" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E44" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F44" s="2">
         <v>677</v>
@@ -4289,19 +4310,19 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C45" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D45" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E45" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F45" s="2">
         <v>662</v>
@@ -4309,19 +4330,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D46" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E46" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F46" s="2">
         <v>632</v>
@@ -4329,19 +4350,19 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D47" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E47" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F47" s="2">
         <v>609</v>
@@ -4349,19 +4370,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" t="s">
         <v>59</v>
       </c>
-      <c r="C48" t="s">
-        <v>60</v>
-      </c>
       <c r="D48" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E48" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F48" s="2">
         <v>602</v>
@@ -4369,19 +4390,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C49" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D49" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E49" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F49" s="2">
         <v>563</v>
@@ -4389,19 +4410,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D50" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F50" s="2">
         <v>458</v>
@@ -4409,19 +4430,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D51" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E51" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F51" s="2">
         <v>429</v>
@@ -4429,19 +4450,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D52" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E52" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F52" s="2">
         <v>403</v>
@@ -4449,19 +4470,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C53" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D53" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E53" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F53" s="2">
         <v>396</v>
@@ -4469,19 +4490,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D54" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E54" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F54" s="2">
         <v>267</v>
@@ -4489,19 +4510,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C55" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D55" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E55" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F55" s="2">
         <v>246</v>
@@ -4509,19 +4530,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C56" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D56" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E56" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F56" s="2">
         <v>234</v>
@@ -4529,19 +4550,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C57" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D57" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E57" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F57" s="2">
         <v>205</v>
@@ -4549,19 +4570,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D58" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E58" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F58" s="2">
         <v>195</v>
@@ -4569,19 +4590,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C59" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E59" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F59" s="2">
         <v>117</v>
@@ -4589,19 +4610,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" t="s">
         <v>71</v>
       </c>
-      <c r="C60" t="s">
-        <v>72</v>
-      </c>
       <c r="D60" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E60" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F60" s="2">
         <v>111</v>
@@ -4609,19 +4630,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C61" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D61" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F61" s="2">
         <v>924</v>
@@ -4629,19 +4650,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C62" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D62" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E62" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F62" s="2">
         <v>195</v>
@@ -4649,19 +4670,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C63" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D63" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E63" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F63" s="2">
         <v>195</v>
@@ -4669,19 +4690,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C64" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E64" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F64" s="2">
         <v>1509</v>
@@ -4689,19 +4710,19 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D65" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E65" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F65" s="2">
         <v>886</v>
@@ -4709,19 +4730,19 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C66" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D66" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E66" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F66" s="2">
         <v>1920</v>
@@ -4729,19 +4750,19 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C67" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D67" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E67" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F67" s="2">
         <v>1844</v>
@@ -4749,19 +4770,19 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D68" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E68" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F68" s="2">
         <v>1320</v>
@@ -4769,19 +4790,19 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C69" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D69" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E69" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F69" s="2">
         <v>1098</v>
@@ -4789,42 +4810,42 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C70" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D70" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E70" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F70" s="2">
         <v>770</v>
       </c>
       <c r="G70" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C71" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D71" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E71" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F71" s="2">
         <v>709</v>
@@ -4832,19 +4853,19 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C72" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D72" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E72" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F72" s="2">
         <v>647</v>
@@ -4852,42 +4873,42 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C73" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D73" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="E73" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F73" s="2">
         <v>508</v>
       </c>
       <c r="G73" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C74" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D74" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E74" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F74" s="2">
         <v>355</v>
@@ -4895,19 +4916,19 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C75" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D75" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E75" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F75" s="2">
         <v>301</v>
@@ -4915,19 +4936,19 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C76" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D76" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E76" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F76" s="2">
         <v>202</v>
@@ -4935,16 +4956,16 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D77" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F77" s="2">
         <v>195</v>
@@ -4952,16 +4973,16 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B78" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" t="s">
         <v>89</v>
       </c>
-      <c r="C78" t="s">
-        <v>90</v>
-      </c>
       <c r="D78" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F78" s="2">
         <v>182</v>
@@ -4969,16 +4990,16 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B79" t="s">
+        <v>90</v>
+      </c>
+      <c r="C79" t="s">
         <v>91</v>
       </c>
-      <c r="C79" t="s">
-        <v>92</v>
-      </c>
       <c r="D79" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F79" s="2">
         <v>91</v>
@@ -4986,16 +5007,16 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B80" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C80" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D80" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F80" s="2">
         <v>12353</v>
@@ -5003,16 +5024,16 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C81" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D81" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F81" s="2">
         <v>7508</v>
@@ -5020,16 +5041,16 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B82" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C82" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D82" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F82" s="2">
         <v>6957</v>
@@ -5037,16 +5058,16 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B83" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C83" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D83" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F83" s="2">
         <v>3724</v>
@@ -5054,16 +5075,16 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C84" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D84" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F84" s="2">
         <v>2784</v>
@@ -5071,56 +5092,56 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C85" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D85" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F85" s="2">
         <v>2641</v>
       </c>
       <c r="G85" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C86" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D86" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F86" s="2">
         <v>2640</v>
       </c>
       <c r="G86" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C87" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D87" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F87" s="2">
         <v>2592</v>
@@ -5128,56 +5149,56 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C88" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D88" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F88" s="2">
         <v>2487</v>
       </c>
       <c r="G88" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C89" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D89" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F89" s="2">
         <v>2324</v>
       </c>
       <c r="G89" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B90" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C90" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D90" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F90" s="2">
         <v>2295</v>
@@ -5185,36 +5206,36 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B91" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C91" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D91" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F91" s="2">
         <v>2188</v>
       </c>
       <c r="G91" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C92" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D92" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F92" s="2">
         <v>2160</v>
@@ -5222,16 +5243,16 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B93" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C93" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D93" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F93" s="2">
         <v>2089</v>
@@ -5239,16 +5260,16 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B94" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C94" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D94" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F94" s="2">
         <v>1901</v>
@@ -5256,16 +5277,16 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C95" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D95" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F95" s="2">
         <v>1817</v>
@@ -5273,16 +5294,16 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B96" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C96" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D96" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F96" s="2">
         <v>1760</v>
@@ -5290,16 +5311,16 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C97" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D97" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F97" s="2">
         <v>1568</v>
@@ -5307,36 +5328,36 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C98" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="D98" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F98" s="2">
         <v>1566</v>
       </c>
       <c r="G98" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B99" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C99" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D99" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F99" s="2">
         <v>1552</v>
@@ -5344,16 +5365,16 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B100" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C100" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D100" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F100" s="2">
         <v>1469</v>
@@ -5361,16 +5382,16 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B101" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C101" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D101" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F101" s="2">
         <v>1452</v>
@@ -5378,16 +5399,16 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B102" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C102" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D102" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F102" s="2">
         <v>1449</v>
@@ -5395,16 +5416,16 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B103" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C103" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D103" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F103" s="2">
         <v>1437</v>
@@ -5412,16 +5433,16 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C104" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D104" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F104" s="2">
         <v>1437</v>
@@ -5429,16 +5450,16 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C105" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D105" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F105" s="2">
         <v>1424</v>
@@ -5446,16 +5467,16 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C106" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D106" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F106" s="2">
         <v>1410</v>
@@ -5463,16 +5484,16 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="C107" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="D107" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F107" s="2">
         <v>1410</v>
@@ -5480,16 +5501,16 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C108" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="D108" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F108" s="2">
         <v>1388</v>
@@ -5497,16 +5518,16 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C109" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D109" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F109" s="2">
         <v>1339</v>
@@ -5514,16 +5535,16 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C110" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D110" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F110" s="2">
         <v>1334</v>
@@ -5531,16 +5552,16 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C111" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D111" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F111" s="2">
         <v>1325</v>
@@ -5548,16 +5569,16 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C112" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D112" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F112" s="2">
         <v>1316</v>
@@ -5565,16 +5586,16 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C113" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D113" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F113" s="2">
         <v>1304</v>
@@ -5582,16 +5603,16 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C114" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D114" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F114" s="2">
         <v>1271</v>
@@ -5599,16 +5620,16 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C115" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="D115" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F115" s="2">
         <v>1262</v>
@@ -5616,16 +5637,16 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B116" t="s">
+        <v>120</v>
+      </c>
+      <c r="C116" t="s">
         <v>121</v>
       </c>
-      <c r="C116" t="s">
-        <v>122</v>
-      </c>
       <c r="D116" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F116" s="2">
         <v>1200</v>
@@ -5633,16 +5654,16 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C117" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D117" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F117" s="2">
         <v>1188</v>
@@ -5650,16 +5671,16 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C118" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D118" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F118" s="2">
         <v>1182</v>
@@ -5667,16 +5688,16 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C119" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D119" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F119" s="2">
         <v>1172</v>
@@ -5684,16 +5705,16 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C120" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D120" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F120" s="2">
         <v>1152</v>
@@ -5701,16 +5722,16 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D121" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F121" s="2">
         <v>1151</v>
@@ -5718,36 +5739,36 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D122" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F122" s="2">
         <v>1147</v>
       </c>
       <c r="G122" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D123" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F123" s="2">
         <v>1142</v>
@@ -5755,36 +5776,36 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D124" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F124" s="2">
         <v>1131</v>
       </c>
       <c r="G124" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D125" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F125" s="2">
         <v>1073</v>
@@ -5792,16 +5813,16 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="D126" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F126" s="2">
         <v>1073</v>
@@ -5809,16 +5830,16 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D127" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F127" s="2">
         <v>1052</v>
@@ -5826,16 +5847,16 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D128" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F128" s="2">
         <v>937</v>
@@ -5843,16 +5864,16 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C129" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="D129" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F129" s="2">
         <v>911</v>
@@ -5860,16 +5881,16 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C130" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D130" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F130" s="2">
         <v>911</v>
@@ -5877,16 +5898,16 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C131" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D131" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F131" s="2">
         <v>874</v>
@@ -5894,16 +5915,16 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C132" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D132" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F132" s="2">
         <v>867</v>
@@ -5911,16 +5932,16 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C133" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D133" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F133" s="2">
         <v>838</v>
@@ -5928,16 +5949,16 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D134" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F134" s="2">
         <v>837</v>
@@ -5945,36 +5966,36 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D135" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F135" s="2">
         <v>835</v>
       </c>
       <c r="G135" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C136" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D136" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F136" s="2">
         <v>817</v>
@@ -5982,16 +6003,16 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C137" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D137" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F137" s="2">
         <v>809</v>
@@ -5999,16 +6020,16 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C138" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D138" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F138" s="2">
         <v>809</v>
@@ -6016,36 +6037,36 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C139" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D139" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F139" s="2">
         <v>801</v>
       </c>
       <c r="G139" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D140" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F140" s="2">
         <v>735</v>
@@ -6053,16 +6074,16 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C141" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D141" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F141" s="2">
         <v>721</v>
@@ -6070,16 +6091,16 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C142" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D142" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F142" s="2">
         <v>664</v>
@@ -6087,16 +6108,16 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C143" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D143" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F143" s="2">
         <v>657</v>
@@ -6104,16 +6125,16 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C144" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D144" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F144" s="2">
         <v>650</v>
@@ -6121,56 +6142,56 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C145" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D145" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F145" s="2">
         <v>647</v>
       </c>
       <c r="G145" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C146" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D146" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F146" s="2">
         <v>647</v>
       </c>
       <c r="G146" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C147" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D147" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F147" s="2">
         <v>647</v>
@@ -6178,16 +6199,16 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C148" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D148" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F148" s="2">
         <v>616</v>
@@ -6195,16 +6216,16 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C149" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D149" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F149" s="2">
         <v>604</v>
@@ -6212,36 +6233,36 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C150" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D150" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F150" s="2">
         <v>544</v>
       </c>
       <c r="G150" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C151" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D151" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F151" s="2">
         <v>451</v>
@@ -6249,16 +6270,16 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C152" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D152" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F152" s="2">
         <v>444</v>
@@ -6266,16 +6287,16 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C153" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D153" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F153" s="2">
         <v>375</v>
@@ -6283,16 +6304,16 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C154" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D154" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F154" s="2">
         <v>370</v>
@@ -6300,16 +6321,16 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D155" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F155" s="2">
         <v>342</v>
@@ -6317,16 +6338,16 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D156" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="F156" s="2">
         <v>329</v>
@@ -6334,16 +6355,16 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C157" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D157" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F157" s="2">
         <v>328</v>
@@ -6351,16 +6372,16 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C158" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D158" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F158" s="2">
         <v>248</v>
@@ -6368,16 +6389,16 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C159" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D159" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F159" s="2">
         <v>195</v>
@@ -6385,962 +6406,962 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C160" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D160" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E160" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F160" s="2">
         <v>3258</v>
       </c>
       <c r="G160" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C161" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D161" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E161" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F161" s="2">
         <v>6192</v>
       </c>
       <c r="G161" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D162" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E162" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F162" s="2">
         <v>3130</v>
       </c>
       <c r="G162" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D163" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E163" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F163" s="2">
         <v>1602</v>
       </c>
       <c r="G163" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D164" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="E164" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F164" s="2">
         <v>1422</v>
       </c>
       <c r="G164" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D165" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E165" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F165" s="2">
         <v>1404</v>
       </c>
       <c r="G165" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D166" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E166" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F166" s="2">
         <v>1377</v>
       </c>
       <c r="G166" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D167" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E167" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F167" s="2">
         <v>1368</v>
       </c>
       <c r="G167" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D168" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E168" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F168" s="2">
         <v>1332</v>
       </c>
       <c r="G168" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D169" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E169" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F169" s="2">
         <v>1332</v>
       </c>
       <c r="G169" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D170" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E170" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F170" s="2">
         <v>1242</v>
       </c>
       <c r="G170" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D171" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E171" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F171" s="2">
         <v>1242</v>
       </c>
       <c r="G171" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D172" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E172" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F172" s="2">
         <v>1206</v>
       </c>
       <c r="G172" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D173" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E173" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F173" s="2">
         <v>1152</v>
       </c>
       <c r="G173" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D174" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E174" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F174" s="2">
         <v>1089</v>
       </c>
       <c r="G174" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C175" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D175" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E175" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F175" s="2">
         <v>932</v>
       </c>
       <c r="G175" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C176" t="s">
-        <v>670</v>
+        <v>776</v>
       </c>
       <c r="D176" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E176" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F176" s="2">
         <v>924</v>
       </c>
       <c r="G176" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B177" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C177" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D177" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E177" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F177" s="2">
         <v>838</v>
       </c>
       <c r="G177" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B178" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C178" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D178" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E178" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F178" s="2">
         <v>832</v>
       </c>
       <c r="G178" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B179" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C179" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D179" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E179" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F179" s="2">
         <v>801</v>
       </c>
       <c r="G179" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B180" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C180" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D180" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E180" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F180" s="2">
         <v>618</v>
       </c>
       <c r="G180" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B181" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C181" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D181" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E181" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F181" s="2">
         <v>601</v>
       </c>
       <c r="G181" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B182" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C182" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D182" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E182" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F182" s="2">
         <v>601</v>
       </c>
       <c r="G182" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B183" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C183" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D183" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E183" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F183" s="2">
         <v>588</v>
       </c>
       <c r="G183" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B184" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C184" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D184" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E184" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F184" s="2">
         <v>544</v>
       </c>
       <c r="G184" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B185" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C185" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D185" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E185" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F185" s="2">
         <v>524</v>
       </c>
       <c r="G185" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B186" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C186" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D186" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E186" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F186" s="2">
         <v>501</v>
       </c>
       <c r="G186" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C187" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D187" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E187" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F187" s="2">
         <v>415</v>
       </c>
       <c r="G187" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C188" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D188" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E188" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F188" s="2">
         <v>390</v>
       </c>
       <c r="G188" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B189" t="s">
+        <v>195</v>
+      </c>
+      <c r="C189" t="s">
         <v>196</v>
       </c>
-      <c r="C189" t="s">
-        <v>197</v>
-      </c>
       <c r="D189" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="E189" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F189" s="2">
         <v>390</v>
       </c>
       <c r="G189" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C190" t="s">
-        <v>681</v>
+        <v>775</v>
       </c>
       <c r="D190" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E190" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F190" s="2">
         <v>2746</v>
       </c>
       <c r="G190" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C191" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D191" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E191" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F191" s="2">
         <v>2322</v>
       </c>
       <c r="G191" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C192" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D192" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E192" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F192" s="2">
         <v>1458</v>
       </c>
       <c r="G192" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C193" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D193" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E193" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F193" s="2">
         <v>1350</v>
       </c>
       <c r="G193" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C194" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D194" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E194" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F194" s="2">
         <v>1242</v>
       </c>
       <c r="G194" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C195" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D195" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E195" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F195" s="2">
         <v>986</v>
       </c>
       <c r="G195" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C196" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D196" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E196" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F196" s="2">
         <v>832</v>
       </c>
       <c r="G196" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C197" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D197" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E197" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F197" s="2">
         <v>755</v>
       </c>
       <c r="G197" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C198" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D198" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E198" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F198" s="2">
         <v>735</v>
       </c>
       <c r="G198" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C199" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D199" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E199" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F199" s="2">
         <v>328</v>
       </c>
       <c r="G199" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C200" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D200" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E200" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F200" s="2">
         <v>328</v>
       </c>
       <c r="G200" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C201" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D201" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E201" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F201" s="2">
         <v>85</v>
@@ -7348,19 +7369,19 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B202" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C202" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D202" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E202" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F202" s="2">
         <v>325</v>
@@ -7368,19 +7389,19 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B203" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C203" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D203" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E203" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F203" s="2">
         <v>424</v>
@@ -7388,42 +7409,42 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B204" t="s">
+        <v>211</v>
+      </c>
+      <c r="C204" t="s">
         <v>212</v>
       </c>
-      <c r="C204" t="s">
-        <v>213</v>
-      </c>
       <c r="D204" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E204" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F204" s="2">
         <v>1287</v>
       </c>
       <c r="G204" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B205" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C205" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="D205" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E205" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F205" s="2">
         <v>1020</v>
@@ -7431,203 +7452,203 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B206" t="s">
+        <v>215</v>
+      </c>
+      <c r="C206" t="s">
         <v>216</v>
       </c>
-      <c r="C206" t="s">
-        <v>217</v>
-      </c>
       <c r="D206" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E206" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F206" s="2">
         <v>401</v>
       </c>
       <c r="G206" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B207" t="s">
+        <v>217</v>
+      </c>
+      <c r="C207" t="s">
         <v>218</v>
       </c>
-      <c r="C207" t="s">
-        <v>219</v>
-      </c>
       <c r="D207" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E207" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F207" s="2">
         <v>13031</v>
       </c>
       <c r="G207" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B208" t="s">
+        <v>219</v>
+      </c>
+      <c r="C208" t="s">
         <v>220</v>
       </c>
-      <c r="C208" t="s">
-        <v>221</v>
-      </c>
       <c r="D208" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E208" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F208" s="2">
         <v>2148</v>
       </c>
       <c r="G208" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B209" t="s">
+        <v>221</v>
+      </c>
+      <c r="C209" t="s">
         <v>222</v>
       </c>
-      <c r="C209" t="s">
-        <v>223</v>
-      </c>
       <c r="D209" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E209" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F209" s="2">
         <v>1901</v>
       </c>
       <c r="G209" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B210" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C210" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D210" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E210" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F210" s="2">
         <v>1850</v>
       </c>
       <c r="G210" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B211" t="s">
+        <v>224</v>
+      </c>
+      <c r="C211" t="s">
         <v>225</v>
       </c>
-      <c r="C211" t="s">
-        <v>226</v>
-      </c>
       <c r="D211" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E211" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F211" s="2">
         <v>1320</v>
       </c>
       <c r="G211" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B212" t="s">
+        <v>226</v>
+      </c>
+      <c r="C212" t="s">
         <v>227</v>
       </c>
-      <c r="C212" t="s">
-        <v>228</v>
-      </c>
       <c r="D212" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E212" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F212" s="2">
         <v>1287</v>
       </c>
       <c r="G212" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B213" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C213" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D213" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E213" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F213" s="2">
         <v>1194</v>
       </c>
       <c r="G213" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B214" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C214" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D214" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E214" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F214" s="2">
         <v>935</v>
@@ -7635,19 +7656,19 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B215" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C215" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D215" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E215" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F215" s="2">
         <v>855</v>
@@ -7655,19 +7676,19 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B216" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C216" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D216" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E216" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F216" s="2">
         <v>826</v>
@@ -7675,65 +7696,65 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B217" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C217" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D217" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E217" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F217" s="2">
         <v>780</v>
       </c>
       <c r="G217" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B218" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C218" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D218" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E218" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F218" s="2">
         <v>780</v>
       </c>
       <c r="G218" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B219" t="s">
+        <v>237</v>
+      </c>
+      <c r="C219" t="s">
         <v>238</v>
       </c>
-      <c r="C219" t="s">
-        <v>239</v>
-      </c>
       <c r="D219" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E219" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F219" s="2">
         <v>756</v>
@@ -7741,42 +7762,42 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B220" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C220" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D220" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E220" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F220" s="2">
         <v>674</v>
       </c>
       <c r="G220" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B221" t="s">
+        <v>240</v>
+      </c>
+      <c r="C221" t="s">
         <v>241</v>
       </c>
-      <c r="C221" t="s">
-        <v>242</v>
-      </c>
       <c r="D221" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E221" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F221" s="2">
         <v>658</v>
@@ -7784,42 +7805,42 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B222" t="s">
+        <v>242</v>
+      </c>
+      <c r="C222" t="s">
         <v>243</v>
       </c>
-      <c r="C222" t="s">
-        <v>244</v>
-      </c>
       <c r="D222" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E222" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F222" s="2">
         <v>586</v>
       </c>
       <c r="G222" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B223" t="s">
+        <v>244</v>
+      </c>
+      <c r="C223" t="s">
         <v>245</v>
       </c>
-      <c r="C223" t="s">
-        <v>246</v>
-      </c>
       <c r="D223" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E223" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F223" s="2">
         <v>429</v>
@@ -7827,88 +7848,88 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B224" t="s">
+        <v>246</v>
+      </c>
+      <c r="C224" t="s">
         <v>247</v>
       </c>
-      <c r="C224" t="s">
-        <v>248</v>
-      </c>
       <c r="D224" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E224" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F224" s="2">
         <v>401</v>
       </c>
       <c r="G224" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B225" t="s">
+        <v>248</v>
+      </c>
+      <c r="C225" t="s">
         <v>249</v>
       </c>
-      <c r="C225" t="s">
-        <v>250</v>
-      </c>
       <c r="D225" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E225" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F225" s="2">
         <v>401</v>
       </c>
       <c r="G225" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B226" t="s">
+        <v>250</v>
+      </c>
+      <c r="C226" t="s">
         <v>251</v>
       </c>
-      <c r="C226" t="s">
-        <v>252</v>
-      </c>
       <c r="D226" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E226" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F226" s="2">
         <v>401</v>
       </c>
       <c r="G226" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B227" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C227" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D227" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E227" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F227" s="2">
         <v>390</v>
@@ -7916,134 +7937,134 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B228" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C228" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D228" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E228" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F228" s="2">
         <v>380</v>
       </c>
       <c r="G228" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B229" t="s">
+        <v>254</v>
+      </c>
+      <c r="C229" t="s">
         <v>255</v>
       </c>
-      <c r="C229" t="s">
-        <v>256</v>
-      </c>
       <c r="D229" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E229" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F229" s="2">
         <v>364</v>
       </c>
       <c r="G229" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B230" t="s">
+        <v>256</v>
+      </c>
+      <c r="C230" t="s">
         <v>257</v>
       </c>
-      <c r="C230" t="s">
-        <v>258</v>
-      </c>
       <c r="D230" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E230" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F230" s="2">
         <v>344</v>
       </c>
       <c r="G230" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B231" t="s">
+        <v>258</v>
+      </c>
+      <c r="C231" t="s">
         <v>259</v>
       </c>
-      <c r="C231" t="s">
-        <v>260</v>
-      </c>
       <c r="D231" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E231" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F231" s="2">
         <v>344</v>
       </c>
       <c r="G231" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B232" t="s">
+        <v>260</v>
+      </c>
+      <c r="C232" t="s">
         <v>261</v>
       </c>
-      <c r="C232" t="s">
-        <v>262</v>
-      </c>
       <c r="D232" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E232" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F232" s="2">
         <v>344</v>
       </c>
       <c r="G232" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B233" t="s">
+        <v>262</v>
+      </c>
+      <c r="C233" t="s">
         <v>263</v>
       </c>
-      <c r="C233" t="s">
-        <v>264</v>
-      </c>
       <c r="D233" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E233" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F233" s="2">
         <v>260</v>
@@ -8051,65 +8072,65 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B234" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C234" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D234" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E234" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F234" s="2">
         <v>195</v>
       </c>
       <c r="G234" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B235" t="s">
+        <v>265</v>
+      </c>
+      <c r="C235" t="s">
         <v>266</v>
       </c>
-      <c r="C235" t="s">
-        <v>267</v>
-      </c>
       <c r="D235" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E235" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F235" s="2">
         <v>182</v>
       </c>
       <c r="G235" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B236" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C236" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D236" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E236" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F236" s="2">
         <v>156</v>
@@ -8117,19 +8138,19 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B237" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C237" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D237" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E237" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F237" s="2">
         <v>55</v>
@@ -8137,19 +8158,19 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B238" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C238" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D238" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E238" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F238" s="2">
         <v>9511</v>
@@ -8157,42 +8178,42 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B239" t="s">
+        <v>269</v>
+      </c>
+      <c r="C239" t="s">
         <v>270</v>
       </c>
-      <c r="C239" t="s">
-        <v>271</v>
-      </c>
       <c r="D239" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E239" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F239" s="2">
         <v>1452</v>
       </c>
       <c r="G239" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B240" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C240" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="D240" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E240" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F240" s="2">
         <v>1010</v>
@@ -8200,19 +8221,19 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B241" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C241" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D241" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E241" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F241" s="2">
         <v>1007</v>
@@ -8220,19 +8241,19 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B242" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C242" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D242" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E242" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F242" s="2">
         <v>932</v>
@@ -8240,19 +8261,19 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B243" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C243" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D243" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E243" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F243" s="2">
         <v>863</v>
@@ -8260,272 +8281,272 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B244" t="s">
+        <v>278</v>
+      </c>
+      <c r="C244" t="s">
         <v>279</v>
       </c>
-      <c r="C244" t="s">
-        <v>280</v>
-      </c>
       <c r="D244" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E244" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F244" s="2">
         <v>832</v>
       </c>
       <c r="G244" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B245" t="s">
+        <v>280</v>
+      </c>
+      <c r="C245" t="s">
         <v>281</v>
       </c>
-      <c r="C245" t="s">
-        <v>282</v>
-      </c>
       <c r="D245" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E245" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F245" s="2">
         <v>832</v>
       </c>
       <c r="G245" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B246" t="s">
+        <v>282</v>
+      </c>
+      <c r="C246" t="s">
         <v>283</v>
       </c>
-      <c r="C246" t="s">
-        <v>284</v>
-      </c>
       <c r="D246" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E246" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F246" s="2">
         <v>777</v>
       </c>
       <c r="G246" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B247" t="s">
+        <v>284</v>
+      </c>
+      <c r="C247" t="s">
         <v>285</v>
       </c>
-      <c r="C247" t="s">
-        <v>286</v>
-      </c>
       <c r="D247" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F247" s="2">
         <v>755</v>
       </c>
       <c r="G247" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B248" t="s">
+        <v>286</v>
+      </c>
+      <c r="C248" t="s">
         <v>287</v>
       </c>
-      <c r="C248" t="s">
-        <v>288</v>
-      </c>
       <c r="D248" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E248" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F248" s="2">
         <v>740</v>
       </c>
       <c r="G248" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B249" t="s">
+        <v>288</v>
+      </c>
+      <c r="C249" t="s">
         <v>289</v>
       </c>
-      <c r="C249" t="s">
-        <v>290</v>
-      </c>
       <c r="D249" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E249" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F249" s="2">
         <v>647</v>
       </c>
       <c r="G249" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B250" t="s">
+        <v>290</v>
+      </c>
+      <c r="C250" t="s">
         <v>291</v>
       </c>
-      <c r="C250" t="s">
-        <v>292</v>
-      </c>
       <c r="D250" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E250" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F250" s="2">
         <v>647</v>
       </c>
       <c r="G250" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B251" t="s">
+        <v>292</v>
+      </c>
+      <c r="C251" t="s">
         <v>293</v>
       </c>
-      <c r="C251" t="s">
-        <v>294</v>
-      </c>
       <c r="D251" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E251" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F251" s="2">
         <v>642</v>
       </c>
       <c r="G251" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B252" t="s">
+        <v>294</v>
+      </c>
+      <c r="C252" t="s">
         <v>295</v>
       </c>
-      <c r="C252" t="s">
-        <v>296</v>
-      </c>
       <c r="D252" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E252" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F252" s="2">
         <v>632</v>
       </c>
       <c r="G252" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B253" t="s">
+        <v>296</v>
+      </c>
+      <c r="C253" t="s">
         <v>297</v>
       </c>
-      <c r="C253" t="s">
-        <v>298</v>
-      </c>
       <c r="D253" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E253" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F253" s="2">
         <v>601</v>
       </c>
       <c r="G253" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B254" t="s">
+        <v>298</v>
+      </c>
+      <c r="C254" t="s">
         <v>299</v>
       </c>
-      <c r="C254" t="s">
-        <v>300</v>
-      </c>
       <c r="D254" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E254" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F254" s="2">
         <v>586</v>
       </c>
       <c r="G254" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B255" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C255" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D255" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E255" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F255" s="2">
         <v>260</v>
@@ -8533,19 +8554,19 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B256" t="s">
+        <v>300</v>
+      </c>
+      <c r="C256" t="s">
         <v>301</v>
       </c>
-      <c r="C256" t="s">
-        <v>302</v>
-      </c>
       <c r="D256" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E256" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F256" s="2">
         <v>260</v>
@@ -8553,19 +8574,19 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B257" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C257" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D257" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E257" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F257" s="2">
         <v>228</v>
@@ -8573,19 +8594,19 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B258" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C258" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D258" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E258" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F258" s="2">
         <v>221</v>
@@ -8593,19 +8614,19 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B259" t="s">
+        <v>303</v>
+      </c>
+      <c r="C259" t="s">
         <v>304</v>
       </c>
-      <c r="C259" t="s">
-        <v>305</v>
-      </c>
       <c r="D259" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E259" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F259" s="2">
         <v>182</v>
@@ -8613,19 +8634,19 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B260" t="s">
+        <v>305</v>
+      </c>
+      <c r="C260" t="s">
         <v>306</v>
       </c>
-      <c r="C260" t="s">
-        <v>307</v>
-      </c>
       <c r="D260" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E260" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F260" s="2">
         <v>182</v>
@@ -8633,19 +8654,19 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B261" t="s">
+        <v>307</v>
+      </c>
+      <c r="C261" t="s">
         <v>308</v>
       </c>
-      <c r="C261" t="s">
-        <v>309</v>
-      </c>
       <c r="D261" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E261" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F261" s="2">
         <v>180</v>
@@ -8653,19 +8674,19 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B262" t="s">
+        <v>309</v>
+      </c>
+      <c r="C262" t="s">
         <v>310</v>
       </c>
-      <c r="C262" t="s">
-        <v>311</v>
-      </c>
       <c r="D262" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E262" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F262" s="2">
         <v>176</v>
@@ -8673,19 +8694,19 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B263" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C263" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D263" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E263" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F263" s="2">
         <v>163</v>
@@ -8693,19 +8714,19 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B264" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C264" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D264" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E264" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F264" s="2">
         <v>3274</v>
@@ -8713,19 +8734,19 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B265" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C265" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D265" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E265" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F265" s="2">
         <v>1233</v>
@@ -8733,19 +8754,19 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B266" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C266" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D266" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E266" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F266" s="2">
         <v>662</v>
@@ -8753,19 +8774,19 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B267" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C267" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D267" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E267" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F267" s="2">
         <v>130</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VSCode\Test\my-vue-app\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jim20\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFEDE22-7658-4A0B-82F4-837D24EB94F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE71C458-6711-47B7-965D-6D280F39BEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{BFCE4DB1-B638-4533-A727-1E11ECBF49A7}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{BFCE4DB1-B638-4533-A727-1E11ECBF49A7}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="851">
   <si>
     <t>Category</t>
   </si>
@@ -2405,6 +2405,300 @@
   </si>
   <si>
     <t>巧克力、麵包-白麵包-長棍麵包-佛卡夏、蘋果-葡萄-麝香葡萄-草莓-芒果-鳳梨-香蕉-桃子-柳橙-哈密瓜</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trending</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色的料理</t>
+  </si>
+  <si>
+    <t>綠色的料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、綠色的料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、黃色的料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、綠色的料理、黃色的料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色的料理、白色的料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、白色的料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色的料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、白色的料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、綠色的料理、白色的料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色的料理、粉紅色的物品</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉紅色的物品</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、粉紅色的物品</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、冰涼果汁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、冰涼果汁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色的料理、冰涼果汁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>秋季美食</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色的料理、秋季美食</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、秋季美食</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、秋季美食</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色的料理、暖心料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、暖心料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉紅色的物品、暖心料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色的料理、暖心料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>暖心料理</t>
+  </si>
+  <si>
+    <t>暖心料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>秋季美食、暖心料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、暖心料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色的料理、秋季美食、暖心料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色的料理、秋季美食、暖心料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色的料理、白色的料理、秋季美食、暖心料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色的料理、白色的料理、暖心料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色的料理、粉紅色的物品、暖心料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>暖心料理、茶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、暖心料理、茶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、暖心料理、茶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色的料理、暖心料理、茶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、粉紅色的物品、暖心料理、茶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉紅色的物品、暖心料理、茶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色的料理、黃色的料理、暖心料理、茶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、秋季美食、暖心料理、茶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色的料理、秋季美食、暖心料理、茶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、冰涼果汁、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰涼果汁、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、暖心料理、茶、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色的料理、暖心料理、茶、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、暖心料理、茶、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉紅色的物品、冰涼果汁、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、冰涼果汁、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>暖心料理、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色的料理、冰涼果汁、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色的料理、冰涼果汁、秋季美食、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、冰涼果汁、秋季美食、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>暖心料理、茶、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>秋季美食、暖心料理、茶、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、秋季美食、暖心料理、茶、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、粉紅色的物品、暖心料理、茶、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉紅色的物品、暖心料理、茶、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰涼果汁、秋季美食、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、冰涼果汁、秋季美食、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、粉紅色的物品、冰涼果汁、甜飲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色的料理、甜點</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、白色的料理、甜點</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、甜點</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>甜點</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、甜點</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>秋季美食、甜點</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色的料理、秋季美食、甜點</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色的料理、甜點</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色的料理、秋季美食、甜點</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃色的料理、秋季美食、甜點</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2415,7 +2709,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2570,15 +2864,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -2882,7 +3167,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3009,11 +3294,8 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3024,52 +3306,50 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="43">
-    <cellStyle name="20% - 輔色1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 輔色2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 輔色3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 輔色4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 輔色5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 輔色6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 輔色1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 輔色2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 輔色3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 輔色4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 輔色5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 輔色6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 輔色1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 輔色2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 輔色3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 輔色4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 輔色5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 輔色6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="中等" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="合計" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="計算方式" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="連結的儲存格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="備註" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="超連結" xfId="42" builtinId="8"/>
-    <cellStyle name="說明文字" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="輔色1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="輔色2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="輔色3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="輔色4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="輔色5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="輔色6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="標題" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="標題 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="標題 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="標題 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="標題 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="輸入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="輸出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="檢查儲存格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="壞" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="警告文字" xfId="14" builtinId="11" customBuiltin="1"/>
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3085,9 +3365,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3125,7 +3405,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3231,7 +3511,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3373,7 +3653,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3382,18 +3662,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE04E7DD-F155-4289-B904-E214A34C0638}">
   <dimension ref="A1:H267"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="2" max="2" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="148.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="100.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="69.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="148.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="100.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="69.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3415,9 +3695,11 @@
       <c r="G1" t="s">
         <v>709</v>
       </c>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H1" s="3" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3436,9 +3718,11 @@
       <c r="F2" s="2">
         <v>1859</v>
       </c>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3457,8 +3741,11 @@
       <c r="F3" s="2">
         <v>1309</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3478,7 +3765,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3497,8 +3784,11 @@
       <c r="F5" s="2">
         <v>598</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3517,8 +3807,11 @@
       <c r="F6" s="2">
         <v>404</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3830,11 @@
       <c r="F7" s="2">
         <v>260</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H7" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3557,8 +3853,11 @@
       <c r="F8" s="2">
         <v>137</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H8" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3577,8 +3876,11 @@
       <c r="F9" s="2">
         <v>126</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H9" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3597,8 +3899,11 @@
       <c r="F10" s="2">
         <v>2429</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -3617,8 +3922,11 @@
       <c r="F11" s="2">
         <v>1197</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -3637,8 +3945,11 @@
       <c r="F12" s="2">
         <v>677</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H12" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3657,8 +3968,11 @@
       <c r="F13" s="2">
         <v>325</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3680,8 +3994,11 @@
       <c r="G14" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H14" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -3703,8 +4020,11 @@
       <c r="G15" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H15" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -3726,8 +4046,11 @@
       <c r="G16" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -3749,8 +4072,11 @@
       <c r="G17" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -3772,8 +4098,11 @@
       <c r="G18" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -3795,8 +4124,11 @@
       <c r="G19" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>711</v>
       </c>
@@ -3815,8 +4147,11 @@
       <c r="F20" s="2">
         <v>709</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -3835,8 +4170,11 @@
       <c r="F21" s="2">
         <v>490</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -3858,8 +4196,11 @@
       <c r="G22" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -3881,8 +4222,11 @@
       <c r="G23" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -3901,8 +4245,11 @@
       <c r="F24" s="2">
         <v>10098</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -3924,8 +4271,11 @@
       <c r="G25" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -3945,7 +4295,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -3965,7 +4315,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -3985,7 +4335,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -4004,8 +4354,11 @@
       <c r="F29" s="2">
         <v>1377</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H29" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>14</v>
       </c>
@@ -4025,7 +4378,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -4044,8 +4397,11 @@
       <c r="F31" s="2">
         <v>1276</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H31" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -4064,8 +4420,11 @@
       <c r="F32" s="2">
         <v>1213</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -4085,7 +4444,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>14</v>
       </c>
@@ -4105,7 +4464,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -4125,7 +4484,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -4147,8 +4506,11 @@
       <c r="G36" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -4167,8 +4529,11 @@
       <c r="F37" s="2">
         <v>882</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H37" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -4188,7 +4553,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -4208,7 +4573,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -4228,7 +4593,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -4247,8 +4612,11 @@
       <c r="F41" s="2">
         <v>801</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H41" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
         <v>14</v>
       </c>
@@ -4267,8 +4635,11 @@
       <c r="F42" s="2">
         <v>747</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
         <v>14</v>
       </c>
@@ -4287,8 +4658,11 @@
       <c r="F43" s="2">
         <v>743</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H43" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -4307,8 +4681,11 @@
       <c r="F44" s="2">
         <v>677</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H44" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -4328,7 +4705,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" t="s">
         <v>14</v>
       </c>
@@ -4348,7 +4725,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8">
       <c r="A47" t="s">
         <v>14</v>
       </c>
@@ -4368,7 +4745,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -4387,8 +4764,11 @@
       <c r="F48" s="2">
         <v>602</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H48" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
         <v>14</v>
       </c>
@@ -4407,8 +4787,11 @@
       <c r="F49" s="2">
         <v>563</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H49" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -4427,8 +4810,11 @@
       <c r="F50" s="2">
         <v>458</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H50" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -4448,7 +4834,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
         <v>14</v>
       </c>
@@ -4468,7 +4854,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
         <v>14</v>
       </c>
@@ -4487,8 +4873,11 @@
       <c r="F53" s="2">
         <v>396</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H53" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
         <v>14</v>
       </c>
@@ -4508,7 +4897,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
         <v>14</v>
       </c>
@@ -4528,7 +4917,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
         <v>14</v>
       </c>
@@ -4548,7 +4937,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
         <v>14</v>
       </c>
@@ -4567,8 +4956,11 @@
       <c r="F57" s="2">
         <v>205</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H57" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
         <v>14</v>
       </c>
@@ -4587,8 +4979,11 @@
       <c r="F58" s="2">
         <v>195</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H58" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
         <v>14</v>
       </c>
@@ -4607,8 +5002,11 @@
       <c r="F59" s="2">
         <v>117</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H59" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
         <v>14</v>
       </c>
@@ -4628,7 +5026,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
         <v>14</v>
       </c>
@@ -4648,7 +5046,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
         <v>14</v>
       </c>
@@ -4667,8 +5065,11 @@
       <c r="F62" s="2">
         <v>195</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H62" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -4687,8 +5088,11 @@
       <c r="F63" s="2">
         <v>195</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H63" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
         <v>14</v>
       </c>
@@ -4707,8 +5111,11 @@
       <c r="F64" s="2">
         <v>1509</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H64" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -4727,8 +5134,11 @@
       <c r="F65" s="2">
         <v>886</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H65" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -4747,8 +5157,11 @@
       <c r="F66" s="2">
         <v>1920</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H66" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -4768,7 +5181,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -4788,7 +5201,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
         <v>14</v>
       </c>
@@ -4808,7 +5221,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
         <v>14</v>
       </c>
@@ -4830,8 +5243,11 @@
       <c r="G70" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H70" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -4851,7 +5267,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -4871,7 +5287,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
         <v>14</v>
       </c>
@@ -4894,7 +5310,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -4914,7 +5330,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -4933,8 +5349,11 @@
       <c r="F75" s="2">
         <v>301</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H75" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -4953,8 +5372,11 @@
       <c r="F76" s="2">
         <v>202</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H76" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -4971,7 +5393,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8">
       <c r="A78" t="s">
         <v>14</v>
       </c>
@@ -4987,8 +5409,11 @@
       <c r="F78" s="2">
         <v>182</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H78" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" t="s">
         <v>14</v>
       </c>
@@ -5004,8 +5429,11 @@
       <c r="F79" s="2">
         <v>91</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H79" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" t="s">
         <v>15</v>
       </c>
@@ -5022,7 +5450,7 @@
         <v>12353</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8">
       <c r="A81" t="s">
         <v>15</v>
       </c>
@@ -5039,7 +5467,7 @@
         <v>7508</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8">
       <c r="A82" t="s">
         <v>15</v>
       </c>
@@ -5056,7 +5484,7 @@
         <v>6957</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8">
       <c r="A83" t="s">
         <v>15</v>
       </c>
@@ -5073,7 +5501,7 @@
         <v>3724</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8">
       <c r="A84" t="s">
         <v>15</v>
       </c>
@@ -5090,7 +5518,7 @@
         <v>2784</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8">
       <c r="A85" t="s">
         <v>15</v>
       </c>
@@ -5109,8 +5537,11 @@
       <c r="G85" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H85" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -5129,8 +5560,11 @@
       <c r="G86" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H86" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -5147,7 +5581,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -5166,8 +5600,11 @@
       <c r="G88" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H88" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -5186,8 +5623,11 @@
       <c r="G89" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H89" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -5203,8 +5643,11 @@
       <c r="F90" s="2">
         <v>2295</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H90" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" t="s">
         <v>15</v>
       </c>
@@ -5223,8 +5666,11 @@
       <c r="G91" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H91" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -5240,8 +5686,11 @@
       <c r="F92" s="2">
         <v>2160</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H92" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93" t="s">
         <v>15</v>
       </c>
@@ -5257,8 +5706,11 @@
       <c r="F93" s="2">
         <v>2089</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H93" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" t="s">
         <v>15</v>
       </c>
@@ -5275,7 +5727,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8">
       <c r="A95" t="s">
         <v>15</v>
       </c>
@@ -5291,8 +5743,11 @@
       <c r="F95" s="2">
         <v>1817</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H95" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" t="s">
         <v>15</v>
       </c>
@@ -5308,8 +5763,11 @@
       <c r="F96" s="2">
         <v>1760</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H96" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
         <v>15</v>
       </c>
@@ -5326,7 +5784,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8">
       <c r="A98" t="s">
         <v>15</v>
       </c>
@@ -5345,8 +5803,11 @@
       <c r="G98" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H98" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99" t="s">
         <v>15</v>
       </c>
@@ -5362,8 +5823,11 @@
       <c r="F99" s="2">
         <v>1552</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H99" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
       <c r="A100" t="s">
         <v>15</v>
       </c>
@@ -5379,8 +5843,11 @@
       <c r="F100" s="2">
         <v>1469</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H100" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
       <c r="A101" t="s">
         <v>15</v>
       </c>
@@ -5397,7 +5864,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8">
       <c r="A102" t="s">
         <v>15</v>
       </c>
@@ -5413,8 +5880,11 @@
       <c r="F102" s="2">
         <v>1449</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H102" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103" t="s">
         <v>15</v>
       </c>
@@ -5430,8 +5900,11 @@
       <c r="F103" s="2">
         <v>1437</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H103" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104" t="s">
         <v>15</v>
       </c>
@@ -5448,7 +5921,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8">
       <c r="A105" t="s">
         <v>15</v>
       </c>
@@ -5464,8 +5937,11 @@
       <c r="F105" s="2">
         <v>1424</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H105" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106" t="s">
         <v>15</v>
       </c>
@@ -5481,8 +5957,11 @@
       <c r="F106" s="2">
         <v>1410</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H106" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
       <c r="A107" t="s">
         <v>15</v>
       </c>
@@ -5498,8 +5977,11 @@
       <c r="F107" s="2">
         <v>1410</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H107" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108" t="s">
         <v>15</v>
       </c>
@@ -5516,7 +5998,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8">
       <c r="A109" t="s">
         <v>15</v>
       </c>
@@ -5533,7 +6015,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8">
       <c r="A110" t="s">
         <v>15</v>
       </c>
@@ -5550,7 +6032,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8">
       <c r="A111" t="s">
         <v>15</v>
       </c>
@@ -5566,8 +6048,11 @@
       <c r="F111" s="2">
         <v>1325</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H111" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112" t="s">
         <v>15</v>
       </c>
@@ -5583,8 +6068,11 @@
       <c r="F112" s="2">
         <v>1316</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H112" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
       <c r="A113" t="s">
         <v>15</v>
       </c>
@@ -5600,8 +6088,11 @@
       <c r="F113" s="2">
         <v>1304</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H113" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
       <c r="A114" t="s">
         <v>15</v>
       </c>
@@ -5617,8 +6108,11 @@
       <c r="F114" s="2">
         <v>1271</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H114" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
       <c r="A115" t="s">
         <v>15</v>
       </c>
@@ -5635,7 +6129,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8">
       <c r="A116" t="s">
         <v>15</v>
       </c>
@@ -5651,8 +6145,11 @@
       <c r="F116" s="2">
         <v>1200</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H116" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
       <c r="A117" t="s">
         <v>15</v>
       </c>
@@ -5669,7 +6166,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8">
       <c r="A118" t="s">
         <v>15</v>
       </c>
@@ -5686,7 +6183,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8">
       <c r="A119" t="s">
         <v>15</v>
       </c>
@@ -5703,7 +6200,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8">
       <c r="A120" t="s">
         <v>15</v>
       </c>
@@ -5719,8 +6216,11 @@
       <c r="F120" s="2">
         <v>1152</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H120" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
       <c r="A121" t="s">
         <v>15</v>
       </c>
@@ -5736,8 +6236,11 @@
       <c r="F121" s="2">
         <v>1151</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H121" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
       <c r="A122" t="s">
         <v>15</v>
       </c>
@@ -5756,8 +6259,11 @@
       <c r="G122" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H122" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
       <c r="A123" t="s">
         <v>15</v>
       </c>
@@ -5773,8 +6279,11 @@
       <c r="F123" s="2">
         <v>1142</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H123" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
       <c r="A124" t="s">
         <v>15</v>
       </c>
@@ -5793,8 +6302,11 @@
       <c r="G124" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H124" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
       <c r="A125" t="s">
         <v>15</v>
       </c>
@@ -5811,7 +6323,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8">
       <c r="A126" t="s">
         <v>15</v>
       </c>
@@ -5827,8 +6339,11 @@
       <c r="F126" s="2">
         <v>1073</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H126" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
       <c r="A127" t="s">
         <v>15</v>
       </c>
@@ -5845,7 +6360,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8">
       <c r="A128" t="s">
         <v>15</v>
       </c>
@@ -5861,8 +6376,11 @@
       <c r="F128" s="2">
         <v>937</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H128" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" t="s">
         <v>15</v>
       </c>
@@ -5879,7 +6397,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8">
       <c r="A130" t="s">
         <v>15</v>
       </c>
@@ -5895,8 +6413,11 @@
       <c r="F130" s="2">
         <v>911</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H130" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" t="s">
         <v>15</v>
       </c>
@@ -5912,8 +6433,11 @@
       <c r="F131" s="2">
         <v>874</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H131" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132" t="s">
         <v>15</v>
       </c>
@@ -5929,8 +6453,11 @@
       <c r="F132" s="2">
         <v>867</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H132" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133" t="s">
         <v>15</v>
       </c>
@@ -5947,7 +6474,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8">
       <c r="A134" t="s">
         <v>15</v>
       </c>
@@ -5963,8 +6490,11 @@
       <c r="F134" s="2">
         <v>837</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H134" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135" t="s">
         <v>15</v>
       </c>
@@ -5983,8 +6513,11 @@
       <c r="G135" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H135" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136" t="s">
         <v>15</v>
       </c>
@@ -6000,8 +6533,11 @@
       <c r="F136" s="2">
         <v>817</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H136" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137" t="s">
         <v>15</v>
       </c>
@@ -6017,8 +6553,11 @@
       <c r="F137" s="2">
         <v>809</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H137" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" t="s">
         <v>15</v>
       </c>
@@ -6035,7 +6574,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8">
       <c r="A139" t="s">
         <v>15</v>
       </c>
@@ -6055,7 +6594,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8">
       <c r="A140" t="s">
         <v>15</v>
       </c>
@@ -6072,7 +6611,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8">
       <c r="A141" t="s">
         <v>15</v>
       </c>
@@ -6088,8 +6627,11 @@
       <c r="F141" s="2">
         <v>721</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H141" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142" t="s">
         <v>15</v>
       </c>
@@ -6105,8 +6647,11 @@
       <c r="F142" s="2">
         <v>664</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H142" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143" t="s">
         <v>15</v>
       </c>
@@ -6122,8 +6667,11 @@
       <c r="F143" s="2">
         <v>657</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H143" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
       <c r="A144" t="s">
         <v>15</v>
       </c>
@@ -6139,8 +6687,11 @@
       <c r="F144" s="2">
         <v>650</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H144" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145" t="s">
         <v>15</v>
       </c>
@@ -6159,8 +6710,11 @@
       <c r="G145" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H145" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -6179,8 +6733,11 @@
       <c r="G146" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H146" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
       <c r="A147" t="s">
         <v>15</v>
       </c>
@@ -6196,8 +6753,11 @@
       <c r="F147" s="2">
         <v>647</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H147" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
       <c r="A148" t="s">
         <v>15</v>
       </c>
@@ -6213,8 +6773,11 @@
       <c r="F148" s="2">
         <v>616</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H148" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
       <c r="A149" t="s">
         <v>15</v>
       </c>
@@ -6230,8 +6793,11 @@
       <c r="F149" s="2">
         <v>604</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H149" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
       <c r="A150" t="s">
         <v>15</v>
       </c>
@@ -6250,8 +6816,11 @@
       <c r="G150" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H150" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
       <c r="A151" t="s">
         <v>15</v>
       </c>
@@ -6267,8 +6836,11 @@
       <c r="F151" s="2">
         <v>451</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H151" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
       <c r="A152" t="s">
         <v>15</v>
       </c>
@@ -6284,8 +6856,11 @@
       <c r="F152" s="2">
         <v>444</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H152" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
       <c r="A153" t="s">
         <v>15</v>
       </c>
@@ -6301,8 +6876,11 @@
       <c r="F153" s="2">
         <v>375</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H153" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
       <c r="A154" t="s">
         <v>15</v>
       </c>
@@ -6318,8 +6896,11 @@
       <c r="F154" s="2">
         <v>370</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H154" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
       <c r="A155" t="s">
         <v>15</v>
       </c>
@@ -6336,7 +6917,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8">
       <c r="A156" t="s">
         <v>15</v>
       </c>
@@ -6352,8 +6933,11 @@
       <c r="F156" s="2">
         <v>329</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H156" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
       <c r="A157" t="s">
         <v>15</v>
       </c>
@@ -6370,7 +6954,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8">
       <c r="A158" t="s">
         <v>15</v>
       </c>
@@ -6386,8 +6970,11 @@
       <c r="F158" s="2">
         <v>248</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H158" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
       <c r="A159" t="s">
         <v>15</v>
       </c>
@@ -6403,8 +6990,11 @@
       <c r="F159" s="2">
         <v>195</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H159" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
       <c r="A160" t="s">
         <v>16</v>
       </c>
@@ -6426,8 +7016,11 @@
       <c r="G160" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H160" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
       <c r="A161" t="s">
         <v>16</v>
       </c>
@@ -6449,8 +7042,11 @@
       <c r="G161" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H161" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
       <c r="A162" t="s">
         <v>16</v>
       </c>
@@ -6472,8 +7068,11 @@
       <c r="G162" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H162" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
       <c r="A163" t="s">
         <v>16</v>
       </c>
@@ -6495,8 +7094,11 @@
       <c r="G163" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H163" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
       <c r="A164" t="s">
         <v>16</v>
       </c>
@@ -6518,8 +7120,11 @@
       <c r="G164" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H164" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
       <c r="A165" t="s">
         <v>16</v>
       </c>
@@ -6541,8 +7146,11 @@
       <c r="G165" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H165" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
       <c r="A166" t="s">
         <v>16</v>
       </c>
@@ -6564,8 +7172,11 @@
       <c r="G166" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H166" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
       <c r="A167" t="s">
         <v>16</v>
       </c>
@@ -6587,8 +7198,11 @@
       <c r="G167" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H167" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
       <c r="A168" t="s">
         <v>16</v>
       </c>
@@ -6610,8 +7224,11 @@
       <c r="G168" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H168" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
       <c r="A169" t="s">
         <v>16</v>
       </c>
@@ -6633,8 +7250,11 @@
       <c r="G169" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H169" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
       <c r="A170" t="s">
         <v>16</v>
       </c>
@@ -6656,8 +7276,11 @@
       <c r="G170" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H170" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
       <c r="A171" t="s">
         <v>16</v>
       </c>
@@ -6679,8 +7302,11 @@
       <c r="G171" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H171" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
       <c r="A172" t="s">
         <v>16</v>
       </c>
@@ -6702,8 +7328,11 @@
       <c r="G172" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H172" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
       <c r="A173" t="s">
         <v>16</v>
       </c>
@@ -6725,8 +7354,11 @@
       <c r="G173" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H173" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -6748,8 +7380,11 @@
       <c r="G174" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H174" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
       <c r="A175" t="s">
         <v>16</v>
       </c>
@@ -6771,8 +7406,11 @@
       <c r="G175" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H175" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
       <c r="A176" t="s">
         <v>16</v>
       </c>
@@ -6794,8 +7432,11 @@
       <c r="G176" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H176" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
       <c r="A177" t="s">
         <v>16</v>
       </c>
@@ -6817,8 +7458,11 @@
       <c r="G177" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H177" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
       <c r="A178" t="s">
         <v>16</v>
       </c>
@@ -6840,8 +7484,11 @@
       <c r="G178" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H178" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
       <c r="A179" t="s">
         <v>16</v>
       </c>
@@ -6863,8 +7510,11 @@
       <c r="G179" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H179" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
       <c r="A180" t="s">
         <v>16</v>
       </c>
@@ -6886,8 +7536,11 @@
       <c r="G180" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H180" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
       <c r="A181" t="s">
         <v>16</v>
       </c>
@@ -6909,8 +7562,11 @@
       <c r="G181" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H181" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
       <c r="A182" t="s">
         <v>16</v>
       </c>
@@ -6932,8 +7588,11 @@
       <c r="G182" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H182" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -6955,8 +7614,11 @@
       <c r="G183" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H183" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
       <c r="A184" t="s">
         <v>16</v>
       </c>
@@ -6978,8 +7640,11 @@
       <c r="G184" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H184" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
       <c r="A185" t="s">
         <v>16</v>
       </c>
@@ -7001,8 +7666,11 @@
       <c r="G185" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H185" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
       <c r="A186" t="s">
         <v>16</v>
       </c>
@@ -7024,8 +7692,11 @@
       <c r="G186" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H186" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
       <c r="A187" t="s">
         <v>16</v>
       </c>
@@ -7047,8 +7718,11 @@
       <c r="G187" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H187" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
       <c r="A188" t="s">
         <v>16</v>
       </c>
@@ -7070,8 +7744,11 @@
       <c r="G188" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H188" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
       <c r="A189" t="s">
         <v>16</v>
       </c>
@@ -7093,8 +7770,11 @@
       <c r="G189" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H189" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
       <c r="A190" t="s">
         <v>16</v>
       </c>
@@ -7116,8 +7796,11 @@
       <c r="G190" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H190" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
       <c r="A191" t="s">
         <v>16</v>
       </c>
@@ -7139,8 +7822,11 @@
       <c r="G191" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H191" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
       <c r="A192" t="s">
         <v>16</v>
       </c>
@@ -7162,8 +7848,11 @@
       <c r="G192" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H192" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
       <c r="A193" t="s">
         <v>16</v>
       </c>
@@ -7185,8 +7874,11 @@
       <c r="G193" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H193" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
       <c r="A194" t="s">
         <v>16</v>
       </c>
@@ -7208,8 +7900,11 @@
       <c r="G194" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H194" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
       <c r="A195" t="s">
         <v>16</v>
       </c>
@@ -7231,8 +7926,11 @@
       <c r="G195" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H195" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
       <c r="A196" t="s">
         <v>16</v>
       </c>
@@ -7254,8 +7952,11 @@
       <c r="G196" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H196" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
       <c r="A197" t="s">
         <v>16</v>
       </c>
@@ -7277,8 +7978,11 @@
       <c r="G197" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H197" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
       <c r="A198" t="s">
         <v>16</v>
       </c>
@@ -7300,8 +8004,11 @@
       <c r="G198" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H198" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
       <c r="A199" t="s">
         <v>16</v>
       </c>
@@ -7323,8 +8030,11 @@
       <c r="G199" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H199" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
       <c r="A200" t="s">
         <v>16</v>
       </c>
@@ -7346,8 +8056,11 @@
       <c r="G200" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H200" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
       <c r="A201" t="s">
         <v>17</v>
       </c>
@@ -7366,8 +8079,11 @@
       <c r="F201" s="2">
         <v>85</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H201" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
       <c r="A202" t="s">
         <v>17</v>
       </c>
@@ -7386,8 +8102,11 @@
       <c r="F202" s="2">
         <v>325</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H202" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
       <c r="A203" t="s">
         <v>17</v>
       </c>
@@ -7407,7 +8126,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8">
       <c r="A204" t="s">
         <v>17</v>
       </c>
@@ -7429,8 +8148,11 @@
       <c r="G204" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H204" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8">
       <c r="A205" t="s">
         <v>17</v>
       </c>
@@ -7449,8 +8171,11 @@
       <c r="F205" s="2">
         <v>1020</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H205" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
       <c r="A206" t="s">
         <v>17</v>
       </c>
@@ -7472,8 +8197,11 @@
       <c r="G206" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H206" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
       <c r="A207" t="s">
         <v>17</v>
       </c>
@@ -7495,8 +8223,11 @@
       <c r="G207" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H207" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
       <c r="A208" t="s">
         <v>17</v>
       </c>
@@ -7518,8 +8249,11 @@
       <c r="G208" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H208" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
       <c r="A209" t="s">
         <v>17</v>
       </c>
@@ -7541,8 +8275,11 @@
       <c r="G209" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H209" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
       <c r="A210" t="s">
         <v>17</v>
       </c>
@@ -7564,8 +8301,11 @@
       <c r="G210" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H210" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
       <c r="A211" t="s">
         <v>17</v>
       </c>
@@ -7587,8 +8327,11 @@
       <c r="G211" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H211" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
       <c r="A212" t="s">
         <v>17</v>
       </c>
@@ -7610,8 +8353,11 @@
       <c r="G212" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H212" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
       <c r="A213" t="s">
         <v>17</v>
       </c>
@@ -7633,8 +8379,11 @@
       <c r="G213" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H213" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
       <c r="A214" t="s">
         <v>17</v>
       </c>
@@ -7653,8 +8402,11 @@
       <c r="F214" s="2">
         <v>935</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H214" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
       <c r="A215" t="s">
         <v>17</v>
       </c>
@@ -7673,8 +8425,11 @@
       <c r="F215" s="2">
         <v>855</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H215" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
       <c r="A216" t="s">
         <v>17</v>
       </c>
@@ -7693,8 +8448,11 @@
       <c r="F216" s="2">
         <v>826</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H216" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
       <c r="A217" t="s">
         <v>17</v>
       </c>
@@ -7716,8 +8474,11 @@
       <c r="G217" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H217" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
       <c r="A218" t="s">
         <v>17</v>
       </c>
@@ -7739,8 +8500,11 @@
       <c r="G218" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H218" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
       <c r="A219" t="s">
         <v>17</v>
       </c>
@@ -7759,8 +8523,11 @@
       <c r="F219" s="2">
         <v>756</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H219" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
       <c r="A220" t="s">
         <v>17</v>
       </c>
@@ -7782,8 +8549,11 @@
       <c r="G220" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H220" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8">
       <c r="A221" t="s">
         <v>17</v>
       </c>
@@ -7802,8 +8572,11 @@
       <c r="F221" s="2">
         <v>658</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H221" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
       <c r="A222" t="s">
         <v>17</v>
       </c>
@@ -7825,8 +8598,11 @@
       <c r="G222" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H222" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8">
       <c r="A223" t="s">
         <v>17</v>
       </c>
@@ -7845,8 +8621,11 @@
       <c r="F223" s="2">
         <v>429</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H223" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
       <c r="A224" t="s">
         <v>17</v>
       </c>
@@ -7868,8 +8647,11 @@
       <c r="G224" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H224" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8">
       <c r="A225" t="s">
         <v>17</v>
       </c>
@@ -7891,8 +8673,11 @@
       <c r="G225" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H225" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8">
       <c r="A226" t="s">
         <v>17</v>
       </c>
@@ -7914,8 +8699,11 @@
       <c r="G226" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H226" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8">
       <c r="A227" t="s">
         <v>17</v>
       </c>
@@ -7934,8 +8722,11 @@
       <c r="F227" s="2">
         <v>390</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H227" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
       <c r="A228" t="s">
         <v>17</v>
       </c>
@@ -7957,8 +8748,11 @@
       <c r="G228" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H228" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
       <c r="A229" t="s">
         <v>17</v>
       </c>
@@ -7980,8 +8774,11 @@
       <c r="G229" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H229" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
       <c r="A230" t="s">
         <v>17</v>
       </c>
@@ -8003,8 +8800,11 @@
       <c r="G230" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H230" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
       <c r="A231" t="s">
         <v>17</v>
       </c>
@@ -8026,8 +8826,11 @@
       <c r="G231" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H231" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8">
       <c r="A232" t="s">
         <v>17</v>
       </c>
@@ -8049,8 +8852,11 @@
       <c r="G232" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H232" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
       <c r="A233" t="s">
         <v>17</v>
       </c>
@@ -8069,8 +8875,11 @@
       <c r="F233" s="2">
         <v>260</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H233" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
       <c r="A234" t="s">
         <v>17</v>
       </c>
@@ -8092,8 +8901,11 @@
       <c r="G234" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H234" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
       <c r="A235" t="s">
         <v>17</v>
       </c>
@@ -8115,8 +8927,11 @@
       <c r="G235" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H235" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
       <c r="A236" t="s">
         <v>17</v>
       </c>
@@ -8135,8 +8950,11 @@
       <c r="F236" s="2">
         <v>156</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H236" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8">
       <c r="A237" t="s">
         <v>17</v>
       </c>
@@ -8155,8 +8973,11 @@
       <c r="F237" s="2">
         <v>55</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H237" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8">
       <c r="A238" t="s">
         <v>17</v>
       </c>
@@ -8175,8 +8996,11 @@
       <c r="F238" s="2">
         <v>9511</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H238" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
       <c r="A239" t="s">
         <v>17</v>
       </c>
@@ -8198,8 +9022,11 @@
       <c r="G239" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H239" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
       <c r="A240" t="s">
         <v>17</v>
       </c>
@@ -8218,8 +9045,11 @@
       <c r="F240" s="2">
         <v>1010</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H240" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8">
       <c r="A241" t="s">
         <v>17</v>
       </c>
@@ -8238,8 +9068,11 @@
       <c r="F241" s="2">
         <v>1007</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H241" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8">
       <c r="A242" t="s">
         <v>17</v>
       </c>
@@ -8258,8 +9091,11 @@
       <c r="F242" s="2">
         <v>932</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H242" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
       <c r="A243" t="s">
         <v>17</v>
       </c>
@@ -8278,8 +9114,11 @@
       <c r="F243" s="2">
         <v>863</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H243" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8">
       <c r="A244" t="s">
         <v>17</v>
       </c>
@@ -8301,8 +9140,11 @@
       <c r="G244" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H244" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8">
       <c r="A245" t="s">
         <v>17</v>
       </c>
@@ -8324,8 +9166,11 @@
       <c r="G245" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H245" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8">
       <c r="A246" t="s">
         <v>17</v>
       </c>
@@ -8347,8 +9192,11 @@
       <c r="G246" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H246" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8">
       <c r="A247" t="s">
         <v>17</v>
       </c>
@@ -8370,8 +9218,11 @@
       <c r="G247" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H247" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8">
       <c r="A248" t="s">
         <v>17</v>
       </c>
@@ -8393,8 +9244,11 @@
       <c r="G248" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H248" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8">
       <c r="A249" t="s">
         <v>17</v>
       </c>
@@ -8416,8 +9270,11 @@
       <c r="G249" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H249" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8">
       <c r="A250" t="s">
         <v>17</v>
       </c>
@@ -8439,8 +9296,11 @@
       <c r="G250" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H250" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8">
       <c r="A251" t="s">
         <v>17</v>
       </c>
@@ -8462,8 +9322,11 @@
       <c r="G251" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H251" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
       <c r="A252" t="s">
         <v>17</v>
       </c>
@@ -8485,8 +9348,11 @@
       <c r="G252" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H252" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
       <c r="A253" t="s">
         <v>17</v>
       </c>
@@ -8508,8 +9374,11 @@
       <c r="G253" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H253" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8">
       <c r="A254" t="s">
         <v>17</v>
       </c>
@@ -8531,8 +9400,11 @@
       <c r="G254" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H254" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8">
       <c r="A255" t="s">
         <v>17</v>
       </c>
@@ -8551,8 +9423,11 @@
       <c r="F255" s="2">
         <v>260</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H255" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8">
       <c r="A256" t="s">
         <v>17</v>
       </c>
@@ -8571,8 +9446,11 @@
       <c r="F256" s="2">
         <v>260</v>
       </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H256" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8">
       <c r="A257" t="s">
         <v>17</v>
       </c>
@@ -8591,8 +9469,11 @@
       <c r="F257" s="2">
         <v>228</v>
       </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H257" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8">
       <c r="A258" t="s">
         <v>17</v>
       </c>
@@ -8611,8 +9492,11 @@
       <c r="F258" s="2">
         <v>221</v>
       </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H258" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8">
       <c r="A259" t="s">
         <v>17</v>
       </c>
@@ -8631,8 +9515,11 @@
       <c r="F259" s="2">
         <v>182</v>
       </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H259" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8">
       <c r="A260" t="s">
         <v>17</v>
       </c>
@@ -8651,8 +9538,11 @@
       <c r="F260" s="2">
         <v>182</v>
       </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H260" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8">
       <c r="A261" t="s">
         <v>17</v>
       </c>
@@ -8671,8 +9561,11 @@
       <c r="F261" s="2">
         <v>180</v>
       </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H261" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8">
       <c r="A262" t="s">
         <v>17</v>
       </c>
@@ -8691,8 +9584,11 @@
       <c r="F262" s="2">
         <v>176</v>
       </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H262" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
       <c r="A263" t="s">
         <v>17</v>
       </c>
@@ -8711,8 +9607,11 @@
       <c r="F263" s="2">
         <v>163</v>
       </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H263" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8">
       <c r="A264" t="s">
         <v>17</v>
       </c>
@@ -8731,8 +9630,11 @@
       <c r="F264" s="2">
         <v>3274</v>
       </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H264" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
       <c r="A265" t="s">
         <v>17</v>
       </c>
@@ -8752,7 +9654,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8">
       <c r="A266" t="s">
         <v>17</v>
       </c>
@@ -8772,7 +9674,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8">
       <c r="A267" t="s">
         <v>17</v>
       </c>
